--- a/InputData/elec/BPMCCS/BAU Pol Mandated Cap Const Sched.xlsx
+++ b/InputData/elec/BPMCCS/BAU Pol Mandated Cap Const Sched.xlsx
@@ -14687,13 +14687,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59FEBC86-B4BF-4815-9A76-C415776EF2B7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43ED1489-0F0F-460E-8DB0-F645CB7D0188}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1145CB82-DA0B-43E0-AC74-05E3A110C197}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B79B8AEF-803A-4C5A-B04E-B80AE175902F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAFCB4CD-1E35-4C21-995D-D24C672E18AF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B24FF82-77E2-4C47-88CE-8E1D1040FA1D}"/>
 </file>
--- a/InputData/elec/BPMCCS/BAU Pol Mandated Cap Const Sched.xlsx
+++ b/InputData/elec/BPMCCS/BAU Pol Mandated Cap Const Sched.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\SouthKorea EPS\InputData\elec\BPMCCS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\South Korea\Models\eps-southkorea\InputData\elec\BPMCCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B2462BF-4B8D-46AE-AACC-CDBA4CE98D39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB0B8CE3-132D-48DA-A558-2AD31AB844D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1116" yWindow="492" windowWidth="22116" windowHeight="12852" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="43200" windowHeight="17145" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="AEO Table 9" sheetId="5" state="hidden" r:id="rId2"/>
     <sheet name="AEO_coal discrepency" sheetId="6" state="hidden" r:id="rId3"/>
     <sheet name="용량증설" sheetId="7" r:id="rId4"/>
-    <sheet name="BPMCCS" sheetId="2" r:id="rId5"/>
+    <sheet name="Nuclear Additions" sheetId="8" r:id="rId5"/>
+    <sheet name="BPMCCS" sheetId="2" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="395">
   <si>
     <t>Note:</t>
   </si>
@@ -943,6 +944,285 @@
   </si>
   <si>
     <t>hydrogen combined cycle</t>
+  </si>
+  <si>
+    <t>Reactor Name</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>Reactor Type</t>
+  </si>
+  <si>
+    <t>Reference Unit Power (MWe)</t>
+  </si>
+  <si>
+    <t>Construction Start</t>
+  </si>
+  <si>
+    <t>First Grid Connection</t>
+  </si>
+  <si>
+    <t>Hanbit 1</t>
+  </si>
+  <si>
+    <t>WH F</t>
+  </si>
+  <si>
+    <t>PWR</t>
+  </si>
+  <si>
+    <t>1981-06</t>
+  </si>
+  <si>
+    <t>1986-03</t>
+  </si>
+  <si>
+    <t>Hanbit 2</t>
+  </si>
+  <si>
+    <t>1981-12</t>
+  </si>
+  <si>
+    <t>1986-11</t>
+  </si>
+  <si>
+    <t>Hanbit 3</t>
+  </si>
+  <si>
+    <t>OPR-1000</t>
+  </si>
+  <si>
+    <t>1989-12</t>
+  </si>
+  <si>
+    <t>1994-10</t>
+  </si>
+  <si>
+    <t>Hanbit 4</t>
+  </si>
+  <si>
+    <t>1990-05</t>
+  </si>
+  <si>
+    <t>1995-07</t>
+  </si>
+  <si>
+    <t>Hanbit 5</t>
+  </si>
+  <si>
+    <t>1997-06</t>
+  </si>
+  <si>
+    <t>2001-12</t>
+  </si>
+  <si>
+    <t>Hanbit 6</t>
+  </si>
+  <si>
+    <t>1997-11</t>
+  </si>
+  <si>
+    <t>2002-09</t>
+  </si>
+  <si>
+    <t>Hanul 1</t>
+  </si>
+  <si>
+    <t>France CPI</t>
+  </si>
+  <si>
+    <t>1983-01</t>
+  </si>
+  <si>
+    <t>1988-04</t>
+  </si>
+  <si>
+    <t>Hanul 2</t>
+  </si>
+  <si>
+    <t>1983-07</t>
+  </si>
+  <si>
+    <t>1989-04</t>
+  </si>
+  <si>
+    <t>Hanul 3</t>
+  </si>
+  <si>
+    <t>1993-07</t>
+  </si>
+  <si>
+    <t>1998-01</t>
+  </si>
+  <si>
+    <t>Hanul 4</t>
+  </si>
+  <si>
+    <t>1993-11</t>
+  </si>
+  <si>
+    <t>1998-12</t>
+  </si>
+  <si>
+    <t>Hanul 5</t>
+  </si>
+  <si>
+    <t>1999-10</t>
+  </si>
+  <si>
+    <t>2003-12</t>
+  </si>
+  <si>
+    <t>Hanul 6</t>
+  </si>
+  <si>
+    <t>2000-09</t>
+  </si>
+  <si>
+    <t>2005-01</t>
+  </si>
+  <si>
+    <t>Kori 2</t>
+  </si>
+  <si>
+    <t>1977-12</t>
+  </si>
+  <si>
+    <t>1983-04</t>
+  </si>
+  <si>
+    <t>Kori 3</t>
+  </si>
+  <si>
+    <t>1979-10</t>
+  </si>
+  <si>
+    <t>1985-01</t>
+  </si>
+  <si>
+    <t>Kori 4</t>
+  </si>
+  <si>
+    <t>1980-04</t>
+  </si>
+  <si>
+    <t>1985-11</t>
+  </si>
+  <si>
+    <t>Saeul 1</t>
+  </si>
+  <si>
+    <t>APR-1400</t>
+  </si>
+  <si>
+    <t>2008-10</t>
+  </si>
+  <si>
+    <t>2016-01</t>
+  </si>
+  <si>
+    <t>Saeul 2</t>
+  </si>
+  <si>
+    <t>2009-08</t>
+  </si>
+  <si>
+    <t>2019-04</t>
+  </si>
+  <si>
+    <t>Shin Hanul 1</t>
+  </si>
+  <si>
+    <t>2012-07</t>
+  </si>
+  <si>
+    <t>2022-06</t>
+  </si>
+  <si>
+    <t>Shin Hanul 2</t>
+  </si>
+  <si>
+    <t>2013-06</t>
+  </si>
+  <si>
+    <t>2023-12</t>
+  </si>
+  <si>
+    <t>Shin Kori 1</t>
+  </si>
+  <si>
+    <t>2006-06</t>
+  </si>
+  <si>
+    <t>2010-08</t>
+  </si>
+  <si>
+    <t>Shin Kori 2</t>
+  </si>
+  <si>
+    <t>2007-06</t>
+  </si>
+  <si>
+    <t>2012-01</t>
+  </si>
+  <si>
+    <t>Shin Wolsong 1</t>
+  </si>
+  <si>
+    <t>2007-11</t>
+  </si>
+  <si>
+    <t>Shin Wolsong 2</t>
+  </si>
+  <si>
+    <t>2008-09</t>
+  </si>
+  <si>
+    <t>2015-02</t>
+  </si>
+  <si>
+    <t>Wolsong 2</t>
+  </si>
+  <si>
+    <t>CANDU 6</t>
+  </si>
+  <si>
+    <t>PHWR</t>
+  </si>
+  <si>
+    <t>1992-09</t>
+  </si>
+  <si>
+    <t>1997-04</t>
+  </si>
+  <si>
+    <t>Wolsong 3</t>
+  </si>
+  <si>
+    <t>1994-03</t>
+  </si>
+  <si>
+    <t>1998-03</t>
+  </si>
+  <si>
+    <t>Wolsong 4</t>
+  </si>
+  <si>
+    <t>1994-07</t>
+  </si>
+  <si>
+    <t>1999-05</t>
+  </si>
+  <si>
+    <t>Saeul 3 and 4: https://www.spglobal.com/commodity-insights/en/news-research/latest-news/electric-power/061025-south-koreas-nuclear-first-power-mix-to-be-reviewed-under-new-president</t>
+  </si>
+  <si>
+    <t>Shin Hanul 3 and 4</t>
+  </si>
+  <si>
+    <t>(same link)</t>
   </si>
 </sst>
 </file>
@@ -957,7 +1237,7 @@
     <numFmt numFmtId="167" formatCode="#,##0.0000"/>
     <numFmt numFmtId="168" formatCode="_(* #,##0.00000_);_(* \(#,##0.00000\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1076,8 +1356,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF95B46A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF212529"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1120,8 +1413,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -1189,6 +1488,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1219,7 +1527,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1305,12 +1613,26 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="8" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="15">
     <cellStyle name="Body: normal cell" xfId="7" xr:uid="{984E6381-458F-4A44-B490-4FDDB410F732}"/>
@@ -1630,9 +1952,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="67.109375" customWidth="1"/>
+    <col min="2" max="2" width="67.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1708,7 +2030,7 @@
   <dimension ref="A1:AH2837"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="31.88671875" customWidth="1"/>
+    <col min="1" max="1" width="31.85546875" customWidth="1"/>
     <col min="2" max="2" width="49" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3394,7 +3716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:34" ht="14.4">
+    <row r="31" spans="1:34">
       <c r="A31" s="7" t="s">
         <v>71</v>
       </c>
@@ -3498,7 +3820,7 @@
         <v>-2.72E-4</v>
       </c>
     </row>
-    <row r="32" spans="1:34" ht="14.4">
+    <row r="32" spans="1:34">
       <c r="A32" s="7" t="s">
         <v>72</v>
       </c>
@@ -3602,7 +3924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:34" ht="14.4">
+    <row r="33" spans="1:34">
       <c r="A33" s="7" t="s">
         <v>73</v>
       </c>
@@ -3706,7 +4028,7 @@
         <v>6.7999999999999999E-5</v>
       </c>
     </row>
-    <row r="34" spans="1:34" ht="14.4">
+    <row r="34" spans="1:34">
       <c r="A34" s="7" t="s">
         <v>74</v>
       </c>
@@ -3810,12 +4132,12 @@
         <v>-3.3E-4</v>
       </c>
     </row>
-    <row r="36" spans="1:34" ht="14.4">
+    <row r="36" spans="1:34">
       <c r="B36" s="11" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="37" spans="1:34" ht="14.4">
+    <row r="37" spans="1:34">
       <c r="A37" s="7" t="s">
         <v>76</v>
       </c>
@@ -3919,7 +4241,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="38" spans="1:34" ht="14.4">
+    <row r="38" spans="1:34">
       <c r="A38" s="7" t="s">
         <v>77</v>
       </c>
@@ -4023,7 +4345,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="39" spans="1:34" ht="14.4">
+    <row r="39" spans="1:34">
       <c r="A39" s="7" t="s">
         <v>78</v>
       </c>
@@ -4127,7 +4449,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="40" spans="1:34" ht="14.4">
+    <row r="40" spans="1:34">
       <c r="A40" s="7" t="s">
         <v>79</v>
       </c>
@@ -4231,7 +4553,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="41" spans="1:34" ht="14.4">
+    <row r="41" spans="1:34">
       <c r="A41" s="7" t="s">
         <v>80</v>
       </c>
@@ -4335,7 +4657,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="42" spans="1:34" ht="14.4">
+    <row r="42" spans="1:34">
       <c r="A42" s="7" t="s">
         <v>82</v>
       </c>
@@ -4439,7 +4761,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="43" spans="1:34" ht="14.4">
+    <row r="43" spans="1:34">
       <c r="A43" s="7" t="s">
         <v>83</v>
       </c>
@@ -4543,7 +4865,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="44" spans="1:34" ht="14.4">
+    <row r="44" spans="1:34">
       <c r="A44" s="7" t="s">
         <v>84</v>
       </c>
@@ -4647,7 +4969,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="45" spans="1:34" ht="14.4">
+    <row r="45" spans="1:34">
       <c r="A45" s="7" t="s">
         <v>85</v>
       </c>
@@ -4751,7 +5073,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="46" spans="1:34" ht="14.4">
+    <row r="46" spans="1:34">
       <c r="A46" s="7" t="s">
         <v>86</v>
       </c>
@@ -4855,7 +5177,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="47" spans="1:34" ht="14.4">
+    <row r="47" spans="1:34">
       <c r="A47" s="7" t="s">
         <v>88</v>
       </c>
@@ -4959,12 +5281,12 @@
         <v>63</v>
       </c>
     </row>
-    <row r="48" spans="1:34" ht="14.4">
+    <row r="48" spans="1:34">
       <c r="B48" s="11" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="49" spans="1:34" ht="14.4">
+    <row r="49" spans="1:34">
       <c r="A49" s="7" t="s">
         <v>90</v>
       </c>
@@ -6529,7 +6851,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="66" spans="1:34" ht="14.4">
+    <row r="66" spans="1:34">
       <c r="A66" s="7" t="s">
         <v>107</v>
       </c>
@@ -7574,7 +7896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:34" ht="14.4">
+    <row r="79" spans="1:34">
       <c r="A79" s="7" t="s">
         <v>120</v>
       </c>
@@ -7782,7 +8104,7 @@
         <v>5.0600000000000005E-4</v>
       </c>
     </row>
-    <row r="81" spans="1:34" ht="14.4">
+    <row r="81" spans="1:34">
       <c r="A81" s="7" t="s">
         <v>124</v>
       </c>
@@ -8200,40 +8522,40 @@
     </row>
     <row r="86" spans="1:34" ht="15" customHeight="1" thickBot="1"/>
     <row r="87" spans="1:34" ht="15" customHeight="1">
-      <c r="B87" s="44" t="s">
+      <c r="B87" s="49" t="s">
         <v>130</v>
       </c>
-      <c r="C87" s="45"/>
-      <c r="D87" s="45"/>
-      <c r="E87" s="45"/>
-      <c r="F87" s="45"/>
-      <c r="G87" s="45"/>
-      <c r="H87" s="45"/>
-      <c r="I87" s="45"/>
-      <c r="J87" s="45"/>
-      <c r="K87" s="45"/>
-      <c r="L87" s="45"/>
-      <c r="M87" s="45"/>
-      <c r="N87" s="45"/>
-      <c r="O87" s="45"/>
-      <c r="P87" s="45"/>
-      <c r="Q87" s="45"/>
-      <c r="R87" s="45"/>
-      <c r="S87" s="45"/>
-      <c r="T87" s="45"/>
-      <c r="U87" s="45"/>
-      <c r="V87" s="45"/>
-      <c r="W87" s="45"/>
-      <c r="X87" s="45"/>
-      <c r="Y87" s="45"/>
-      <c r="Z87" s="45"/>
-      <c r="AA87" s="45"/>
-      <c r="AB87" s="45"/>
-      <c r="AC87" s="45"/>
-      <c r="AD87" s="45"/>
-      <c r="AE87" s="45"/>
-      <c r="AF87" s="45"/>
-      <c r="AG87" s="45"/>
+      <c r="C87" s="50"/>
+      <c r="D87" s="50"/>
+      <c r="E87" s="50"/>
+      <c r="F87" s="50"/>
+      <c r="G87" s="50"/>
+      <c r="H87" s="50"/>
+      <c r="I87" s="50"/>
+      <c r="J87" s="50"/>
+      <c r="K87" s="50"/>
+      <c r="L87" s="50"/>
+      <c r="M87" s="50"/>
+      <c r="N87" s="50"/>
+      <c r="O87" s="50"/>
+      <c r="P87" s="50"/>
+      <c r="Q87" s="50"/>
+      <c r="R87" s="50"/>
+      <c r="S87" s="50"/>
+      <c r="T87" s="50"/>
+      <c r="U87" s="50"/>
+      <c r="V87" s="50"/>
+      <c r="W87" s="50"/>
+      <c r="X87" s="50"/>
+      <c r="Y87" s="50"/>
+      <c r="Z87" s="50"/>
+      <c r="AA87" s="50"/>
+      <c r="AB87" s="50"/>
+      <c r="AC87" s="50"/>
+      <c r="AD87" s="50"/>
+      <c r="AE87" s="50"/>
+      <c r="AF87" s="50"/>
+      <c r="AG87" s="50"/>
       <c r="AH87" s="22"/>
     </row>
     <row r="88" spans="1:34" ht="15" customHeight="1">
@@ -8256,7 +8578,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="92" spans="1:34" ht="14.4">
+    <row r="92" spans="1:34">
       <c r="B92" s="23" t="s">
         <v>135</v>
       </c>
@@ -8301,12 +8623,12 @@
         <v>143</v>
       </c>
     </row>
-    <row r="101" spans="2:34" ht="14.4">
+    <row r="101" spans="2:34">
       <c r="B101" s="23" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="102" spans="2:34" ht="14.4">
+    <row r="102" spans="2:34">
       <c r="B102" s="23" t="s">
         <v>145</v>
       </c>
@@ -8357,704 +8679,704 @@
       </c>
     </row>
     <row r="112" spans="2:34" ht="15" customHeight="1">
-      <c r="B112" s="43"/>
-      <c r="C112" s="43"/>
-      <c r="D112" s="43"/>
-      <c r="E112" s="43"/>
-      <c r="F112" s="43"/>
-      <c r="G112" s="43"/>
-      <c r="H112" s="43"/>
-      <c r="I112" s="43"/>
-      <c r="J112" s="43"/>
-      <c r="K112" s="43"/>
-      <c r="L112" s="43"/>
-      <c r="M112" s="43"/>
-      <c r="N112" s="43"/>
-      <c r="O112" s="43"/>
-      <c r="P112" s="43"/>
-      <c r="Q112" s="43"/>
-      <c r="R112" s="43"/>
-      <c r="S112" s="43"/>
-      <c r="T112" s="43"/>
-      <c r="U112" s="43"/>
-      <c r="V112" s="43"/>
-      <c r="W112" s="43"/>
-      <c r="X112" s="43"/>
-      <c r="Y112" s="43"/>
-      <c r="Z112" s="43"/>
-      <c r="AA112" s="43"/>
-      <c r="AB112" s="43"/>
-      <c r="AC112" s="43"/>
-      <c r="AD112" s="43"/>
-      <c r="AE112" s="43"/>
-      <c r="AF112" s="43"/>
-      <c r="AG112" s="43"/>
-      <c r="AH112" s="43"/>
+      <c r="B112" s="48"/>
+      <c r="C112" s="48"/>
+      <c r="D112" s="48"/>
+      <c r="E112" s="48"/>
+      <c r="F112" s="48"/>
+      <c r="G112" s="48"/>
+      <c r="H112" s="48"/>
+      <c r="I112" s="48"/>
+      <c r="J112" s="48"/>
+      <c r="K112" s="48"/>
+      <c r="L112" s="48"/>
+      <c r="M112" s="48"/>
+      <c r="N112" s="48"/>
+      <c r="O112" s="48"/>
+      <c r="P112" s="48"/>
+      <c r="Q112" s="48"/>
+      <c r="R112" s="48"/>
+      <c r="S112" s="48"/>
+      <c r="T112" s="48"/>
+      <c r="U112" s="48"/>
+      <c r="V112" s="48"/>
+      <c r="W112" s="48"/>
+      <c r="X112" s="48"/>
+      <c r="Y112" s="48"/>
+      <c r="Z112" s="48"/>
+      <c r="AA112" s="48"/>
+      <c r="AB112" s="48"/>
+      <c r="AC112" s="48"/>
+      <c r="AD112" s="48"/>
+      <c r="AE112" s="48"/>
+      <c r="AF112" s="48"/>
+      <c r="AG112" s="48"/>
+      <c r="AH112" s="48"/>
     </row>
     <row r="308" spans="2:34" ht="15" customHeight="1">
-      <c r="B308" s="43"/>
-      <c r="C308" s="43"/>
-      <c r="D308" s="43"/>
-      <c r="E308" s="43"/>
-      <c r="F308" s="43"/>
-      <c r="G308" s="43"/>
-      <c r="H308" s="43"/>
-      <c r="I308" s="43"/>
-      <c r="J308" s="43"/>
-      <c r="K308" s="43"/>
-      <c r="L308" s="43"/>
-      <c r="M308" s="43"/>
-      <c r="N308" s="43"/>
-      <c r="O308" s="43"/>
-      <c r="P308" s="43"/>
-      <c r="Q308" s="43"/>
-      <c r="R308" s="43"/>
-      <c r="S308" s="43"/>
-      <c r="T308" s="43"/>
-      <c r="U308" s="43"/>
-      <c r="V308" s="43"/>
-      <c r="W308" s="43"/>
-      <c r="X308" s="43"/>
-      <c r="Y308" s="43"/>
-      <c r="Z308" s="43"/>
-      <c r="AA308" s="43"/>
-      <c r="AB308" s="43"/>
-      <c r="AC308" s="43"/>
-      <c r="AD308" s="43"/>
-      <c r="AE308" s="43"/>
-      <c r="AF308" s="43"/>
-      <c r="AG308" s="43"/>
-      <c r="AH308" s="43"/>
+      <c r="B308" s="48"/>
+      <c r="C308" s="48"/>
+      <c r="D308" s="48"/>
+      <c r="E308" s="48"/>
+      <c r="F308" s="48"/>
+      <c r="G308" s="48"/>
+      <c r="H308" s="48"/>
+      <c r="I308" s="48"/>
+      <c r="J308" s="48"/>
+      <c r="K308" s="48"/>
+      <c r="L308" s="48"/>
+      <c r="M308" s="48"/>
+      <c r="N308" s="48"/>
+      <c r="O308" s="48"/>
+      <c r="P308" s="48"/>
+      <c r="Q308" s="48"/>
+      <c r="R308" s="48"/>
+      <c r="S308" s="48"/>
+      <c r="T308" s="48"/>
+      <c r="U308" s="48"/>
+      <c r="V308" s="48"/>
+      <c r="W308" s="48"/>
+      <c r="X308" s="48"/>
+      <c r="Y308" s="48"/>
+      <c r="Z308" s="48"/>
+      <c r="AA308" s="48"/>
+      <c r="AB308" s="48"/>
+      <c r="AC308" s="48"/>
+      <c r="AD308" s="48"/>
+      <c r="AE308" s="48"/>
+      <c r="AF308" s="48"/>
+      <c r="AG308" s="48"/>
+      <c r="AH308" s="48"/>
     </row>
     <row r="511" spans="2:34" ht="15" customHeight="1">
-      <c r="B511" s="43"/>
-      <c r="C511" s="43"/>
-      <c r="D511" s="43"/>
-      <c r="E511" s="43"/>
-      <c r="F511" s="43"/>
-      <c r="G511" s="43"/>
-      <c r="H511" s="43"/>
-      <c r="I511" s="43"/>
-      <c r="J511" s="43"/>
-      <c r="K511" s="43"/>
-      <c r="L511" s="43"/>
-      <c r="M511" s="43"/>
-      <c r="N511" s="43"/>
-      <c r="O511" s="43"/>
-      <c r="P511" s="43"/>
-      <c r="Q511" s="43"/>
-      <c r="R511" s="43"/>
-      <c r="S511" s="43"/>
-      <c r="T511" s="43"/>
-      <c r="U511" s="43"/>
-      <c r="V511" s="43"/>
-      <c r="W511" s="43"/>
-      <c r="X511" s="43"/>
-      <c r="Y511" s="43"/>
-      <c r="Z511" s="43"/>
-      <c r="AA511" s="43"/>
-      <c r="AB511" s="43"/>
-      <c r="AC511" s="43"/>
-      <c r="AD511" s="43"/>
-      <c r="AE511" s="43"/>
-      <c r="AF511" s="43"/>
-      <c r="AG511" s="43"/>
-      <c r="AH511" s="43"/>
+      <c r="B511" s="48"/>
+      <c r="C511" s="48"/>
+      <c r="D511" s="48"/>
+      <c r="E511" s="48"/>
+      <c r="F511" s="48"/>
+      <c r="G511" s="48"/>
+      <c r="H511" s="48"/>
+      <c r="I511" s="48"/>
+      <c r="J511" s="48"/>
+      <c r="K511" s="48"/>
+      <c r="L511" s="48"/>
+      <c r="M511" s="48"/>
+      <c r="N511" s="48"/>
+      <c r="O511" s="48"/>
+      <c r="P511" s="48"/>
+      <c r="Q511" s="48"/>
+      <c r="R511" s="48"/>
+      <c r="S511" s="48"/>
+      <c r="T511" s="48"/>
+      <c r="U511" s="48"/>
+      <c r="V511" s="48"/>
+      <c r="W511" s="48"/>
+      <c r="X511" s="48"/>
+      <c r="Y511" s="48"/>
+      <c r="Z511" s="48"/>
+      <c r="AA511" s="48"/>
+      <c r="AB511" s="48"/>
+      <c r="AC511" s="48"/>
+      <c r="AD511" s="48"/>
+      <c r="AE511" s="48"/>
+      <c r="AF511" s="48"/>
+      <c r="AG511" s="48"/>
+      <c r="AH511" s="48"/>
     </row>
     <row r="712" spans="2:34" ht="15" customHeight="1">
-      <c r="B712" s="43"/>
-      <c r="C712" s="43"/>
-      <c r="D712" s="43"/>
-      <c r="E712" s="43"/>
-      <c r="F712" s="43"/>
-      <c r="G712" s="43"/>
-      <c r="H712" s="43"/>
-      <c r="I712" s="43"/>
-      <c r="J712" s="43"/>
-      <c r="K712" s="43"/>
-      <c r="L712" s="43"/>
-      <c r="M712" s="43"/>
-      <c r="N712" s="43"/>
-      <c r="O712" s="43"/>
-      <c r="P712" s="43"/>
-      <c r="Q712" s="43"/>
-      <c r="R712" s="43"/>
-      <c r="S712" s="43"/>
-      <c r="T712" s="43"/>
-      <c r="U712" s="43"/>
-      <c r="V712" s="43"/>
-      <c r="W712" s="43"/>
-      <c r="X712" s="43"/>
-      <c r="Y712" s="43"/>
-      <c r="Z712" s="43"/>
-      <c r="AA712" s="43"/>
-      <c r="AB712" s="43"/>
-      <c r="AC712" s="43"/>
-      <c r="AD712" s="43"/>
-      <c r="AE712" s="43"/>
-      <c r="AF712" s="43"/>
-      <c r="AG712" s="43"/>
-      <c r="AH712" s="43"/>
+      <c r="B712" s="48"/>
+      <c r="C712" s="48"/>
+      <c r="D712" s="48"/>
+      <c r="E712" s="48"/>
+      <c r="F712" s="48"/>
+      <c r="G712" s="48"/>
+      <c r="H712" s="48"/>
+      <c r="I712" s="48"/>
+      <c r="J712" s="48"/>
+      <c r="K712" s="48"/>
+      <c r="L712" s="48"/>
+      <c r="M712" s="48"/>
+      <c r="N712" s="48"/>
+      <c r="O712" s="48"/>
+      <c r="P712" s="48"/>
+      <c r="Q712" s="48"/>
+      <c r="R712" s="48"/>
+      <c r="S712" s="48"/>
+      <c r="T712" s="48"/>
+      <c r="U712" s="48"/>
+      <c r="V712" s="48"/>
+      <c r="W712" s="48"/>
+      <c r="X712" s="48"/>
+      <c r="Y712" s="48"/>
+      <c r="Z712" s="48"/>
+      <c r="AA712" s="48"/>
+      <c r="AB712" s="48"/>
+      <c r="AC712" s="48"/>
+      <c r="AD712" s="48"/>
+      <c r="AE712" s="48"/>
+      <c r="AF712" s="48"/>
+      <c r="AG712" s="48"/>
+      <c r="AH712" s="48"/>
     </row>
     <row r="887" spans="2:34" ht="15" customHeight="1">
-      <c r="B887" s="43"/>
-      <c r="C887" s="43"/>
-      <c r="D887" s="43"/>
-      <c r="E887" s="43"/>
-      <c r="F887" s="43"/>
-      <c r="G887" s="43"/>
-      <c r="H887" s="43"/>
-      <c r="I887" s="43"/>
-      <c r="J887" s="43"/>
-      <c r="K887" s="43"/>
-      <c r="L887" s="43"/>
-      <c r="M887" s="43"/>
-      <c r="N887" s="43"/>
-      <c r="O887" s="43"/>
-      <c r="P887" s="43"/>
-      <c r="Q887" s="43"/>
-      <c r="R887" s="43"/>
-      <c r="S887" s="43"/>
-      <c r="T887" s="43"/>
-      <c r="U887" s="43"/>
-      <c r="V887" s="43"/>
-      <c r="W887" s="43"/>
-      <c r="X887" s="43"/>
-      <c r="Y887" s="43"/>
-      <c r="Z887" s="43"/>
-      <c r="AA887" s="43"/>
-      <c r="AB887" s="43"/>
-      <c r="AC887" s="43"/>
-      <c r="AD887" s="43"/>
-      <c r="AE887" s="43"/>
-      <c r="AF887" s="43"/>
-      <c r="AG887" s="43"/>
-      <c r="AH887" s="43"/>
+      <c r="B887" s="48"/>
+      <c r="C887" s="48"/>
+      <c r="D887" s="48"/>
+      <c r="E887" s="48"/>
+      <c r="F887" s="48"/>
+      <c r="G887" s="48"/>
+      <c r="H887" s="48"/>
+      <c r="I887" s="48"/>
+      <c r="J887" s="48"/>
+      <c r="K887" s="48"/>
+      <c r="L887" s="48"/>
+      <c r="M887" s="48"/>
+      <c r="N887" s="48"/>
+      <c r="O887" s="48"/>
+      <c r="P887" s="48"/>
+      <c r="Q887" s="48"/>
+      <c r="R887" s="48"/>
+      <c r="S887" s="48"/>
+      <c r="T887" s="48"/>
+      <c r="U887" s="48"/>
+      <c r="V887" s="48"/>
+      <c r="W887" s="48"/>
+      <c r="X887" s="48"/>
+      <c r="Y887" s="48"/>
+      <c r="Z887" s="48"/>
+      <c r="AA887" s="48"/>
+      <c r="AB887" s="48"/>
+      <c r="AC887" s="48"/>
+      <c r="AD887" s="48"/>
+      <c r="AE887" s="48"/>
+      <c r="AF887" s="48"/>
+      <c r="AG887" s="48"/>
+      <c r="AH887" s="48"/>
     </row>
     <row r="1100" spans="2:34" ht="15" customHeight="1">
-      <c r="B1100" s="43"/>
-      <c r="C1100" s="43"/>
-      <c r="D1100" s="43"/>
-      <c r="E1100" s="43"/>
-      <c r="F1100" s="43"/>
-      <c r="G1100" s="43"/>
-      <c r="H1100" s="43"/>
-      <c r="I1100" s="43"/>
-      <c r="J1100" s="43"/>
-      <c r="K1100" s="43"/>
-      <c r="L1100" s="43"/>
-      <c r="M1100" s="43"/>
-      <c r="N1100" s="43"/>
-      <c r="O1100" s="43"/>
-      <c r="P1100" s="43"/>
-      <c r="Q1100" s="43"/>
-      <c r="R1100" s="43"/>
-      <c r="S1100" s="43"/>
-      <c r="T1100" s="43"/>
-      <c r="U1100" s="43"/>
-      <c r="V1100" s="43"/>
-      <c r="W1100" s="43"/>
-      <c r="X1100" s="43"/>
-      <c r="Y1100" s="43"/>
-      <c r="Z1100" s="43"/>
-      <c r="AA1100" s="43"/>
-      <c r="AB1100" s="43"/>
-      <c r="AC1100" s="43"/>
-      <c r="AD1100" s="43"/>
-      <c r="AE1100" s="43"/>
-      <c r="AF1100" s="43"/>
-      <c r="AG1100" s="43"/>
-      <c r="AH1100" s="43"/>
+      <c r="B1100" s="48"/>
+      <c r="C1100" s="48"/>
+      <c r="D1100" s="48"/>
+      <c r="E1100" s="48"/>
+      <c r="F1100" s="48"/>
+      <c r="G1100" s="48"/>
+      <c r="H1100" s="48"/>
+      <c r="I1100" s="48"/>
+      <c r="J1100" s="48"/>
+      <c r="K1100" s="48"/>
+      <c r="L1100" s="48"/>
+      <c r="M1100" s="48"/>
+      <c r="N1100" s="48"/>
+      <c r="O1100" s="48"/>
+      <c r="P1100" s="48"/>
+      <c r="Q1100" s="48"/>
+      <c r="R1100" s="48"/>
+      <c r="S1100" s="48"/>
+      <c r="T1100" s="48"/>
+      <c r="U1100" s="48"/>
+      <c r="V1100" s="48"/>
+      <c r="W1100" s="48"/>
+      <c r="X1100" s="48"/>
+      <c r="Y1100" s="48"/>
+      <c r="Z1100" s="48"/>
+      <c r="AA1100" s="48"/>
+      <c r="AB1100" s="48"/>
+      <c r="AC1100" s="48"/>
+      <c r="AD1100" s="48"/>
+      <c r="AE1100" s="48"/>
+      <c r="AF1100" s="48"/>
+      <c r="AG1100" s="48"/>
+      <c r="AH1100" s="48"/>
     </row>
     <row r="1227" spans="2:34" ht="15" customHeight="1">
-      <c r="B1227" s="43"/>
-      <c r="C1227" s="43"/>
-      <c r="D1227" s="43"/>
-      <c r="E1227" s="43"/>
-      <c r="F1227" s="43"/>
-      <c r="G1227" s="43"/>
-      <c r="H1227" s="43"/>
-      <c r="I1227" s="43"/>
-      <c r="J1227" s="43"/>
-      <c r="K1227" s="43"/>
-      <c r="L1227" s="43"/>
-      <c r="M1227" s="43"/>
-      <c r="N1227" s="43"/>
-      <c r="O1227" s="43"/>
-      <c r="P1227" s="43"/>
-      <c r="Q1227" s="43"/>
-      <c r="R1227" s="43"/>
-      <c r="S1227" s="43"/>
-      <c r="T1227" s="43"/>
-      <c r="U1227" s="43"/>
-      <c r="V1227" s="43"/>
-      <c r="W1227" s="43"/>
-      <c r="X1227" s="43"/>
-      <c r="Y1227" s="43"/>
-      <c r="Z1227" s="43"/>
-      <c r="AA1227" s="43"/>
-      <c r="AB1227" s="43"/>
-      <c r="AC1227" s="43"/>
-      <c r="AD1227" s="43"/>
-      <c r="AE1227" s="43"/>
-      <c r="AF1227" s="43"/>
-      <c r="AG1227" s="43"/>
-      <c r="AH1227" s="43"/>
+      <c r="B1227" s="48"/>
+      <c r="C1227" s="48"/>
+      <c r="D1227" s="48"/>
+      <c r="E1227" s="48"/>
+      <c r="F1227" s="48"/>
+      <c r="G1227" s="48"/>
+      <c r="H1227" s="48"/>
+      <c r="I1227" s="48"/>
+      <c r="J1227" s="48"/>
+      <c r="K1227" s="48"/>
+      <c r="L1227" s="48"/>
+      <c r="M1227" s="48"/>
+      <c r="N1227" s="48"/>
+      <c r="O1227" s="48"/>
+      <c r="P1227" s="48"/>
+      <c r="Q1227" s="48"/>
+      <c r="R1227" s="48"/>
+      <c r="S1227" s="48"/>
+      <c r="T1227" s="48"/>
+      <c r="U1227" s="48"/>
+      <c r="V1227" s="48"/>
+      <c r="W1227" s="48"/>
+      <c r="X1227" s="48"/>
+      <c r="Y1227" s="48"/>
+      <c r="Z1227" s="48"/>
+      <c r="AA1227" s="48"/>
+      <c r="AB1227" s="48"/>
+      <c r="AC1227" s="48"/>
+      <c r="AD1227" s="48"/>
+      <c r="AE1227" s="48"/>
+      <c r="AF1227" s="48"/>
+      <c r="AG1227" s="48"/>
+      <c r="AH1227" s="48"/>
     </row>
     <row r="1390" spans="2:34" ht="15" customHeight="1">
-      <c r="B1390" s="43"/>
-      <c r="C1390" s="43"/>
-      <c r="D1390" s="43"/>
-      <c r="E1390" s="43"/>
-      <c r="F1390" s="43"/>
-      <c r="G1390" s="43"/>
-      <c r="H1390" s="43"/>
-      <c r="I1390" s="43"/>
-      <c r="J1390" s="43"/>
-      <c r="K1390" s="43"/>
-      <c r="L1390" s="43"/>
-      <c r="M1390" s="43"/>
-      <c r="N1390" s="43"/>
-      <c r="O1390" s="43"/>
-      <c r="P1390" s="43"/>
-      <c r="Q1390" s="43"/>
-      <c r="R1390" s="43"/>
-      <c r="S1390" s="43"/>
-      <c r="T1390" s="43"/>
-      <c r="U1390" s="43"/>
-      <c r="V1390" s="43"/>
-      <c r="W1390" s="43"/>
-      <c r="X1390" s="43"/>
-      <c r="Y1390" s="43"/>
-      <c r="Z1390" s="43"/>
-      <c r="AA1390" s="43"/>
-      <c r="AB1390" s="43"/>
-      <c r="AC1390" s="43"/>
-      <c r="AD1390" s="43"/>
-      <c r="AE1390" s="43"/>
-      <c r="AF1390" s="43"/>
-      <c r="AG1390" s="43"/>
-      <c r="AH1390" s="43"/>
+      <c r="B1390" s="48"/>
+      <c r="C1390" s="48"/>
+      <c r="D1390" s="48"/>
+      <c r="E1390" s="48"/>
+      <c r="F1390" s="48"/>
+      <c r="G1390" s="48"/>
+      <c r="H1390" s="48"/>
+      <c r="I1390" s="48"/>
+      <c r="J1390" s="48"/>
+      <c r="K1390" s="48"/>
+      <c r="L1390" s="48"/>
+      <c r="M1390" s="48"/>
+      <c r="N1390" s="48"/>
+      <c r="O1390" s="48"/>
+      <c r="P1390" s="48"/>
+      <c r="Q1390" s="48"/>
+      <c r="R1390" s="48"/>
+      <c r="S1390" s="48"/>
+      <c r="T1390" s="48"/>
+      <c r="U1390" s="48"/>
+      <c r="V1390" s="48"/>
+      <c r="W1390" s="48"/>
+      <c r="X1390" s="48"/>
+      <c r="Y1390" s="48"/>
+      <c r="Z1390" s="48"/>
+      <c r="AA1390" s="48"/>
+      <c r="AB1390" s="48"/>
+      <c r="AC1390" s="48"/>
+      <c r="AD1390" s="48"/>
+      <c r="AE1390" s="48"/>
+      <c r="AF1390" s="48"/>
+      <c r="AG1390" s="48"/>
+      <c r="AH1390" s="48"/>
     </row>
     <row r="1502" spans="2:34" ht="15" customHeight="1">
-      <c r="B1502" s="43"/>
-      <c r="C1502" s="43"/>
-      <c r="D1502" s="43"/>
-      <c r="E1502" s="43"/>
-      <c r="F1502" s="43"/>
-      <c r="G1502" s="43"/>
-      <c r="H1502" s="43"/>
-      <c r="I1502" s="43"/>
-      <c r="J1502" s="43"/>
-      <c r="K1502" s="43"/>
-      <c r="L1502" s="43"/>
-      <c r="M1502" s="43"/>
-      <c r="N1502" s="43"/>
-      <c r="O1502" s="43"/>
-      <c r="P1502" s="43"/>
-      <c r="Q1502" s="43"/>
-      <c r="R1502" s="43"/>
-      <c r="S1502" s="43"/>
-      <c r="T1502" s="43"/>
-      <c r="U1502" s="43"/>
-      <c r="V1502" s="43"/>
-      <c r="W1502" s="43"/>
-      <c r="X1502" s="43"/>
-      <c r="Y1502" s="43"/>
-      <c r="Z1502" s="43"/>
-      <c r="AA1502" s="43"/>
-      <c r="AB1502" s="43"/>
-      <c r="AC1502" s="43"/>
-      <c r="AD1502" s="43"/>
-      <c r="AE1502" s="43"/>
-      <c r="AF1502" s="43"/>
-      <c r="AG1502" s="43"/>
-      <c r="AH1502" s="43"/>
+      <c r="B1502" s="48"/>
+      <c r="C1502" s="48"/>
+      <c r="D1502" s="48"/>
+      <c r="E1502" s="48"/>
+      <c r="F1502" s="48"/>
+      <c r="G1502" s="48"/>
+      <c r="H1502" s="48"/>
+      <c r="I1502" s="48"/>
+      <c r="J1502" s="48"/>
+      <c r="K1502" s="48"/>
+      <c r="L1502" s="48"/>
+      <c r="M1502" s="48"/>
+      <c r="N1502" s="48"/>
+      <c r="O1502" s="48"/>
+      <c r="P1502" s="48"/>
+      <c r="Q1502" s="48"/>
+      <c r="R1502" s="48"/>
+      <c r="S1502" s="48"/>
+      <c r="T1502" s="48"/>
+      <c r="U1502" s="48"/>
+      <c r="V1502" s="48"/>
+      <c r="W1502" s="48"/>
+      <c r="X1502" s="48"/>
+      <c r="Y1502" s="48"/>
+      <c r="Z1502" s="48"/>
+      <c r="AA1502" s="48"/>
+      <c r="AB1502" s="48"/>
+      <c r="AC1502" s="48"/>
+      <c r="AD1502" s="48"/>
+      <c r="AE1502" s="48"/>
+      <c r="AF1502" s="48"/>
+      <c r="AG1502" s="48"/>
+      <c r="AH1502" s="48"/>
     </row>
     <row r="1604" spans="2:34" ht="15" customHeight="1">
-      <c r="B1604" s="43"/>
-      <c r="C1604" s="43"/>
-      <c r="D1604" s="43"/>
-      <c r="E1604" s="43"/>
-      <c r="F1604" s="43"/>
-      <c r="G1604" s="43"/>
-      <c r="H1604" s="43"/>
-      <c r="I1604" s="43"/>
-      <c r="J1604" s="43"/>
-      <c r="K1604" s="43"/>
-      <c r="L1604" s="43"/>
-      <c r="M1604" s="43"/>
-      <c r="N1604" s="43"/>
-      <c r="O1604" s="43"/>
-      <c r="P1604" s="43"/>
-      <c r="Q1604" s="43"/>
-      <c r="R1604" s="43"/>
-      <c r="S1604" s="43"/>
-      <c r="T1604" s="43"/>
-      <c r="U1604" s="43"/>
-      <c r="V1604" s="43"/>
-      <c r="W1604" s="43"/>
-      <c r="X1604" s="43"/>
-      <c r="Y1604" s="43"/>
-      <c r="Z1604" s="43"/>
-      <c r="AA1604" s="43"/>
-      <c r="AB1604" s="43"/>
-      <c r="AC1604" s="43"/>
-      <c r="AD1604" s="43"/>
-      <c r="AE1604" s="43"/>
-      <c r="AF1604" s="43"/>
-      <c r="AG1604" s="43"/>
-      <c r="AH1604" s="43"/>
+      <c r="B1604" s="48"/>
+      <c r="C1604" s="48"/>
+      <c r="D1604" s="48"/>
+      <c r="E1604" s="48"/>
+      <c r="F1604" s="48"/>
+      <c r="G1604" s="48"/>
+      <c r="H1604" s="48"/>
+      <c r="I1604" s="48"/>
+      <c r="J1604" s="48"/>
+      <c r="K1604" s="48"/>
+      <c r="L1604" s="48"/>
+      <c r="M1604" s="48"/>
+      <c r="N1604" s="48"/>
+      <c r="O1604" s="48"/>
+      <c r="P1604" s="48"/>
+      <c r="Q1604" s="48"/>
+      <c r="R1604" s="48"/>
+      <c r="S1604" s="48"/>
+      <c r="T1604" s="48"/>
+      <c r="U1604" s="48"/>
+      <c r="V1604" s="48"/>
+      <c r="W1604" s="48"/>
+      <c r="X1604" s="48"/>
+      <c r="Y1604" s="48"/>
+      <c r="Z1604" s="48"/>
+      <c r="AA1604" s="48"/>
+      <c r="AB1604" s="48"/>
+      <c r="AC1604" s="48"/>
+      <c r="AD1604" s="48"/>
+      <c r="AE1604" s="48"/>
+      <c r="AF1604" s="48"/>
+      <c r="AG1604" s="48"/>
+      <c r="AH1604" s="48"/>
     </row>
     <row r="1698" spans="2:34" ht="15" customHeight="1">
-      <c r="B1698" s="43"/>
-      <c r="C1698" s="43"/>
-      <c r="D1698" s="43"/>
-      <c r="E1698" s="43"/>
-      <c r="F1698" s="43"/>
-      <c r="G1698" s="43"/>
-      <c r="H1698" s="43"/>
-      <c r="I1698" s="43"/>
-      <c r="J1698" s="43"/>
-      <c r="K1698" s="43"/>
-      <c r="L1698" s="43"/>
-      <c r="M1698" s="43"/>
-      <c r="N1698" s="43"/>
-      <c r="O1698" s="43"/>
-      <c r="P1698" s="43"/>
-      <c r="Q1698" s="43"/>
-      <c r="R1698" s="43"/>
-      <c r="S1698" s="43"/>
-      <c r="T1698" s="43"/>
-      <c r="U1698" s="43"/>
-      <c r="V1698" s="43"/>
-      <c r="W1698" s="43"/>
-      <c r="X1698" s="43"/>
-      <c r="Y1698" s="43"/>
-      <c r="Z1698" s="43"/>
-      <c r="AA1698" s="43"/>
-      <c r="AB1698" s="43"/>
-      <c r="AC1698" s="43"/>
-      <c r="AD1698" s="43"/>
-      <c r="AE1698" s="43"/>
-      <c r="AF1698" s="43"/>
-      <c r="AG1698" s="43"/>
-      <c r="AH1698" s="43"/>
+      <c r="B1698" s="48"/>
+      <c r="C1698" s="48"/>
+      <c r="D1698" s="48"/>
+      <c r="E1698" s="48"/>
+      <c r="F1698" s="48"/>
+      <c r="G1698" s="48"/>
+      <c r="H1698" s="48"/>
+      <c r="I1698" s="48"/>
+      <c r="J1698" s="48"/>
+      <c r="K1698" s="48"/>
+      <c r="L1698" s="48"/>
+      <c r="M1698" s="48"/>
+      <c r="N1698" s="48"/>
+      <c r="O1698" s="48"/>
+      <c r="P1698" s="48"/>
+      <c r="Q1698" s="48"/>
+      <c r="R1698" s="48"/>
+      <c r="S1698" s="48"/>
+      <c r="T1698" s="48"/>
+      <c r="U1698" s="48"/>
+      <c r="V1698" s="48"/>
+      <c r="W1698" s="48"/>
+      <c r="X1698" s="48"/>
+      <c r="Y1698" s="48"/>
+      <c r="Z1698" s="48"/>
+      <c r="AA1698" s="48"/>
+      <c r="AB1698" s="48"/>
+      <c r="AC1698" s="48"/>
+      <c r="AD1698" s="48"/>
+      <c r="AE1698" s="48"/>
+      <c r="AF1698" s="48"/>
+      <c r="AG1698" s="48"/>
+      <c r="AH1698" s="48"/>
     </row>
     <row r="1945" spans="2:34" ht="15" customHeight="1">
-      <c r="B1945" s="43"/>
-      <c r="C1945" s="43"/>
-      <c r="D1945" s="43"/>
-      <c r="E1945" s="43"/>
-      <c r="F1945" s="43"/>
-      <c r="G1945" s="43"/>
-      <c r="H1945" s="43"/>
-      <c r="I1945" s="43"/>
-      <c r="J1945" s="43"/>
-      <c r="K1945" s="43"/>
-      <c r="L1945" s="43"/>
-      <c r="M1945" s="43"/>
-      <c r="N1945" s="43"/>
-      <c r="O1945" s="43"/>
-      <c r="P1945" s="43"/>
-      <c r="Q1945" s="43"/>
-      <c r="R1945" s="43"/>
-      <c r="S1945" s="43"/>
-      <c r="T1945" s="43"/>
-      <c r="U1945" s="43"/>
-      <c r="V1945" s="43"/>
-      <c r="W1945" s="43"/>
-      <c r="X1945" s="43"/>
-      <c r="Y1945" s="43"/>
-      <c r="Z1945" s="43"/>
-      <c r="AA1945" s="43"/>
-      <c r="AB1945" s="43"/>
-      <c r="AC1945" s="43"/>
-      <c r="AD1945" s="43"/>
-      <c r="AE1945" s="43"/>
-      <c r="AF1945" s="43"/>
-      <c r="AG1945" s="43"/>
-      <c r="AH1945" s="43"/>
+      <c r="B1945" s="48"/>
+      <c r="C1945" s="48"/>
+      <c r="D1945" s="48"/>
+      <c r="E1945" s="48"/>
+      <c r="F1945" s="48"/>
+      <c r="G1945" s="48"/>
+      <c r="H1945" s="48"/>
+      <c r="I1945" s="48"/>
+      <c r="J1945" s="48"/>
+      <c r="K1945" s="48"/>
+      <c r="L1945" s="48"/>
+      <c r="M1945" s="48"/>
+      <c r="N1945" s="48"/>
+      <c r="O1945" s="48"/>
+      <c r="P1945" s="48"/>
+      <c r="Q1945" s="48"/>
+      <c r="R1945" s="48"/>
+      <c r="S1945" s="48"/>
+      <c r="T1945" s="48"/>
+      <c r="U1945" s="48"/>
+      <c r="V1945" s="48"/>
+      <c r="W1945" s="48"/>
+      <c r="X1945" s="48"/>
+      <c r="Y1945" s="48"/>
+      <c r="Z1945" s="48"/>
+      <c r="AA1945" s="48"/>
+      <c r="AB1945" s="48"/>
+      <c r="AC1945" s="48"/>
+      <c r="AD1945" s="48"/>
+      <c r="AE1945" s="48"/>
+      <c r="AF1945" s="48"/>
+      <c r="AG1945" s="48"/>
+      <c r="AH1945" s="48"/>
     </row>
     <row r="2031" spans="2:34" ht="15" customHeight="1">
-      <c r="B2031" s="43"/>
-      <c r="C2031" s="43"/>
-      <c r="D2031" s="43"/>
-      <c r="E2031" s="43"/>
-      <c r="F2031" s="43"/>
-      <c r="G2031" s="43"/>
-      <c r="H2031" s="43"/>
-      <c r="I2031" s="43"/>
-      <c r="J2031" s="43"/>
-      <c r="K2031" s="43"/>
-      <c r="L2031" s="43"/>
-      <c r="M2031" s="43"/>
-      <c r="N2031" s="43"/>
-      <c r="O2031" s="43"/>
-      <c r="P2031" s="43"/>
-      <c r="Q2031" s="43"/>
-      <c r="R2031" s="43"/>
-      <c r="S2031" s="43"/>
-      <c r="T2031" s="43"/>
-      <c r="U2031" s="43"/>
-      <c r="V2031" s="43"/>
-      <c r="W2031" s="43"/>
-      <c r="X2031" s="43"/>
-      <c r="Y2031" s="43"/>
-      <c r="Z2031" s="43"/>
-      <c r="AA2031" s="43"/>
-      <c r="AB2031" s="43"/>
-      <c r="AC2031" s="43"/>
-      <c r="AD2031" s="43"/>
-      <c r="AE2031" s="43"/>
-      <c r="AF2031" s="43"/>
-      <c r="AG2031" s="43"/>
-      <c r="AH2031" s="43"/>
+      <c r="B2031" s="48"/>
+      <c r="C2031" s="48"/>
+      <c r="D2031" s="48"/>
+      <c r="E2031" s="48"/>
+      <c r="F2031" s="48"/>
+      <c r="G2031" s="48"/>
+      <c r="H2031" s="48"/>
+      <c r="I2031" s="48"/>
+      <c r="J2031" s="48"/>
+      <c r="K2031" s="48"/>
+      <c r="L2031" s="48"/>
+      <c r="M2031" s="48"/>
+      <c r="N2031" s="48"/>
+      <c r="O2031" s="48"/>
+      <c r="P2031" s="48"/>
+      <c r="Q2031" s="48"/>
+      <c r="R2031" s="48"/>
+      <c r="S2031" s="48"/>
+      <c r="T2031" s="48"/>
+      <c r="U2031" s="48"/>
+      <c r="V2031" s="48"/>
+      <c r="W2031" s="48"/>
+      <c r="X2031" s="48"/>
+      <c r="Y2031" s="48"/>
+      <c r="Z2031" s="48"/>
+      <c r="AA2031" s="48"/>
+      <c r="AB2031" s="48"/>
+      <c r="AC2031" s="48"/>
+      <c r="AD2031" s="48"/>
+      <c r="AE2031" s="48"/>
+      <c r="AF2031" s="48"/>
+      <c r="AG2031" s="48"/>
+      <c r="AH2031" s="48"/>
     </row>
     <row r="2153" spans="2:34" ht="15" customHeight="1">
-      <c r="B2153" s="43"/>
-      <c r="C2153" s="43"/>
-      <c r="D2153" s="43"/>
-      <c r="E2153" s="43"/>
-      <c r="F2153" s="43"/>
-      <c r="G2153" s="43"/>
-      <c r="H2153" s="43"/>
-      <c r="I2153" s="43"/>
-      <c r="J2153" s="43"/>
-      <c r="K2153" s="43"/>
-      <c r="L2153" s="43"/>
-      <c r="M2153" s="43"/>
-      <c r="N2153" s="43"/>
-      <c r="O2153" s="43"/>
-      <c r="P2153" s="43"/>
-      <c r="Q2153" s="43"/>
-      <c r="R2153" s="43"/>
-      <c r="S2153" s="43"/>
-      <c r="T2153" s="43"/>
-      <c r="U2153" s="43"/>
-      <c r="V2153" s="43"/>
-      <c r="W2153" s="43"/>
-      <c r="X2153" s="43"/>
-      <c r="Y2153" s="43"/>
-      <c r="Z2153" s="43"/>
-      <c r="AA2153" s="43"/>
-      <c r="AB2153" s="43"/>
-      <c r="AC2153" s="43"/>
-      <c r="AD2153" s="43"/>
-      <c r="AE2153" s="43"/>
-      <c r="AF2153" s="43"/>
-      <c r="AG2153" s="43"/>
-      <c r="AH2153" s="43"/>
+      <c r="B2153" s="48"/>
+      <c r="C2153" s="48"/>
+      <c r="D2153" s="48"/>
+      <c r="E2153" s="48"/>
+      <c r="F2153" s="48"/>
+      <c r="G2153" s="48"/>
+      <c r="H2153" s="48"/>
+      <c r="I2153" s="48"/>
+      <c r="J2153" s="48"/>
+      <c r="K2153" s="48"/>
+      <c r="L2153" s="48"/>
+      <c r="M2153" s="48"/>
+      <c r="N2153" s="48"/>
+      <c r="O2153" s="48"/>
+      <c r="P2153" s="48"/>
+      <c r="Q2153" s="48"/>
+      <c r="R2153" s="48"/>
+      <c r="S2153" s="48"/>
+      <c r="T2153" s="48"/>
+      <c r="U2153" s="48"/>
+      <c r="V2153" s="48"/>
+      <c r="W2153" s="48"/>
+      <c r="X2153" s="48"/>
+      <c r="Y2153" s="48"/>
+      <c r="Z2153" s="48"/>
+      <c r="AA2153" s="48"/>
+      <c r="AB2153" s="48"/>
+      <c r="AC2153" s="48"/>
+      <c r="AD2153" s="48"/>
+      <c r="AE2153" s="48"/>
+      <c r="AF2153" s="48"/>
+      <c r="AG2153" s="48"/>
+      <c r="AH2153" s="48"/>
     </row>
     <row r="2317" spans="2:34" ht="15" customHeight="1">
-      <c r="B2317" s="43"/>
-      <c r="C2317" s="43"/>
-      <c r="D2317" s="43"/>
-      <c r="E2317" s="43"/>
-      <c r="F2317" s="43"/>
-      <c r="G2317" s="43"/>
-      <c r="H2317" s="43"/>
-      <c r="I2317" s="43"/>
-      <c r="J2317" s="43"/>
-      <c r="K2317" s="43"/>
-      <c r="L2317" s="43"/>
-      <c r="M2317" s="43"/>
-      <c r="N2317" s="43"/>
-      <c r="O2317" s="43"/>
-      <c r="P2317" s="43"/>
-      <c r="Q2317" s="43"/>
-      <c r="R2317" s="43"/>
-      <c r="S2317" s="43"/>
-      <c r="T2317" s="43"/>
-      <c r="U2317" s="43"/>
-      <c r="V2317" s="43"/>
-      <c r="W2317" s="43"/>
-      <c r="X2317" s="43"/>
-      <c r="Y2317" s="43"/>
-      <c r="Z2317" s="43"/>
-      <c r="AA2317" s="43"/>
-      <c r="AB2317" s="43"/>
-      <c r="AC2317" s="43"/>
-      <c r="AD2317" s="43"/>
-      <c r="AE2317" s="43"/>
-      <c r="AF2317" s="43"/>
-      <c r="AG2317" s="43"/>
-      <c r="AH2317" s="43"/>
+      <c r="B2317" s="48"/>
+      <c r="C2317" s="48"/>
+      <c r="D2317" s="48"/>
+      <c r="E2317" s="48"/>
+      <c r="F2317" s="48"/>
+      <c r="G2317" s="48"/>
+      <c r="H2317" s="48"/>
+      <c r="I2317" s="48"/>
+      <c r="J2317" s="48"/>
+      <c r="K2317" s="48"/>
+      <c r="L2317" s="48"/>
+      <c r="M2317" s="48"/>
+      <c r="N2317" s="48"/>
+      <c r="O2317" s="48"/>
+      <c r="P2317" s="48"/>
+      <c r="Q2317" s="48"/>
+      <c r="R2317" s="48"/>
+      <c r="S2317" s="48"/>
+      <c r="T2317" s="48"/>
+      <c r="U2317" s="48"/>
+      <c r="V2317" s="48"/>
+      <c r="W2317" s="48"/>
+      <c r="X2317" s="48"/>
+      <c r="Y2317" s="48"/>
+      <c r="Z2317" s="48"/>
+      <c r="AA2317" s="48"/>
+      <c r="AB2317" s="48"/>
+      <c r="AC2317" s="48"/>
+      <c r="AD2317" s="48"/>
+      <c r="AE2317" s="48"/>
+      <c r="AF2317" s="48"/>
+      <c r="AG2317" s="48"/>
+      <c r="AH2317" s="48"/>
     </row>
     <row r="2419" spans="2:34" ht="15" customHeight="1">
-      <c r="B2419" s="43"/>
-      <c r="C2419" s="43"/>
-      <c r="D2419" s="43"/>
-      <c r="E2419" s="43"/>
-      <c r="F2419" s="43"/>
-      <c r="G2419" s="43"/>
-      <c r="H2419" s="43"/>
-      <c r="I2419" s="43"/>
-      <c r="J2419" s="43"/>
-      <c r="K2419" s="43"/>
-      <c r="L2419" s="43"/>
-      <c r="M2419" s="43"/>
-      <c r="N2419" s="43"/>
-      <c r="O2419" s="43"/>
-      <c r="P2419" s="43"/>
-      <c r="Q2419" s="43"/>
-      <c r="R2419" s="43"/>
-      <c r="S2419" s="43"/>
-      <c r="T2419" s="43"/>
-      <c r="U2419" s="43"/>
-      <c r="V2419" s="43"/>
-      <c r="W2419" s="43"/>
-      <c r="X2419" s="43"/>
-      <c r="Y2419" s="43"/>
-      <c r="Z2419" s="43"/>
-      <c r="AA2419" s="43"/>
-      <c r="AB2419" s="43"/>
-      <c r="AC2419" s="43"/>
-      <c r="AD2419" s="43"/>
-      <c r="AE2419" s="43"/>
-      <c r="AF2419" s="43"/>
-      <c r="AG2419" s="43"/>
-      <c r="AH2419" s="43"/>
+      <c r="B2419" s="48"/>
+      <c r="C2419" s="48"/>
+      <c r="D2419" s="48"/>
+      <c r="E2419" s="48"/>
+      <c r="F2419" s="48"/>
+      <c r="G2419" s="48"/>
+      <c r="H2419" s="48"/>
+      <c r="I2419" s="48"/>
+      <c r="J2419" s="48"/>
+      <c r="K2419" s="48"/>
+      <c r="L2419" s="48"/>
+      <c r="M2419" s="48"/>
+      <c r="N2419" s="48"/>
+      <c r="O2419" s="48"/>
+      <c r="P2419" s="48"/>
+      <c r="Q2419" s="48"/>
+      <c r="R2419" s="48"/>
+      <c r="S2419" s="48"/>
+      <c r="T2419" s="48"/>
+      <c r="U2419" s="48"/>
+      <c r="V2419" s="48"/>
+      <c r="W2419" s="48"/>
+      <c r="X2419" s="48"/>
+      <c r="Y2419" s="48"/>
+      <c r="Z2419" s="48"/>
+      <c r="AA2419" s="48"/>
+      <c r="AB2419" s="48"/>
+      <c r="AC2419" s="48"/>
+      <c r="AD2419" s="48"/>
+      <c r="AE2419" s="48"/>
+      <c r="AF2419" s="48"/>
+      <c r="AG2419" s="48"/>
+      <c r="AH2419" s="48"/>
     </row>
     <row r="2509" spans="2:34" ht="15" customHeight="1">
-      <c r="B2509" s="43"/>
-      <c r="C2509" s="43"/>
-      <c r="D2509" s="43"/>
-      <c r="E2509" s="43"/>
-      <c r="F2509" s="43"/>
-      <c r="G2509" s="43"/>
-      <c r="H2509" s="43"/>
-      <c r="I2509" s="43"/>
-      <c r="J2509" s="43"/>
-      <c r="K2509" s="43"/>
-      <c r="L2509" s="43"/>
-      <c r="M2509" s="43"/>
-      <c r="N2509" s="43"/>
-      <c r="O2509" s="43"/>
-      <c r="P2509" s="43"/>
-      <c r="Q2509" s="43"/>
-      <c r="R2509" s="43"/>
-      <c r="S2509" s="43"/>
-      <c r="T2509" s="43"/>
-      <c r="U2509" s="43"/>
-      <c r="V2509" s="43"/>
-      <c r="W2509" s="43"/>
-      <c r="X2509" s="43"/>
-      <c r="Y2509" s="43"/>
-      <c r="Z2509" s="43"/>
-      <c r="AA2509" s="43"/>
-      <c r="AB2509" s="43"/>
-      <c r="AC2509" s="43"/>
-      <c r="AD2509" s="43"/>
-      <c r="AE2509" s="43"/>
-      <c r="AF2509" s="43"/>
-      <c r="AG2509" s="43"/>
-      <c r="AH2509" s="43"/>
+      <c r="B2509" s="48"/>
+      <c r="C2509" s="48"/>
+      <c r="D2509" s="48"/>
+      <c r="E2509" s="48"/>
+      <c r="F2509" s="48"/>
+      <c r="G2509" s="48"/>
+      <c r="H2509" s="48"/>
+      <c r="I2509" s="48"/>
+      <c r="J2509" s="48"/>
+      <c r="K2509" s="48"/>
+      <c r="L2509" s="48"/>
+      <c r="M2509" s="48"/>
+      <c r="N2509" s="48"/>
+      <c r="O2509" s="48"/>
+      <c r="P2509" s="48"/>
+      <c r="Q2509" s="48"/>
+      <c r="R2509" s="48"/>
+      <c r="S2509" s="48"/>
+      <c r="T2509" s="48"/>
+      <c r="U2509" s="48"/>
+      <c r="V2509" s="48"/>
+      <c r="W2509" s="48"/>
+      <c r="X2509" s="48"/>
+      <c r="Y2509" s="48"/>
+      <c r="Z2509" s="48"/>
+      <c r="AA2509" s="48"/>
+      <c r="AB2509" s="48"/>
+      <c r="AC2509" s="48"/>
+      <c r="AD2509" s="48"/>
+      <c r="AE2509" s="48"/>
+      <c r="AF2509" s="48"/>
+      <c r="AG2509" s="48"/>
+      <c r="AH2509" s="48"/>
     </row>
     <row r="2598" spans="2:34" ht="15" customHeight="1">
-      <c r="B2598" s="43"/>
-      <c r="C2598" s="43"/>
-      <c r="D2598" s="43"/>
-      <c r="E2598" s="43"/>
-      <c r="F2598" s="43"/>
-      <c r="G2598" s="43"/>
-      <c r="H2598" s="43"/>
-      <c r="I2598" s="43"/>
-      <c r="J2598" s="43"/>
-      <c r="K2598" s="43"/>
-      <c r="L2598" s="43"/>
-      <c r="M2598" s="43"/>
-      <c r="N2598" s="43"/>
-      <c r="O2598" s="43"/>
-      <c r="P2598" s="43"/>
-      <c r="Q2598" s="43"/>
-      <c r="R2598" s="43"/>
-      <c r="S2598" s="43"/>
-      <c r="T2598" s="43"/>
-      <c r="U2598" s="43"/>
-      <c r="V2598" s="43"/>
-      <c r="W2598" s="43"/>
-      <c r="X2598" s="43"/>
-      <c r="Y2598" s="43"/>
-      <c r="Z2598" s="43"/>
-      <c r="AA2598" s="43"/>
-      <c r="AB2598" s="43"/>
-      <c r="AC2598" s="43"/>
-      <c r="AD2598" s="43"/>
-      <c r="AE2598" s="43"/>
-      <c r="AF2598" s="43"/>
-      <c r="AG2598" s="43"/>
-      <c r="AH2598" s="43"/>
+      <c r="B2598" s="48"/>
+      <c r="C2598" s="48"/>
+      <c r="D2598" s="48"/>
+      <c r="E2598" s="48"/>
+      <c r="F2598" s="48"/>
+      <c r="G2598" s="48"/>
+      <c r="H2598" s="48"/>
+      <c r="I2598" s="48"/>
+      <c r="J2598" s="48"/>
+      <c r="K2598" s="48"/>
+      <c r="L2598" s="48"/>
+      <c r="M2598" s="48"/>
+      <c r="N2598" s="48"/>
+      <c r="O2598" s="48"/>
+      <c r="P2598" s="48"/>
+      <c r="Q2598" s="48"/>
+      <c r="R2598" s="48"/>
+      <c r="S2598" s="48"/>
+      <c r="T2598" s="48"/>
+      <c r="U2598" s="48"/>
+      <c r="V2598" s="48"/>
+      <c r="W2598" s="48"/>
+      <c r="X2598" s="48"/>
+      <c r="Y2598" s="48"/>
+      <c r="Z2598" s="48"/>
+      <c r="AA2598" s="48"/>
+      <c r="AB2598" s="48"/>
+      <c r="AC2598" s="48"/>
+      <c r="AD2598" s="48"/>
+      <c r="AE2598" s="48"/>
+      <c r="AF2598" s="48"/>
+      <c r="AG2598" s="48"/>
+      <c r="AH2598" s="48"/>
     </row>
     <row r="2719" spans="2:34" ht="15" customHeight="1">
-      <c r="B2719" s="43"/>
-      <c r="C2719" s="43"/>
-      <c r="D2719" s="43"/>
-      <c r="E2719" s="43"/>
-      <c r="F2719" s="43"/>
-      <c r="G2719" s="43"/>
-      <c r="H2719" s="43"/>
-      <c r="I2719" s="43"/>
-      <c r="J2719" s="43"/>
-      <c r="K2719" s="43"/>
-      <c r="L2719" s="43"/>
-      <c r="M2719" s="43"/>
-      <c r="N2719" s="43"/>
-      <c r="O2719" s="43"/>
-      <c r="P2719" s="43"/>
-      <c r="Q2719" s="43"/>
-      <c r="R2719" s="43"/>
-      <c r="S2719" s="43"/>
-      <c r="T2719" s="43"/>
-      <c r="U2719" s="43"/>
-      <c r="V2719" s="43"/>
-      <c r="W2719" s="43"/>
-      <c r="X2719" s="43"/>
-      <c r="Y2719" s="43"/>
-      <c r="Z2719" s="43"/>
-      <c r="AA2719" s="43"/>
-      <c r="AB2719" s="43"/>
-      <c r="AC2719" s="43"/>
-      <c r="AD2719" s="43"/>
-      <c r="AE2719" s="43"/>
-      <c r="AF2719" s="43"/>
-      <c r="AG2719" s="43"/>
-      <c r="AH2719" s="43"/>
+      <c r="B2719" s="48"/>
+      <c r="C2719" s="48"/>
+      <c r="D2719" s="48"/>
+      <c r="E2719" s="48"/>
+      <c r="F2719" s="48"/>
+      <c r="G2719" s="48"/>
+      <c r="H2719" s="48"/>
+      <c r="I2719" s="48"/>
+      <c r="J2719" s="48"/>
+      <c r="K2719" s="48"/>
+      <c r="L2719" s="48"/>
+      <c r="M2719" s="48"/>
+      <c r="N2719" s="48"/>
+      <c r="O2719" s="48"/>
+      <c r="P2719" s="48"/>
+      <c r="Q2719" s="48"/>
+      <c r="R2719" s="48"/>
+      <c r="S2719" s="48"/>
+      <c r="T2719" s="48"/>
+      <c r="U2719" s="48"/>
+      <c r="V2719" s="48"/>
+      <c r="W2719" s="48"/>
+      <c r="X2719" s="48"/>
+      <c r="Y2719" s="48"/>
+      <c r="Z2719" s="48"/>
+      <c r="AA2719" s="48"/>
+      <c r="AB2719" s="48"/>
+      <c r="AC2719" s="48"/>
+      <c r="AD2719" s="48"/>
+      <c r="AE2719" s="48"/>
+      <c r="AF2719" s="48"/>
+      <c r="AG2719" s="48"/>
+      <c r="AH2719" s="48"/>
     </row>
     <row r="2837" spans="2:34" ht="15" customHeight="1">
-      <c r="B2837" s="43"/>
-      <c r="C2837" s="43"/>
-      <c r="D2837" s="43"/>
-      <c r="E2837" s="43"/>
-      <c r="F2837" s="43"/>
-      <c r="G2837" s="43"/>
-      <c r="H2837" s="43"/>
-      <c r="I2837" s="43"/>
-      <c r="J2837" s="43"/>
-      <c r="K2837" s="43"/>
-      <c r="L2837" s="43"/>
-      <c r="M2837" s="43"/>
-      <c r="N2837" s="43"/>
-      <c r="O2837" s="43"/>
-      <c r="P2837" s="43"/>
-      <c r="Q2837" s="43"/>
-      <c r="R2837" s="43"/>
-      <c r="S2837" s="43"/>
-      <c r="T2837" s="43"/>
-      <c r="U2837" s="43"/>
-      <c r="V2837" s="43"/>
-      <c r="W2837" s="43"/>
-      <c r="X2837" s="43"/>
-      <c r="Y2837" s="43"/>
-      <c r="Z2837" s="43"/>
-      <c r="AA2837" s="43"/>
-      <c r="AB2837" s="43"/>
-      <c r="AC2837" s="43"/>
-      <c r="AD2837" s="43"/>
-      <c r="AE2837" s="43"/>
-      <c r="AF2837" s="43"/>
-      <c r="AG2837" s="43"/>
-      <c r="AH2837" s="43"/>
+      <c r="B2837" s="48"/>
+      <c r="C2837" s="48"/>
+      <c r="D2837" s="48"/>
+      <c r="E2837" s="48"/>
+      <c r="F2837" s="48"/>
+      <c r="G2837" s="48"/>
+      <c r="H2837" s="48"/>
+      <c r="I2837" s="48"/>
+      <c r="J2837" s="48"/>
+      <c r="K2837" s="48"/>
+      <c r="L2837" s="48"/>
+      <c r="M2837" s="48"/>
+      <c r="N2837" s="48"/>
+      <c r="O2837" s="48"/>
+      <c r="P2837" s="48"/>
+      <c r="Q2837" s="48"/>
+      <c r="R2837" s="48"/>
+      <c r="S2837" s="48"/>
+      <c r="T2837" s="48"/>
+      <c r="U2837" s="48"/>
+      <c r="V2837" s="48"/>
+      <c r="W2837" s="48"/>
+      <c r="X2837" s="48"/>
+      <c r="Y2837" s="48"/>
+      <c r="Z2837" s="48"/>
+      <c r="AA2837" s="48"/>
+      <c r="AB2837" s="48"/>
+      <c r="AC2837" s="48"/>
+      <c r="AD2837" s="48"/>
+      <c r="AE2837" s="48"/>
+      <c r="AF2837" s="48"/>
+      <c r="AG2837" s="48"/>
+      <c r="AH2837" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="21">
@@ -9089,10 +9411,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7AAE509-8CD2-46CB-B214-D587CC47D2F8}">
   <dimension ref="A1:AH16"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="47.5546875" style="37" customWidth="1"/>
-    <col min="8" max="8" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="47.5703125" style="37" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="15" customHeight="1">
@@ -9627,7 +9949,7 @@
       </c>
       <c r="AH8" s="27"/>
     </row>
-    <row r="9" spans="1:34" ht="29.4" thickBot="1">
+    <row r="9" spans="1:34" ht="30.75" thickBot="1">
       <c r="B9" s="28" t="s">
         <v>156</v>
       </c>
@@ -9753,7 +10075,7 @@
         <v>15.95382699999999</v>
       </c>
     </row>
-    <row r="10" spans="1:34" ht="15" thickBot="1">
+    <row r="10" spans="1:34" ht="15.75" thickBot="1">
       <c r="A10" t="s">
         <v>159</v>
       </c>
@@ -9879,7 +10201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:34" ht="29.4" thickBot="1">
+    <row r="11" spans="1:34" ht="30.75" thickBot="1">
       <c r="A11" t="s">
         <v>159</v>
       </c>
@@ -9937,13 +10259,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DE83DD4-CB13-4EE4-BD52-2204426D41C9}">
   <dimension ref="A1:M158"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="9.109375" style="40"/>
-    <col min="3" max="3" width="23.44140625" style="40" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="9.109375" style="40"/>
-    <col min="13" max="13" width="46.109375" style="40" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.109375" style="40"/>
+    <col min="1" max="2" width="9.140625" style="40"/>
+    <col min="3" max="3" width="23.42578125" style="40" bestFit="1" customWidth="1"/>
+    <col min="4" max="12" width="9.140625" style="40"/>
+    <col min="13" max="13" width="46.140625" style="40" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="40"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -11935,17 +12257,609 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{254B4463-BB38-493F-B47F-A19475BAE606}">
+  <dimension ref="A1:F31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6" ht="48">
+      <c r="A1" s="43" t="s">
+        <v>302</v>
+      </c>
+      <c r="B1" s="43" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1" s="43" t="s">
+        <v>304</v>
+      </c>
+      <c r="D1" s="43" t="s">
+        <v>305</v>
+      </c>
+      <c r="E1" s="43" t="s">
+        <v>306</v>
+      </c>
+      <c r="F1" s="44" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="45" t="s">
+        <v>308</v>
+      </c>
+      <c r="B2" s="46" t="s">
+        <v>309</v>
+      </c>
+      <c r="C2" s="46" t="s">
+        <v>310</v>
+      </c>
+      <c r="D2" s="46">
+        <v>965</v>
+      </c>
+      <c r="E2" s="46" t="s">
+        <v>311</v>
+      </c>
+      <c r="F2" s="47" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="45" t="s">
+        <v>313</v>
+      </c>
+      <c r="B3" s="46" t="s">
+        <v>309</v>
+      </c>
+      <c r="C3" s="46" t="s">
+        <v>310</v>
+      </c>
+      <c r="D3" s="46">
+        <v>952</v>
+      </c>
+      <c r="E3" s="46" t="s">
+        <v>314</v>
+      </c>
+      <c r="F3" s="47" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="24">
+      <c r="A4" s="45" t="s">
+        <v>316</v>
+      </c>
+      <c r="B4" s="46" t="s">
+        <v>317</v>
+      </c>
+      <c r="C4" s="46" t="s">
+        <v>310</v>
+      </c>
+      <c r="D4" s="46">
+        <v>983</v>
+      </c>
+      <c r="E4" s="46" t="s">
+        <v>318</v>
+      </c>
+      <c r="F4" s="47" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="24">
+      <c r="A5" s="45" t="s">
+        <v>320</v>
+      </c>
+      <c r="B5" s="46" t="s">
+        <v>317</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>310</v>
+      </c>
+      <c r="D5" s="46">
+        <v>961</v>
+      </c>
+      <c r="E5" s="46" t="s">
+        <v>321</v>
+      </c>
+      <c r="F5" s="47" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="24">
+      <c r="A6" s="45" t="s">
+        <v>323</v>
+      </c>
+      <c r="B6" s="46" t="s">
+        <v>317</v>
+      </c>
+      <c r="C6" s="46" t="s">
+        <v>310</v>
+      </c>
+      <c r="D6" s="46">
+        <v>974</v>
+      </c>
+      <c r="E6" s="46" t="s">
+        <v>324</v>
+      </c>
+      <c r="F6" s="47" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="24">
+      <c r="A7" s="45" t="s">
+        <v>326</v>
+      </c>
+      <c r="B7" s="46" t="s">
+        <v>317</v>
+      </c>
+      <c r="C7" s="46" t="s">
+        <v>310</v>
+      </c>
+      <c r="D7" s="46">
+        <v>978</v>
+      </c>
+      <c r="E7" s="46" t="s">
+        <v>327</v>
+      </c>
+      <c r="F7" s="47" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="24">
+      <c r="A8" s="45" t="s">
+        <v>329</v>
+      </c>
+      <c r="B8" s="46" t="s">
+        <v>330</v>
+      </c>
+      <c r="C8" s="46" t="s">
+        <v>310</v>
+      </c>
+      <c r="D8" s="46">
+        <v>953</v>
+      </c>
+      <c r="E8" s="46" t="s">
+        <v>331</v>
+      </c>
+      <c r="F8" s="47" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="24">
+      <c r="A9" s="45" t="s">
+        <v>333</v>
+      </c>
+      <c r="B9" s="46" t="s">
+        <v>330</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>310</v>
+      </c>
+      <c r="D9" s="46">
+        <v>957</v>
+      </c>
+      <c r="E9" s="46" t="s">
+        <v>334</v>
+      </c>
+      <c r="F9" s="47" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="24">
+      <c r="A10" s="45" t="s">
+        <v>336</v>
+      </c>
+      <c r="B10" s="46" t="s">
+        <v>317</v>
+      </c>
+      <c r="C10" s="46" t="s">
+        <v>310</v>
+      </c>
+      <c r="D10" s="46">
+        <v>991</v>
+      </c>
+      <c r="E10" s="46" t="s">
+        <v>337</v>
+      </c>
+      <c r="F10" s="47" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="24">
+      <c r="A11" s="45" t="s">
+        <v>339</v>
+      </c>
+      <c r="B11" s="46" t="s">
+        <v>317</v>
+      </c>
+      <c r="C11" s="46" t="s">
+        <v>310</v>
+      </c>
+      <c r="D11" s="46">
+        <v>994</v>
+      </c>
+      <c r="E11" s="46" t="s">
+        <v>340</v>
+      </c>
+      <c r="F11" s="47" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="24">
+      <c r="A12" s="45" t="s">
+        <v>342</v>
+      </c>
+      <c r="B12" s="46" t="s">
+        <v>317</v>
+      </c>
+      <c r="C12" s="46" t="s">
+        <v>310</v>
+      </c>
+      <c r="D12" s="46">
+        <v>989</v>
+      </c>
+      <c r="E12" s="46" t="s">
+        <v>343</v>
+      </c>
+      <c r="F12" s="47" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="24">
+      <c r="A13" s="45" t="s">
+        <v>345</v>
+      </c>
+      <c r="B13" s="46" t="s">
+        <v>317</v>
+      </c>
+      <c r="C13" s="46" t="s">
+        <v>310</v>
+      </c>
+      <c r="D13" s="46">
+        <v>987</v>
+      </c>
+      <c r="E13" s="46" t="s">
+        <v>346</v>
+      </c>
+      <c r="F13" s="47" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="45" t="s">
+        <v>348</v>
+      </c>
+      <c r="B14" s="46" t="s">
+        <v>309</v>
+      </c>
+      <c r="C14" s="46" t="s">
+        <v>310</v>
+      </c>
+      <c r="D14" s="46">
+        <v>640</v>
+      </c>
+      <c r="E14" s="46" t="s">
+        <v>349</v>
+      </c>
+      <c r="F14" s="47" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="45" t="s">
+        <v>351</v>
+      </c>
+      <c r="B15" s="46" t="s">
+        <v>309</v>
+      </c>
+      <c r="C15" s="46" t="s">
+        <v>310</v>
+      </c>
+      <c r="D15" s="46">
+        <v>996</v>
+      </c>
+      <c r="E15" s="46" t="s">
+        <v>352</v>
+      </c>
+      <c r="F15" s="47" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="45" t="s">
+        <v>354</v>
+      </c>
+      <c r="B16" s="46" t="s">
+        <v>309</v>
+      </c>
+      <c r="C16" s="46" t="s">
+        <v>310</v>
+      </c>
+      <c r="D16" s="46">
+        <v>1001</v>
+      </c>
+      <c r="E16" s="46" t="s">
+        <v>355</v>
+      </c>
+      <c r="F16" s="47" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="45" t="s">
+        <v>357</v>
+      </c>
+      <c r="B17" s="46" t="s">
+        <v>358</v>
+      </c>
+      <c r="C17" s="46" t="s">
+        <v>310</v>
+      </c>
+      <c r="D17" s="46">
+        <v>1392</v>
+      </c>
+      <c r="E17" s="46" t="s">
+        <v>359</v>
+      </c>
+      <c r="F17" s="47" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="45" t="s">
+        <v>361</v>
+      </c>
+      <c r="B18" s="46" t="s">
+        <v>358</v>
+      </c>
+      <c r="C18" s="46" t="s">
+        <v>310</v>
+      </c>
+      <c r="D18" s="46">
+        <v>1392</v>
+      </c>
+      <c r="E18" s="46" t="s">
+        <v>362</v>
+      </c>
+      <c r="F18" s="47" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="30">
+      <c r="A19" s="45" t="s">
+        <v>364</v>
+      </c>
+      <c r="B19" s="46" t="s">
+        <v>358</v>
+      </c>
+      <c r="C19" s="46" t="s">
+        <v>310</v>
+      </c>
+      <c r="D19" s="46">
+        <v>1429</v>
+      </c>
+      <c r="E19" s="46" t="s">
+        <v>365</v>
+      </c>
+      <c r="F19" s="47" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="30">
+      <c r="A20" s="45" t="s">
+        <v>367</v>
+      </c>
+      <c r="B20" s="46" t="s">
+        <v>358</v>
+      </c>
+      <c r="C20" s="46" t="s">
+        <v>310</v>
+      </c>
+      <c r="D20" s="46">
+        <v>1416</v>
+      </c>
+      <c r="E20" s="46" t="s">
+        <v>368</v>
+      </c>
+      <c r="F20" s="47" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="30">
+      <c r="A21" s="45" t="s">
+        <v>370</v>
+      </c>
+      <c r="B21" s="46" t="s">
+        <v>317</v>
+      </c>
+      <c r="C21" s="46" t="s">
+        <v>310</v>
+      </c>
+      <c r="D21" s="46">
+        <v>986</v>
+      </c>
+      <c r="E21" s="46" t="s">
+        <v>371</v>
+      </c>
+      <c r="F21" s="47" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="30">
+      <c r="A22" s="45" t="s">
+        <v>373</v>
+      </c>
+      <c r="B22" s="46" t="s">
+        <v>317</v>
+      </c>
+      <c r="C22" s="46" t="s">
+        <v>310</v>
+      </c>
+      <c r="D22" s="46">
+        <v>982</v>
+      </c>
+      <c r="E22" s="46" t="s">
+        <v>374</v>
+      </c>
+      <c r="F22" s="47" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="45">
+      <c r="A23" s="45" t="s">
+        <v>376</v>
+      </c>
+      <c r="B23" s="46" t="s">
+        <v>317</v>
+      </c>
+      <c r="C23" s="46" t="s">
+        <v>310</v>
+      </c>
+      <c r="D23" s="46">
+        <v>980</v>
+      </c>
+      <c r="E23" s="46" t="s">
+        <v>377</v>
+      </c>
+      <c r="F23" s="47" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="45">
+      <c r="A24" s="45" t="s">
+        <v>378</v>
+      </c>
+      <c r="B24" s="46" t="s">
+        <v>317</v>
+      </c>
+      <c r="C24" s="46" t="s">
+        <v>310</v>
+      </c>
+      <c r="D24" s="46">
+        <v>976</v>
+      </c>
+      <c r="E24" s="46" t="s">
+        <v>379</v>
+      </c>
+      <c r="F24" s="47" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="30">
+      <c r="A25" s="45" t="s">
+        <v>381</v>
+      </c>
+      <c r="B25" s="46" t="s">
+        <v>382</v>
+      </c>
+      <c r="C25" s="46" t="s">
+        <v>383</v>
+      </c>
+      <c r="D25" s="46">
+        <v>571</v>
+      </c>
+      <c r="E25" s="46" t="s">
+        <v>384</v>
+      </c>
+      <c r="F25" s="47" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="30">
+      <c r="A26" s="45" t="s">
+        <v>386</v>
+      </c>
+      <c r="B26" s="46" t="s">
+        <v>382</v>
+      </c>
+      <c r="C26" s="46" t="s">
+        <v>383</v>
+      </c>
+      <c r="D26" s="46">
+        <v>595</v>
+      </c>
+      <c r="E26" s="46" t="s">
+        <v>387</v>
+      </c>
+      <c r="F26" s="47" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="30">
+      <c r="A27" s="45" t="s">
+        <v>389</v>
+      </c>
+      <c r="B27" s="46" t="s">
+        <v>382</v>
+      </c>
+      <c r="C27" s="46" t="s">
+        <v>383</v>
+      </c>
+      <c r="D27" s="46">
+        <v>569</v>
+      </c>
+      <c r="E27" s="46" t="s">
+        <v>390</v>
+      </c>
+      <c r="F27" s="47" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" t="s">
+        <v>393</v>
+      </c>
+      <c r="B31" t="s">
+        <v>394</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" display="https://world-nuclear.org/nuclear-reactor-database/details/HANBIT-1" xr:uid="{7266CC90-E10F-4BBF-98B2-159C947D2863}"/>
+    <hyperlink ref="A3" r:id="rId2" display="https://world-nuclear.org/nuclear-reactor-database/details/HANBIT-2" xr:uid="{ED7A0C0D-A652-4518-AD3C-6DD5BE2F1056}"/>
+    <hyperlink ref="A4" r:id="rId3" display="https://world-nuclear.org/nuclear-reactor-database/details/HANBIT-3" xr:uid="{3D417A3E-DFC2-4A1E-BDEE-EFE35C13CE91}"/>
+    <hyperlink ref="A5" r:id="rId4" display="https://world-nuclear.org/nuclear-reactor-database/details/HANBIT-4" xr:uid="{15C11589-81A2-493C-A948-BCAD10F2ABF6}"/>
+    <hyperlink ref="A6" r:id="rId5" display="https://world-nuclear.org/nuclear-reactor-database/details/HANBIT-5" xr:uid="{B174DE62-6EAA-48B3-B3B4-632EA3950B56}"/>
+    <hyperlink ref="A7" r:id="rId6" display="https://world-nuclear.org/nuclear-reactor-database/details/HANBIT-6" xr:uid="{164E0363-D8B1-482E-BAB9-CA00349531B4}"/>
+    <hyperlink ref="A8" r:id="rId7" display="https://world-nuclear.org/nuclear-reactor-database/details/HANUL-1" xr:uid="{F090CC0C-E235-43F6-8EB1-1243FF0DB3DF}"/>
+    <hyperlink ref="A9" r:id="rId8" display="https://world-nuclear.org/nuclear-reactor-database/details/HANUL-2" xr:uid="{958BA558-B279-4F38-B99C-4CCA33D8FBE4}"/>
+    <hyperlink ref="A10" r:id="rId9" display="https://world-nuclear.org/nuclear-reactor-database/details/HANUL-3" xr:uid="{B2C3058E-5766-4003-A0BF-289357E8F47B}"/>
+    <hyperlink ref="A11" r:id="rId10" display="https://world-nuclear.org/nuclear-reactor-database/details/HANUL-4" xr:uid="{826A5557-C160-48A1-AFF0-E9A04FD35348}"/>
+    <hyperlink ref="A12" r:id="rId11" display="https://world-nuclear.org/nuclear-reactor-database/details/HANUL-5" xr:uid="{68D8A1A4-1914-4396-971D-02DBF1FFDB81}"/>
+    <hyperlink ref="A13" r:id="rId12" display="https://world-nuclear.org/nuclear-reactor-database/details/HANUL-6" xr:uid="{20F6E7CE-7DB9-4D02-A58E-230151C2BE63}"/>
+    <hyperlink ref="A14" r:id="rId13" display="https://world-nuclear.org/nuclear-reactor-database/details/KORI-2" xr:uid="{E2E95EF5-D422-4B00-9508-1A45C8830F16}"/>
+    <hyperlink ref="A15" r:id="rId14" display="https://world-nuclear.org/nuclear-reactor-database/details/KORI-3" xr:uid="{6BC0187F-8EE3-44C9-A774-EFD0B207B01B}"/>
+    <hyperlink ref="A16" r:id="rId15" display="https://world-nuclear.org/nuclear-reactor-database/details/KORI-4" xr:uid="{FFC89F85-9152-44DF-9A3D-923E7395A807}"/>
+    <hyperlink ref="A17" r:id="rId16" display="https://world-nuclear.org/nuclear-reactor-database/details/SAEUL-1" xr:uid="{D84E7013-D1C8-4B4D-AEA0-7FD65D1B0C1C}"/>
+    <hyperlink ref="A18" r:id="rId17" display="https://world-nuclear.org/nuclear-reactor-database/details/SAEUL-2" xr:uid="{AC3A659A-62B1-49B8-AEBD-B83113E060E6}"/>
+    <hyperlink ref="A19" r:id="rId18" display="https://world-nuclear.org/nuclear-reactor-database/details/SHIN-HANUL-1" xr:uid="{188DE7DE-E682-41A1-BFB4-92C478E44034}"/>
+    <hyperlink ref="A20" r:id="rId19" display="https://world-nuclear.org/nuclear-reactor-database/details/SHIN-HANUL-2" xr:uid="{7BE90415-397B-4B82-959D-1F57EDDE9DE5}"/>
+    <hyperlink ref="A21" r:id="rId20" display="https://world-nuclear.org/nuclear-reactor-database/details/SHIN-KORI-1" xr:uid="{891168B7-7500-48C2-A5E8-107EFB8DDD02}"/>
+    <hyperlink ref="A22" r:id="rId21" display="https://world-nuclear.org/nuclear-reactor-database/details/SHIN-KORI-2" xr:uid="{93A9DAC4-67F8-48CE-9C6E-F7091738BAF3}"/>
+    <hyperlink ref="A23" r:id="rId22" display="https://world-nuclear.org/nuclear-reactor-database/details/SHIN-WOLSONG-1" xr:uid="{0EF9681E-BCC3-4AB5-83B3-D47C2ACF5AD7}"/>
+    <hyperlink ref="A24" r:id="rId23" display="https://world-nuclear.org/nuclear-reactor-database/details/SHIN-WOLSONG-2" xr:uid="{D7086C8D-F0DB-4EDA-88E7-BF3D9D58E0E6}"/>
+    <hyperlink ref="A25" r:id="rId24" display="https://world-nuclear.org/nuclear-reactor-database/details/WOLSONG-2" xr:uid="{213DEAE4-24A8-4471-A83F-EABF57C1A6D3}"/>
+    <hyperlink ref="A26" r:id="rId25" display="https://world-nuclear.org/nuclear-reactor-database/details/WOLSONG-3" xr:uid="{279E5DA0-8205-4FFC-8BD3-82B583A547E0}"/>
+    <hyperlink ref="A27" r:id="rId26" display="https://world-nuclear.org/nuclear-reactor-database/details/WOLSONG-4" xr:uid="{31A393FC-8141-47FF-842A-1779EABD0185}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId27"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AG35"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:AG25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.21875" customWidth="1"/>
-    <col min="3" max="3" width="8.33203125" customWidth="1"/>
-    <col min="10" max="10" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" customWidth="1"/>
+    <col min="3" max="3" width="8.28515625" customWidth="1"/>
+    <col min="10" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33">
@@ -11958,19 +12872,19 @@
       <c r="C1">
         <v>2020</v>
       </c>
-      <c r="D1" s="46">
+      <c r="D1">
         <v>2021</v>
       </c>
-      <c r="E1" s="46">
+      <c r="E1">
         <v>2022</v>
       </c>
-      <c r="F1" s="46">
+      <c r="F1">
         <v>2023</v>
       </c>
-      <c r="G1" s="46">
+      <c r="G1">
         <v>2024</v>
       </c>
-      <c r="H1" s="46">
+      <c r="H1">
         <v>2025</v>
       </c>
       <c r="I1">
@@ -12059,19 +12973,19 @@
       <c r="C2">
         <v>0</v>
       </c>
-      <c r="D2" s="46">
-        <v>0</v>
-      </c>
-      <c r="E2" s="46">
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>2080</v>
       </c>
-      <c r="F2" s="46">
-        <v>0</v>
-      </c>
-      <c r="G2" s="46">
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
         <v>1050</v>
       </c>
-      <c r="H2" s="46">
+      <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
@@ -12160,19 +13074,19 @@
       <c r="C3">
         <v>0</v>
       </c>
-      <c r="D3" s="46">
-        <v>0</v>
-      </c>
-      <c r="E3" s="46">
-        <v>0</v>
-      </c>
-      <c r="F3" s="46">
-        <v>0</v>
-      </c>
-      <c r="G3" s="46">
-        <v>0</v>
-      </c>
-      <c r="H3" s="46">
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
@@ -12262,19 +13176,19 @@
         <f t="array" ref="C4:Q4">TRANSPOSE(용량증설!M4:M18)</f>
         <v>1567</v>
       </c>
-      <c r="D4" s="46">
-        <v>0</v>
-      </c>
-      <c r="E4" s="46">
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>1000</v>
       </c>
-      <c r="F4" s="46">
-        <v>0</v>
-      </c>
-      <c r="G4" s="46">
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
         <v>4284</v>
       </c>
-      <c r="H4" s="46">
+      <c r="H4">
         <v>2500</v>
       </c>
       <c r="I4">
@@ -12363,23 +13277,24 @@
       <c r="C5">
         <v>0</v>
       </c>
-      <c r="D5" s="46">
-        <v>0</v>
-      </c>
-      <c r="E5" s="46">
-        <v>0</v>
-      </c>
-      <c r="F5" s="46">
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="16">
+        <f>'Nuclear Additions'!D19</f>
+        <v>1429</v>
+      </c>
+      <c r="F5">
         <v>1400</v>
       </c>
-      <c r="G5" s="46">
-        <v>0</v>
-      </c>
-      <c r="H5" s="46">
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -12400,7 +13315,7 @@
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -12464,19 +13379,19 @@
       <c r="C6">
         <v>0</v>
       </c>
-      <c r="D6" s="46">
-        <v>0</v>
-      </c>
-      <c r="E6" s="46">
-        <v>0</v>
-      </c>
-      <c r="F6" s="46">
-        <v>0</v>
-      </c>
-      <c r="G6" s="46">
-        <v>0</v>
-      </c>
-      <c r="H6" s="46">
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
@@ -12565,19 +13480,19 @@
       <c r="C7">
         <v>0</v>
       </c>
-      <c r="D7" s="46">
-        <v>0</v>
-      </c>
-      <c r="E7" s="46">
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
         <v>184.45939999999973</v>
       </c>
-      <c r="F7" s="46">
+      <c r="F7">
         <v>258.85960000000023</v>
       </c>
-      <c r="G7" s="46">
+      <c r="G7">
         <v>99.308999999999742</v>
       </c>
-      <c r="H7" s="46">
+      <c r="H7">
         <v>0</v>
       </c>
       <c r="I7">
@@ -12666,19 +13581,19 @@
       <c r="C8">
         <v>0</v>
       </c>
-      <c r="D8" s="46">
-        <v>0</v>
-      </c>
-      <c r="E8" s="46">
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
         <v>2628.1662219999998</v>
       </c>
-      <c r="F8" s="46">
+      <c r="F8">
         <v>2797.7593620000007</v>
       </c>
-      <c r="G8" s="46">
+      <c r="G8">
         <v>3173.1843929999995</v>
       </c>
-      <c r="H8" s="46">
+      <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
@@ -12767,19 +13682,19 @@
       <c r="C9">
         <v>0</v>
       </c>
-      <c r="D9" s="46">
-        <v>0</v>
-      </c>
-      <c r="E9" s="46">
-        <v>0</v>
-      </c>
-      <c r="F9" s="46">
-        <v>0</v>
-      </c>
-      <c r="G9" s="46">
-        <v>0</v>
-      </c>
-      <c r="H9" s="46">
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
@@ -12868,19 +13783,19 @@
       <c r="C10">
         <v>0</v>
       </c>
-      <c r="D10" s="46">
-        <v>0</v>
-      </c>
-      <c r="E10" s="46">
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
         <v>315.98956500000008</v>
       </c>
-      <c r="F10" s="46">
+      <c r="F10">
         <v>9.5494350000001305</v>
       </c>
-      <c r="G10" s="46">
+      <c r="G10">
         <v>424.07599999999979</v>
       </c>
-      <c r="H10" s="46">
+      <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
@@ -12969,19 +13884,19 @@
       <c r="C11">
         <v>0</v>
       </c>
-      <c r="D11" s="46">
-        <v>0</v>
-      </c>
-      <c r="E11" s="46">
-        <v>0</v>
-      </c>
-      <c r="F11" s="46">
-        <v>0</v>
-      </c>
-      <c r="G11" s="46">
-        <v>0</v>
-      </c>
-      <c r="H11" s="46">
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
@@ -13386,37 +14301,48 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <f>1.25*1000</f>
+        <v>1250</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <f t="shared" ref="I15:R15" si="0">1.25*1000</f>
+        <v>1250</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1250</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1250</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1250</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1250</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1250</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1250</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1250</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <f>1.25*1000</f>
+        <v>1250</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1250</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -14473,76 +15399,6 @@
       <c r="AG25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:33">
-      <c r="D26" s="46"/>
-      <c r="E26" s="46"/>
-      <c r="F26" s="46"/>
-      <c r="G26" s="46"/>
-      <c r="H26" s="46"/>
-    </row>
-    <row r="27" spans="1:33">
-      <c r="D27" s="46"/>
-      <c r="E27" s="46"/>
-      <c r="F27" s="46"/>
-      <c r="G27" s="46"/>
-      <c r="H27" s="46"/>
-    </row>
-    <row r="28" spans="1:33">
-      <c r="D28" s="46"/>
-      <c r="E28" s="46"/>
-      <c r="F28" s="46"/>
-      <c r="G28" s="46"/>
-      <c r="H28" s="46"/>
-    </row>
-    <row r="29" spans="1:33">
-      <c r="D29" s="46"/>
-      <c r="E29" s="46"/>
-      <c r="F29" s="46"/>
-      <c r="G29" s="46"/>
-      <c r="H29" s="46"/>
-    </row>
-    <row r="30" spans="1:33">
-      <c r="D30" s="46"/>
-      <c r="E30" s="46"/>
-      <c r="F30" s="46"/>
-      <c r="G30" s="46"/>
-      <c r="H30" s="46"/>
-    </row>
-    <row r="31" spans="1:33">
-      <c r="D31" s="46"/>
-      <c r="E31" s="46"/>
-      <c r="F31" s="46"/>
-      <c r="G31" s="46"/>
-      <c r="H31" s="46"/>
-    </row>
-    <row r="32" spans="1:33">
-      <c r="D32" s="46"/>
-      <c r="E32" s="46"/>
-      <c r="F32" s="46"/>
-      <c r="G32" s="46"/>
-      <c r="H32" s="46"/>
-    </row>
-    <row r="33" spans="4:8">
-      <c r="D33" s="46"/>
-      <c r="E33" s="46"/>
-      <c r="F33" s="46"/>
-      <c r="G33" s="46"/>
-      <c r="H33" s="46"/>
-    </row>
-    <row r="34" spans="4:8">
-      <c r="D34" s="46"/>
-      <c r="E34" s="46"/>
-      <c r="F34" s="46"/>
-      <c r="G34" s="46"/>
-      <c r="H34" s="46"/>
-    </row>
-    <row r="35" spans="4:8">
-      <c r="D35" s="46"/>
-      <c r="E35" s="46"/>
-      <c r="F35" s="46"/>
-      <c r="G35" s="46"/>
-      <c r="H35" s="46"/>
     </row>
   </sheetData>
   <phoneticPr fontId="15" type="noConversion"/>
@@ -14551,15 +15407,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
     <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
@@ -14703,21 +15550,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B79B8AEF-803A-4C5A-B04E-B80AE175902F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43ED1489-0F0F-460E-8DB0-F645CB7D0188}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14735,11 +15583,19 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B24FF82-77E2-4C47-88CE-8E1D1040FA1D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B79B8AEF-803A-4C5A-B04E-B80AE175902F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/InputData/elec/BPMCCS/BAU Pol Mandated Cap Const Sched.xlsx
+++ b/InputData/elec/BPMCCS/BAU Pol Mandated Cap Const Sched.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\South Korea\Models\eps-southkorea\InputData\elec\BPMCCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB0B8CE3-132D-48DA-A558-2AD31AB844D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A38BB8-4C69-44A5-BCBD-8C8B4B686A17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="43200" windowHeight="17145" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,8 @@
     <sheet name="AEO_coal discrepency" sheetId="6" state="hidden" r:id="rId3"/>
     <sheet name="용량증설" sheetId="7" r:id="rId4"/>
     <sheet name="Nuclear Additions" sheetId="8" r:id="rId5"/>
-    <sheet name="BPMCCS" sheetId="2" r:id="rId6"/>
+    <sheet name="KOSIS Capacities" sheetId="9" r:id="rId6"/>
+    <sheet name="BPMCCS" sheetId="2" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="436">
   <si>
     <t>Note:</t>
   </si>
@@ -1223,21 +1224,210 @@
   </si>
   <si>
     <t>(same link)</t>
+  </si>
+  <si>
+    <t>단위: kW</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unit: kW</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>합계</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>수력</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>원자력</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>집단</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대체</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>기타</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="9"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <t>화력</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Total</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hydro</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nuclear</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>District Energy</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Alternative Energy</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Others</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="9"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <t>Thermal</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">석탄혼소 </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>석유화력</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>액화천연가스</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>복합화력</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>내연력</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Coal Mix</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Oil Thermal</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>LNG</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Combined Cycle</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Internal Combustion</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>%</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 부생가스, 증류탑폐열, 여열회수, 천연가스압터빈</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. Waste heat in distillation tower, waste heat recovery, natural gas pressure turbine and by-product gas.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>주: 1. 상용자가 제외</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Note: 1. Except Non-utility in common use</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">      2. 2001. 4. 2. 한전의 발전부문은 발전부문 및 전력거래소로 분리</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">           2. On April 2, 2001, KEPCO's power generation division was divided into 6 generation subsidiary companies and a Power Exchange</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>자료: 한국전력공사</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Source: Korea Electric Power Corporation</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>All Power Plant Types Except Nuclear</t>
+  </si>
+  <si>
+    <t>Nuclear</t>
+  </si>
+  <si>
+    <t>KESIS</t>
+  </si>
+  <si>
+    <t>Yearbook of Energy Statistics (2024)</t>
+  </si>
+  <si>
+    <t>https://kesis.keei.re.kr/board.es?mid=a20301020000&amp;bid=0047</t>
+  </si>
+  <si>
+    <t>V-2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+  <numFmts count="13">
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="167" formatCode="#,##0.0000"/>
     <numFmt numFmtId="168" formatCode="_(* #,##0.00000_);_(* \(#,##0.00000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="169" formatCode="0.0_ "/>
+    <numFmt numFmtId="170" formatCode="0.0_);[Red]\(0.0\)"/>
+    <numFmt numFmtId="171" formatCode="#,##0_ "/>
+    <numFmt numFmtId="172" formatCode="#,##0.0_ "/>
+    <numFmt numFmtId="173" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="174" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1369,8 +1559,30 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1419,8 +1631,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -1497,8 +1721,292 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="double">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="double">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="15">
+  <cellStyleXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1526,8 +2034,9 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1633,10 +2142,252 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="19" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="19" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="19" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="19" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="19" fillId="9" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="19" fillId="9" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="19" fillId="9" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="19" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="19" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="19" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="173" fontId="19" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="174" fontId="19" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="174" fontId="19" fillId="9" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="19" fillId="9" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="19" fillId="9" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="19" fillId="9" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="173" fontId="19" fillId="9" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="174" fontId="19" fillId="9" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="19" fillId="9" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="19" fillId="9" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="19" fillId="9" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="173" fontId="19" fillId="9" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="174" fontId="19" fillId="9" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="173" fontId="19" fillId="9" borderId="28" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="174" fontId="19" fillId="9" borderId="28" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="173" fontId="19" fillId="9" borderId="0" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="173" fontId="19" fillId="9" borderId="25" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="174" fontId="19" fillId="9" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="19" fillId="9" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="19" fillId="9" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="173" fontId="19" fillId="9" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="174" fontId="19" fillId="9" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="173" fontId="19" fillId="9" borderId="33" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="19" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="19" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="21" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="37" fontId="19" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="19" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="19" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="37" fontId="19" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="37" fontId="19" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="15">
+  <cellStyles count="16">
     <cellStyle name="Body: normal cell" xfId="7" xr:uid="{984E6381-458F-4A44-B490-4FDDB410F732}"/>
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="15" builtinId="6"/>
     <cellStyle name="Comma 2" xfId="12" xr:uid="{F8B02F3F-7A99-46A8-9686-1C5588CF7FD5}"/>
     <cellStyle name="Font: Calibri, 9pt regular" xfId="3" xr:uid="{3EC9FFD2-A3A3-4163-A3B2-4851434903A2}"/>
     <cellStyle name="Footnotes: top row" xfId="8" xr:uid="{750572D9-22F8-472C-B35D-F5E1DC0D1319}"/>
@@ -1951,7 +2702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="67.140625" customWidth="1"/>
@@ -1966,62 +2717,98 @@
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="130" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="B4" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="B4" s="2">
+    <row r="5" spans="1:2">
+      <c r="B5" s="2">
         <v>2020</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="B5" t="s">
+    <row r="6" spans="1:2">
+      <c r="B6" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="B6" s="41" t="s">
+    <row r="7" spans="1:2">
+      <c r="B7" s="41" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="B7" t="s">
+    <row r="8" spans="1:2">
+      <c r="B8" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
     <row r="10" spans="1:2">
-      <c r="A10" t="s">
+      <c r="B10" s="130" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="B11" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="B12" s="2">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="B13" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="B14" s="131" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="B15" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1" xr:uid="{27F0587B-215B-4B75-B2A1-FA72167AE656}"/>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{27F0587B-215B-4B75-B2A1-FA72167AE656}"/>
+    <hyperlink ref="B14" r:id="rId2" xr:uid="{D46E19BD-76F1-4014-A666-1DFC5699163F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -9380,15 +10167,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B2598:AH2598"/>
-    <mergeCell ref="B2719:AH2719"/>
-    <mergeCell ref="B2837:AH2837"/>
-    <mergeCell ref="B1945:AH1945"/>
-    <mergeCell ref="B2031:AH2031"/>
-    <mergeCell ref="B2153:AH2153"/>
-    <mergeCell ref="B2317:AH2317"/>
-    <mergeCell ref="B2419:AH2419"/>
-    <mergeCell ref="B2509:AH2509"/>
     <mergeCell ref="B1698:AH1698"/>
     <mergeCell ref="B87:AG87"/>
     <mergeCell ref="B112:AH112"/>
@@ -9401,6 +10179,15 @@
     <mergeCell ref="B1390:AH1390"/>
     <mergeCell ref="B1502:AH1502"/>
     <mergeCell ref="B1604:AH1604"/>
+    <mergeCell ref="B2598:AH2598"/>
+    <mergeCell ref="B2719:AH2719"/>
+    <mergeCell ref="B2837:AH2837"/>
+    <mergeCell ref="B1945:AH1945"/>
+    <mergeCell ref="B2031:AH2031"/>
+    <mergeCell ref="B2153:AH2153"/>
+    <mergeCell ref="B2317:AH2317"/>
+    <mergeCell ref="B2419:AH2419"/>
+    <mergeCell ref="B2509:AH2509"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12849,6 +13636,3726 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D37EAD28-0959-4196-8FEB-9FD43BFE4423}">
+  <dimension ref="A1:Y53"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="6" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25" ht="15.75" thickBot="1">
+      <c r="A1" s="51" t="s">
+        <v>395</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="52"/>
+      <c r="Q1" s="54"/>
+      <c r="R1" s="52"/>
+      <c r="S1" s="54"/>
+      <c r="T1" s="52"/>
+      <c r="U1" s="54"/>
+      <c r="V1" s="52"/>
+      <c r="W1" s="54"/>
+      <c r="X1" s="52"/>
+      <c r="Y1" s="55" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25">
+      <c r="A2" s="56"/>
+      <c r="B2" s="57" t="s">
+        <v>397</v>
+      </c>
+      <c r="C2" s="58"/>
+      <c r="D2" s="57" t="s">
+        <v>398</v>
+      </c>
+      <c r="E2" s="58"/>
+      <c r="F2" s="57" t="s">
+        <v>399</v>
+      </c>
+      <c r="G2" s="58"/>
+      <c r="H2" s="57" t="s">
+        <v>400</v>
+      </c>
+      <c r="I2" s="58"/>
+      <c r="J2" s="57" t="s">
+        <v>401</v>
+      </c>
+      <c r="K2" s="58"/>
+      <c r="L2" s="57" t="s">
+        <v>402</v>
+      </c>
+      <c r="M2" s="58"/>
+      <c r="N2" s="57" t="s">
+        <v>403</v>
+      </c>
+      <c r="O2" s="59"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="60"/>
+      <c r="V2" s="60"/>
+      <c r="W2" s="60"/>
+      <c r="X2" s="60"/>
+      <c r="Y2" s="61"/>
+    </row>
+    <row r="3" spans="1:25">
+      <c r="A3" s="62"/>
+      <c r="B3" s="63" t="s">
+        <v>404</v>
+      </c>
+      <c r="C3" s="64"/>
+      <c r="D3" s="63" t="s">
+        <v>405</v>
+      </c>
+      <c r="E3" s="64"/>
+      <c r="F3" s="63" t="s">
+        <v>406</v>
+      </c>
+      <c r="G3" s="64"/>
+      <c r="H3" s="63" t="s">
+        <v>407</v>
+      </c>
+      <c r="I3" s="64"/>
+      <c r="J3" s="63" t="s">
+        <v>408</v>
+      </c>
+      <c r="K3" s="64"/>
+      <c r="L3" s="63" t="s">
+        <v>409</v>
+      </c>
+      <c r="M3" s="64"/>
+      <c r="N3" s="63" t="s">
+        <v>410</v>
+      </c>
+      <c r="O3" s="65"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66"/>
+      <c r="U3" s="66"/>
+      <c r="V3" s="66"/>
+      <c r="W3" s="66"/>
+      <c r="X3" s="66"/>
+      <c r="Y3" s="67"/>
+    </row>
+    <row r="4" spans="1:25">
+      <c r="A4" s="62"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="70"/>
+      <c r="K4" s="71"/>
+      <c r="L4" s="70"/>
+      <c r="M4" s="71"/>
+      <c r="N4" s="70"/>
+      <c r="O4" s="71"/>
+      <c r="P4" s="72" t="s">
+        <v>411</v>
+      </c>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="72" t="s">
+        <v>412</v>
+      </c>
+      <c r="S4" s="73"/>
+      <c r="T4" s="72" t="s">
+        <v>413</v>
+      </c>
+      <c r="U4" s="73"/>
+      <c r="V4" s="72" t="s">
+        <v>414</v>
+      </c>
+      <c r="W4" s="73"/>
+      <c r="X4" s="72" t="s">
+        <v>415</v>
+      </c>
+      <c r="Y4" s="73"/>
+    </row>
+    <row r="5" spans="1:25">
+      <c r="A5" s="74"/>
+      <c r="B5" s="75"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="75"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="78"/>
+      <c r="K5" s="77"/>
+      <c r="L5" s="75"/>
+      <c r="M5" s="77"/>
+      <c r="N5" s="75"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="80" t="s">
+        <v>416</v>
+      </c>
+      <c r="Q5" s="81"/>
+      <c r="R5" s="80" t="s">
+        <v>417</v>
+      </c>
+      <c r="S5" s="81"/>
+      <c r="T5" s="80" t="s">
+        <v>418</v>
+      </c>
+      <c r="U5" s="81"/>
+      <c r="V5" s="80" t="s">
+        <v>419</v>
+      </c>
+      <c r="W5" s="81"/>
+      <c r="X5" s="80" t="s">
+        <v>420</v>
+      </c>
+      <c r="Y5" s="81"/>
+    </row>
+    <row r="6" spans="1:25" ht="15.75" thickBot="1">
+      <c r="A6" s="82"/>
+      <c r="B6" s="83"/>
+      <c r="C6" s="84" t="s">
+        <v>421</v>
+      </c>
+      <c r="D6" s="83"/>
+      <c r="E6" s="85" t="s">
+        <v>421</v>
+      </c>
+      <c r="F6" s="83"/>
+      <c r="G6" s="85" t="s">
+        <v>421</v>
+      </c>
+      <c r="H6" s="83"/>
+      <c r="I6" s="85" t="s">
+        <v>421</v>
+      </c>
+      <c r="J6" s="83"/>
+      <c r="K6" s="85" t="s">
+        <v>421</v>
+      </c>
+      <c r="L6" s="83"/>
+      <c r="M6" s="85" t="s">
+        <v>421</v>
+      </c>
+      <c r="N6" s="83"/>
+      <c r="O6" s="86" t="s">
+        <v>421</v>
+      </c>
+      <c r="P6" s="83"/>
+      <c r="Q6" s="86" t="s">
+        <v>421</v>
+      </c>
+      <c r="R6" s="83"/>
+      <c r="S6" s="86" t="s">
+        <v>421</v>
+      </c>
+      <c r="T6" s="83"/>
+      <c r="U6" s="86" t="s">
+        <v>421</v>
+      </c>
+      <c r="V6" s="83"/>
+      <c r="W6" s="87" t="s">
+        <v>421</v>
+      </c>
+      <c r="X6" s="83"/>
+      <c r="Y6" s="86" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" ht="15.75" thickTop="1">
+      <c r="A7" s="88">
+        <v>1981</v>
+      </c>
+      <c r="B7" s="89">
+        <v>9835380</v>
+      </c>
+      <c r="C7" s="90">
+        <v>100</v>
+      </c>
+      <c r="D7" s="91">
+        <v>1201730</v>
+      </c>
+      <c r="E7" s="90">
+        <v>12.218</v>
+      </c>
+      <c r="F7" s="92">
+        <v>587000</v>
+      </c>
+      <c r="G7" s="93">
+        <v>5.968</v>
+      </c>
+      <c r="H7" s="92">
+        <v>0</v>
+      </c>
+      <c r="I7" s="93">
+        <v>0</v>
+      </c>
+      <c r="J7" s="92">
+        <v>0</v>
+      </c>
+      <c r="K7" s="93">
+        <v>0</v>
+      </c>
+      <c r="L7" s="92">
+        <v>0</v>
+      </c>
+      <c r="M7" s="93">
+        <v>0</v>
+      </c>
+      <c r="N7" s="92">
+        <v>8046650</v>
+      </c>
+      <c r="O7" s="94">
+        <v>81.813000000000002</v>
+      </c>
+      <c r="P7" s="92">
+        <v>725000</v>
+      </c>
+      <c r="Q7" s="93">
+        <v>7.3710000000000004</v>
+      </c>
+      <c r="R7" s="92">
+        <v>6087300</v>
+      </c>
+      <c r="S7" s="93">
+        <v>61.892000000000003</v>
+      </c>
+      <c r="T7" s="92">
+        <v>0</v>
+      </c>
+      <c r="U7" s="93">
+        <v>0</v>
+      </c>
+      <c r="V7" s="92">
+        <v>920000</v>
+      </c>
+      <c r="W7" s="93">
+        <v>9.3539999999999992</v>
+      </c>
+      <c r="X7" s="92">
+        <v>314350</v>
+      </c>
+      <c r="Y7" s="93">
+        <v>3.1960000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
+      <c r="A8" s="88">
+        <v>1982</v>
+      </c>
+      <c r="B8" s="89">
+        <v>10304063</v>
+      </c>
+      <c r="C8" s="90">
+        <v>100</v>
+      </c>
+      <c r="D8" s="91">
+        <v>1201730</v>
+      </c>
+      <c r="E8" s="90">
+        <v>11.663</v>
+      </c>
+      <c r="F8" s="92">
+        <v>1265683</v>
+      </c>
+      <c r="G8" s="93">
+        <v>12.282999999999999</v>
+      </c>
+      <c r="H8" s="92">
+        <v>0</v>
+      </c>
+      <c r="I8" s="93">
+        <v>0</v>
+      </c>
+      <c r="J8" s="92">
+        <v>0</v>
+      </c>
+      <c r="K8" s="93">
+        <v>0</v>
+      </c>
+      <c r="L8" s="92">
+        <v>0</v>
+      </c>
+      <c r="M8" s="93">
+        <v>0</v>
+      </c>
+      <c r="N8" s="92">
+        <v>7836650</v>
+      </c>
+      <c r="O8" s="93">
+        <v>76.054000000000002</v>
+      </c>
+      <c r="P8" s="92">
+        <v>650000</v>
+      </c>
+      <c r="Q8" s="93">
+        <v>6.3079999999999998</v>
+      </c>
+      <c r="R8" s="92">
+        <v>6072300</v>
+      </c>
+      <c r="S8" s="93">
+        <v>58.930999999999997</v>
+      </c>
+      <c r="T8" s="92">
+        <v>0</v>
+      </c>
+      <c r="U8" s="93">
+        <v>0</v>
+      </c>
+      <c r="V8" s="92">
+        <v>920000</v>
+      </c>
+      <c r="W8" s="93">
+        <v>8.9290000000000003</v>
+      </c>
+      <c r="X8" s="92">
+        <v>194350</v>
+      </c>
+      <c r="Y8" s="93">
+        <v>1.8859999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25">
+      <c r="A9" s="88">
+        <v>1983</v>
+      </c>
+      <c r="B9" s="89">
+        <v>13115263</v>
+      </c>
+      <c r="C9" s="90">
+        <v>100</v>
+      </c>
+      <c r="D9" s="91">
+        <v>1201730</v>
+      </c>
+      <c r="E9" s="90">
+        <v>9.1630000000000003</v>
+      </c>
+      <c r="F9" s="92">
+        <v>1915683</v>
+      </c>
+      <c r="G9" s="93">
+        <v>14.606999999999999</v>
+      </c>
+      <c r="H9" s="92">
+        <v>0</v>
+      </c>
+      <c r="I9" s="93">
+        <v>0</v>
+      </c>
+      <c r="J9" s="92">
+        <v>0</v>
+      </c>
+      <c r="K9" s="93">
+        <v>0</v>
+      </c>
+      <c r="L9" s="92">
+        <v>0</v>
+      </c>
+      <c r="M9" s="93">
+        <v>0</v>
+      </c>
+      <c r="N9" s="92">
+        <v>9997850</v>
+      </c>
+      <c r="O9" s="93">
+        <v>76.230999999999995</v>
+      </c>
+      <c r="P9" s="92">
+        <v>2110000</v>
+      </c>
+      <c r="Q9" s="93">
+        <v>16.088000000000001</v>
+      </c>
+      <c r="R9" s="92">
+        <v>6772300</v>
+      </c>
+      <c r="S9" s="93">
+        <v>51.637</v>
+      </c>
+      <c r="T9" s="92">
+        <v>0</v>
+      </c>
+      <c r="U9" s="93">
+        <v>0</v>
+      </c>
+      <c r="V9" s="92">
+        <v>920000</v>
+      </c>
+      <c r="W9" s="93">
+        <v>7.0149999999999997</v>
+      </c>
+      <c r="X9" s="92">
+        <v>195550</v>
+      </c>
+      <c r="Y9" s="93">
+        <v>1.4910000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
+      <c r="A10" s="88">
+        <v>1984</v>
+      </c>
+      <c r="B10" s="89">
+        <v>14190263</v>
+      </c>
+      <c r="C10" s="90">
+        <v>100</v>
+      </c>
+      <c r="D10" s="91">
+        <v>1201730</v>
+      </c>
+      <c r="E10" s="90">
+        <v>8.4689999999999994</v>
+      </c>
+      <c r="F10" s="92">
+        <v>1915683</v>
+      </c>
+      <c r="G10" s="93">
+        <v>13.5</v>
+      </c>
+      <c r="H10" s="92">
+        <v>0</v>
+      </c>
+      <c r="I10" s="93">
+        <v>0</v>
+      </c>
+      <c r="J10" s="92">
+        <v>0</v>
+      </c>
+      <c r="K10" s="93">
+        <v>0</v>
+      </c>
+      <c r="L10" s="92">
+        <v>0</v>
+      </c>
+      <c r="M10" s="93">
+        <v>0</v>
+      </c>
+      <c r="N10" s="92">
+        <v>11072850</v>
+      </c>
+      <c r="O10" s="93">
+        <v>78.031000000000006</v>
+      </c>
+      <c r="P10" s="92">
+        <v>3170000</v>
+      </c>
+      <c r="Q10" s="93">
+        <v>22.338999999999999</v>
+      </c>
+      <c r="R10" s="92">
+        <v>6772300</v>
+      </c>
+      <c r="S10" s="93">
+        <v>47.725000000000001</v>
+      </c>
+      <c r="T10" s="92">
+        <v>0</v>
+      </c>
+      <c r="U10" s="93">
+        <v>0</v>
+      </c>
+      <c r="V10" s="92">
+        <v>920000</v>
+      </c>
+      <c r="W10" s="93">
+        <v>6.4829999999999997</v>
+      </c>
+      <c r="X10" s="92">
+        <v>210550</v>
+      </c>
+      <c r="Y10" s="93">
+        <v>1.484</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
+      <c r="A11" s="95">
+        <v>1985</v>
+      </c>
+      <c r="B11" s="96">
+        <v>16136703</v>
+      </c>
+      <c r="C11" s="97">
+        <v>100</v>
+      </c>
+      <c r="D11" s="98">
+        <v>2223170</v>
+      </c>
+      <c r="E11" s="97">
+        <v>13.776999999999999</v>
+      </c>
+      <c r="F11" s="99">
+        <v>2865683</v>
+      </c>
+      <c r="G11" s="100">
+        <v>17.759</v>
+      </c>
+      <c r="H11" s="99">
+        <v>0</v>
+      </c>
+      <c r="I11" s="100">
+        <v>0</v>
+      </c>
+      <c r="J11" s="99">
+        <v>0</v>
+      </c>
+      <c r="K11" s="100">
+        <v>0</v>
+      </c>
+      <c r="L11" s="99">
+        <v>0</v>
+      </c>
+      <c r="M11" s="100">
+        <v>0</v>
+      </c>
+      <c r="N11" s="99">
+        <v>11047850</v>
+      </c>
+      <c r="O11" s="100">
+        <v>68.463999999999999</v>
+      </c>
+      <c r="P11" s="99">
+        <v>3700000</v>
+      </c>
+      <c r="Q11" s="100">
+        <v>22.928999999999998</v>
+      </c>
+      <c r="R11" s="99">
+        <v>6212300</v>
+      </c>
+      <c r="S11" s="100">
+        <v>38.497999999999998</v>
+      </c>
+      <c r="T11" s="99">
+        <v>0</v>
+      </c>
+      <c r="U11" s="100">
+        <v>0</v>
+      </c>
+      <c r="V11" s="99">
+        <v>920000</v>
+      </c>
+      <c r="W11" s="100">
+        <v>5.7009999999999996</v>
+      </c>
+      <c r="X11" s="99">
+        <v>215550</v>
+      </c>
+      <c r="Y11" s="100">
+        <v>1.3360000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25">
+      <c r="A12" s="101">
+        <v>1986</v>
+      </c>
+      <c r="B12" s="102">
+        <v>18060083</v>
+      </c>
+      <c r="C12" s="103">
+        <v>100</v>
+      </c>
+      <c r="D12" s="104">
+        <v>2224550</v>
+      </c>
+      <c r="E12" s="103">
+        <v>12.317</v>
+      </c>
+      <c r="F12" s="105">
+        <v>4765683</v>
+      </c>
+      <c r="G12" s="106">
+        <v>26.388000000000002</v>
+      </c>
+      <c r="H12" s="105">
+        <v>0</v>
+      </c>
+      <c r="I12" s="106">
+        <v>0</v>
+      </c>
+      <c r="J12" s="105">
+        <v>0</v>
+      </c>
+      <c r="K12" s="106">
+        <v>0</v>
+      </c>
+      <c r="L12" s="105">
+        <v>0</v>
+      </c>
+      <c r="M12" s="106">
+        <v>0</v>
+      </c>
+      <c r="N12" s="105">
+        <v>11069850</v>
+      </c>
+      <c r="O12" s="106">
+        <v>61.295000000000002</v>
+      </c>
+      <c r="P12" s="105">
+        <v>3700000</v>
+      </c>
+      <c r="Q12" s="106">
+        <v>20.486999999999998</v>
+      </c>
+      <c r="R12" s="105">
+        <v>6212300</v>
+      </c>
+      <c r="S12" s="106">
+        <v>34.398000000000003</v>
+      </c>
+      <c r="T12" s="107">
+        <v>0</v>
+      </c>
+      <c r="U12" s="108">
+        <v>0</v>
+      </c>
+      <c r="V12" s="105">
+        <v>920000</v>
+      </c>
+      <c r="W12" s="106">
+        <v>5.0940000000000003</v>
+      </c>
+      <c r="X12" s="105">
+        <v>237550</v>
+      </c>
+      <c r="Y12" s="106">
+        <v>1.3149999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25">
+      <c r="A13" s="88">
+        <v>1987</v>
+      </c>
+      <c r="B13" s="89">
+        <v>19020503</v>
+      </c>
+      <c r="C13" s="90">
+        <v>100</v>
+      </c>
+      <c r="D13" s="91">
+        <v>2232270</v>
+      </c>
+      <c r="E13" s="90">
+        <v>11.736000000000001</v>
+      </c>
+      <c r="F13" s="92">
+        <v>5715683</v>
+      </c>
+      <c r="G13" s="93">
+        <v>30.05</v>
+      </c>
+      <c r="H13" s="92">
+        <v>0</v>
+      </c>
+      <c r="I13" s="93">
+        <v>0</v>
+      </c>
+      <c r="J13" s="92">
+        <v>0</v>
+      </c>
+      <c r="K13" s="93">
+        <v>0</v>
+      </c>
+      <c r="L13" s="92">
+        <v>0</v>
+      </c>
+      <c r="M13" s="93">
+        <v>0</v>
+      </c>
+      <c r="N13" s="92">
+        <v>11072550</v>
+      </c>
+      <c r="O13" s="93">
+        <v>58.213999999999999</v>
+      </c>
+      <c r="P13" s="92">
+        <v>3700000</v>
+      </c>
+      <c r="Q13" s="93">
+        <v>19.452999999999999</v>
+      </c>
+      <c r="R13" s="92">
+        <v>3662300</v>
+      </c>
+      <c r="S13" s="93">
+        <v>19.254000000000001</v>
+      </c>
+      <c r="T13" s="92">
+        <v>2550000</v>
+      </c>
+      <c r="U13" s="93">
+        <v>13.407</v>
+      </c>
+      <c r="V13" s="92">
+        <v>920000</v>
+      </c>
+      <c r="W13" s="93">
+        <v>4.8369999999999997</v>
+      </c>
+      <c r="X13" s="92">
+        <v>240250</v>
+      </c>
+      <c r="Y13" s="93">
+        <v>1.2629999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25">
+      <c r="A14" s="88">
+        <v>1988</v>
+      </c>
+      <c r="B14" s="89">
+        <v>19944123</v>
+      </c>
+      <c r="C14" s="90">
+        <v>100</v>
+      </c>
+      <c r="D14" s="91">
+        <v>2235740</v>
+      </c>
+      <c r="E14" s="90">
+        <v>11.21</v>
+      </c>
+      <c r="F14" s="92">
+        <v>6665683</v>
+      </c>
+      <c r="G14" s="93">
+        <v>33.421999999999997</v>
+      </c>
+      <c r="H14" s="92">
+        <v>0</v>
+      </c>
+      <c r="I14" s="93">
+        <v>0</v>
+      </c>
+      <c r="J14" s="92">
+        <v>0</v>
+      </c>
+      <c r="K14" s="93">
+        <v>0</v>
+      </c>
+      <c r="L14" s="92">
+        <v>0</v>
+      </c>
+      <c r="M14" s="93">
+        <v>0</v>
+      </c>
+      <c r="N14" s="92">
+        <v>11042700</v>
+      </c>
+      <c r="O14" s="93">
+        <v>55.368000000000002</v>
+      </c>
+      <c r="P14" s="92">
+        <v>3700000</v>
+      </c>
+      <c r="Q14" s="93">
+        <v>18.552</v>
+      </c>
+      <c r="R14" s="92">
+        <v>3662300</v>
+      </c>
+      <c r="S14" s="93">
+        <v>18.363</v>
+      </c>
+      <c r="T14" s="92">
+        <v>2550000</v>
+      </c>
+      <c r="U14" s="93">
+        <v>12.786</v>
+      </c>
+      <c r="V14" s="92">
+        <v>895000</v>
+      </c>
+      <c r="W14" s="93">
+        <v>4.4880000000000004</v>
+      </c>
+      <c r="X14" s="92">
+        <v>235400</v>
+      </c>
+      <c r="Y14" s="93">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25">
+      <c r="A15" s="88">
+        <v>1989</v>
+      </c>
+      <c r="B15" s="89">
+        <v>20997043</v>
+      </c>
+      <c r="C15" s="90">
+        <v>100</v>
+      </c>
+      <c r="D15" s="91">
+        <v>2338660</v>
+      </c>
+      <c r="E15" s="90">
+        <v>11.138</v>
+      </c>
+      <c r="F15" s="92">
+        <v>7615683</v>
+      </c>
+      <c r="G15" s="93">
+        <v>36.270000000000003</v>
+      </c>
+      <c r="H15" s="92">
+        <v>0</v>
+      </c>
+      <c r="I15" s="93">
+        <v>0</v>
+      </c>
+      <c r="J15" s="92">
+        <v>0</v>
+      </c>
+      <c r="K15" s="93">
+        <v>0</v>
+      </c>
+      <c r="L15" s="92">
+        <v>0</v>
+      </c>
+      <c r="M15" s="93">
+        <v>0</v>
+      </c>
+      <c r="N15" s="92">
+        <v>11042700</v>
+      </c>
+      <c r="O15" s="93">
+        <v>52.591999999999999</v>
+      </c>
+      <c r="P15" s="92">
+        <v>3700000</v>
+      </c>
+      <c r="Q15" s="93">
+        <v>17.622</v>
+      </c>
+      <c r="R15" s="92">
+        <v>3662300</v>
+      </c>
+      <c r="S15" s="93">
+        <v>17.442</v>
+      </c>
+      <c r="T15" s="92">
+        <v>2550000</v>
+      </c>
+      <c r="U15" s="93">
+        <v>12.145</v>
+      </c>
+      <c r="V15" s="92">
+        <v>840000</v>
+      </c>
+      <c r="W15" s="93">
+        <v>4.0010000000000003</v>
+      </c>
+      <c r="X15" s="92">
+        <v>290400</v>
+      </c>
+      <c r="Y15" s="93">
+        <v>1.383</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25">
+      <c r="A16" s="95">
+        <v>1990</v>
+      </c>
+      <c r="B16" s="96">
+        <v>21021123</v>
+      </c>
+      <c r="C16" s="97">
+        <v>100</v>
+      </c>
+      <c r="D16" s="98">
+        <v>2340040</v>
+      </c>
+      <c r="E16" s="97">
+        <v>11.132</v>
+      </c>
+      <c r="F16" s="99">
+        <v>7615683</v>
+      </c>
+      <c r="G16" s="100">
+        <v>36.228999999999999</v>
+      </c>
+      <c r="H16" s="99">
+        <v>0</v>
+      </c>
+      <c r="I16" s="100">
+        <v>0</v>
+      </c>
+      <c r="J16" s="99">
+        <v>0</v>
+      </c>
+      <c r="K16" s="100">
+        <v>0</v>
+      </c>
+      <c r="L16" s="99">
+        <v>0</v>
+      </c>
+      <c r="M16" s="100">
+        <v>0</v>
+      </c>
+      <c r="N16" s="99">
+        <v>11065400</v>
+      </c>
+      <c r="O16" s="100">
+        <v>52.639000000000003</v>
+      </c>
+      <c r="P16" s="99">
+        <v>3700000</v>
+      </c>
+      <c r="Q16" s="100">
+        <v>17.600999999999999</v>
+      </c>
+      <c r="R16" s="99">
+        <v>3662300</v>
+      </c>
+      <c r="S16" s="100">
+        <v>17.422000000000001</v>
+      </c>
+      <c r="T16" s="99">
+        <v>2550000</v>
+      </c>
+      <c r="U16" s="100">
+        <v>12.131</v>
+      </c>
+      <c r="V16" s="99">
+        <v>840000</v>
+      </c>
+      <c r="W16" s="100">
+        <v>3.996</v>
+      </c>
+      <c r="X16" s="99">
+        <v>313100</v>
+      </c>
+      <c r="Y16" s="100">
+        <v>1.4890000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25">
+      <c r="A17" s="101">
+        <v>1991</v>
+      </c>
+      <c r="B17" s="102">
+        <v>21110623</v>
+      </c>
+      <c r="C17" s="103">
+        <v>100</v>
+      </c>
+      <c r="D17" s="104">
+        <v>2444540</v>
+      </c>
+      <c r="E17" s="103">
+        <v>11.58</v>
+      </c>
+      <c r="F17" s="105">
+        <v>7615683</v>
+      </c>
+      <c r="G17" s="106">
+        <v>36.075000000000003</v>
+      </c>
+      <c r="H17" s="105">
+        <v>0</v>
+      </c>
+      <c r="I17" s="106">
+        <v>0</v>
+      </c>
+      <c r="J17" s="105">
+        <v>0</v>
+      </c>
+      <c r="K17" s="106">
+        <v>0</v>
+      </c>
+      <c r="L17" s="105">
+        <v>0</v>
+      </c>
+      <c r="M17" s="106">
+        <v>0</v>
+      </c>
+      <c r="N17" s="105">
+        <v>11050400</v>
+      </c>
+      <c r="O17" s="106">
+        <v>52.344999999999999</v>
+      </c>
+      <c r="P17" s="105">
+        <v>3700000</v>
+      </c>
+      <c r="Q17" s="106">
+        <v>17.527000000000001</v>
+      </c>
+      <c r="R17" s="105">
+        <v>3662300</v>
+      </c>
+      <c r="S17" s="106">
+        <v>17.347999999999999</v>
+      </c>
+      <c r="T17" s="105">
+        <v>2550000</v>
+      </c>
+      <c r="U17" s="106">
+        <v>12.079000000000001</v>
+      </c>
+      <c r="V17" s="105">
+        <v>760000</v>
+      </c>
+      <c r="W17" s="106">
+        <v>3.6</v>
+      </c>
+      <c r="X17" s="105">
+        <v>378100</v>
+      </c>
+      <c r="Y17" s="106">
+        <v>1.7909999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25">
+      <c r="A18" s="88">
+        <v>1992</v>
+      </c>
+      <c r="B18" s="89">
+        <v>24120073</v>
+      </c>
+      <c r="C18" s="90">
+        <v>100</v>
+      </c>
+      <c r="D18" s="91">
+        <v>2497790</v>
+      </c>
+      <c r="E18" s="90">
+        <v>10.356</v>
+      </c>
+      <c r="F18" s="92">
+        <v>7615683</v>
+      </c>
+      <c r="G18" s="93">
+        <v>31.574000000000002</v>
+      </c>
+      <c r="H18" s="92">
+        <v>0</v>
+      </c>
+      <c r="I18" s="93">
+        <v>0</v>
+      </c>
+      <c r="J18" s="92">
+        <v>0</v>
+      </c>
+      <c r="K18" s="93">
+        <v>0</v>
+      </c>
+      <c r="L18" s="92">
+        <v>0</v>
+      </c>
+      <c r="M18" s="93">
+        <v>0</v>
+      </c>
+      <c r="N18" s="92">
+        <v>14006600</v>
+      </c>
+      <c r="O18" s="93">
+        <v>58.07</v>
+      </c>
+      <c r="P18" s="92">
+        <v>3700000</v>
+      </c>
+      <c r="Q18" s="93">
+        <v>15.34</v>
+      </c>
+      <c r="R18" s="92">
+        <v>3662300</v>
+      </c>
+      <c r="S18" s="93">
+        <v>15.183999999999999</v>
+      </c>
+      <c r="T18" s="92">
+        <v>2550000</v>
+      </c>
+      <c r="U18" s="93">
+        <v>10.571999999999999</v>
+      </c>
+      <c r="V18" s="92">
+        <v>3706200</v>
+      </c>
+      <c r="W18" s="93">
+        <v>15.366</v>
+      </c>
+      <c r="X18" s="92">
+        <v>388100</v>
+      </c>
+      <c r="Y18" s="93">
+        <v>1.609</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25">
+      <c r="A19" s="88">
+        <v>1993</v>
+      </c>
+      <c r="B19" s="89">
+        <v>27653693</v>
+      </c>
+      <c r="C19" s="90">
+        <v>100</v>
+      </c>
+      <c r="D19" s="91">
+        <v>2503710</v>
+      </c>
+      <c r="E19" s="90">
+        <v>9.0540000000000003</v>
+      </c>
+      <c r="F19" s="92">
+        <v>7615683</v>
+      </c>
+      <c r="G19" s="93">
+        <v>27.539000000000001</v>
+      </c>
+      <c r="H19" s="92">
+        <v>0</v>
+      </c>
+      <c r="I19" s="93">
+        <v>0</v>
+      </c>
+      <c r="J19" s="92">
+        <v>0</v>
+      </c>
+      <c r="K19" s="93">
+        <v>0</v>
+      </c>
+      <c r="L19" s="92">
+        <v>0</v>
+      </c>
+      <c r="M19" s="93">
+        <v>0</v>
+      </c>
+      <c r="N19" s="92">
+        <v>17534300</v>
+      </c>
+      <c r="O19" s="93">
+        <v>63.406999999999996</v>
+      </c>
+      <c r="P19" s="92">
+        <v>5760000</v>
+      </c>
+      <c r="Q19" s="93">
+        <v>20.829000000000001</v>
+      </c>
+      <c r="R19" s="92">
+        <v>4424800</v>
+      </c>
+      <c r="S19" s="93">
+        <v>16.001000000000001</v>
+      </c>
+      <c r="T19" s="92">
+        <v>1787500</v>
+      </c>
+      <c r="U19" s="93">
+        <v>6.4640000000000004</v>
+      </c>
+      <c r="V19" s="92">
+        <v>5172550</v>
+      </c>
+      <c r="W19" s="93">
+        <v>18.704999999999998</v>
+      </c>
+      <c r="X19" s="92">
+        <v>389450</v>
+      </c>
+      <c r="Y19" s="93">
+        <v>1.4079999999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25">
+      <c r="A20" s="88">
+        <v>1994</v>
+      </c>
+      <c r="B20" s="89">
+        <v>28749573</v>
+      </c>
+      <c r="C20" s="90">
+        <v>100</v>
+      </c>
+      <c r="D20" s="91">
+        <v>2492590</v>
+      </c>
+      <c r="E20" s="90">
+        <v>8.67</v>
+      </c>
+      <c r="F20" s="92">
+        <v>7615683</v>
+      </c>
+      <c r="G20" s="93">
+        <v>26.49</v>
+      </c>
+      <c r="H20" s="92">
+        <v>0</v>
+      </c>
+      <c r="I20" s="93">
+        <v>0</v>
+      </c>
+      <c r="J20" s="92">
+        <v>0</v>
+      </c>
+      <c r="K20" s="93">
+        <v>0</v>
+      </c>
+      <c r="L20" s="92">
+        <v>0</v>
+      </c>
+      <c r="M20" s="93">
+        <v>0</v>
+      </c>
+      <c r="N20" s="92">
+        <v>18641300</v>
+      </c>
+      <c r="O20" s="93">
+        <v>64.84</v>
+      </c>
+      <c r="P20" s="92">
+        <v>6820000</v>
+      </c>
+      <c r="Q20" s="93">
+        <v>23.722000000000001</v>
+      </c>
+      <c r="R20" s="92">
+        <v>4424800</v>
+      </c>
+      <c r="S20" s="93">
+        <v>15.391</v>
+      </c>
+      <c r="T20" s="92">
+        <v>1787500</v>
+      </c>
+      <c r="U20" s="93">
+        <v>6.2169999999999996</v>
+      </c>
+      <c r="V20" s="92">
+        <v>5333550</v>
+      </c>
+      <c r="W20" s="93">
+        <v>18.552</v>
+      </c>
+      <c r="X20" s="92">
+        <v>275450</v>
+      </c>
+      <c r="Y20" s="93">
+        <v>0.95799999999999996</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25">
+      <c r="A21" s="95">
+        <v>1995</v>
+      </c>
+      <c r="B21" s="96">
+        <v>32183873</v>
+      </c>
+      <c r="C21" s="97">
+        <v>100</v>
+      </c>
+      <c r="D21" s="98">
+        <v>3093390</v>
+      </c>
+      <c r="E21" s="97">
+        <v>9.6120000000000001</v>
+      </c>
+      <c r="F21" s="99">
+        <v>8615683</v>
+      </c>
+      <c r="G21" s="100">
+        <v>26.77</v>
+      </c>
+      <c r="H21" s="99">
+        <v>0</v>
+      </c>
+      <c r="I21" s="100">
+        <v>0</v>
+      </c>
+      <c r="J21" s="99">
+        <v>0</v>
+      </c>
+      <c r="K21" s="100">
+        <v>0</v>
+      </c>
+      <c r="L21" s="99">
+        <v>0</v>
+      </c>
+      <c r="M21" s="100">
+        <v>0</v>
+      </c>
+      <c r="N21" s="99">
+        <v>20474800</v>
+      </c>
+      <c r="O21" s="100">
+        <v>63.618000000000002</v>
+      </c>
+      <c r="P21" s="99">
+        <v>7820000</v>
+      </c>
+      <c r="Q21" s="100">
+        <v>24.297999999999998</v>
+      </c>
+      <c r="R21" s="99">
+        <v>4674800</v>
+      </c>
+      <c r="S21" s="100">
+        <v>14.525</v>
+      </c>
+      <c r="T21" s="99">
+        <v>1537500</v>
+      </c>
+      <c r="U21" s="100">
+        <v>4.7770000000000001</v>
+      </c>
+      <c r="V21" s="99">
+        <v>6183550</v>
+      </c>
+      <c r="W21" s="100">
+        <v>19.213000000000001</v>
+      </c>
+      <c r="X21" s="99">
+        <v>258950</v>
+      </c>
+      <c r="Y21" s="100">
+        <v>0.80500000000000005</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25">
+      <c r="A22" s="101">
+        <v>1996</v>
+      </c>
+      <c r="B22" s="102">
+        <v>35715433</v>
+      </c>
+      <c r="C22" s="103">
+        <v>100</v>
+      </c>
+      <c r="D22" s="104">
+        <v>3094450</v>
+      </c>
+      <c r="E22" s="103">
+        <v>8.6639999999999997</v>
+      </c>
+      <c r="F22" s="105">
+        <v>9615683</v>
+      </c>
+      <c r="G22" s="106">
+        <v>26.922999999999998</v>
+      </c>
+      <c r="H22" s="105">
+        <v>0</v>
+      </c>
+      <c r="I22" s="106">
+        <v>0</v>
+      </c>
+      <c r="J22" s="105">
+        <v>0</v>
+      </c>
+      <c r="K22" s="106">
+        <v>0</v>
+      </c>
+      <c r="L22" s="105">
+        <v>0</v>
+      </c>
+      <c r="M22" s="106">
+        <v>0</v>
+      </c>
+      <c r="N22" s="105">
+        <v>23005300</v>
+      </c>
+      <c r="O22" s="106">
+        <v>64.412999999999997</v>
+      </c>
+      <c r="P22" s="105">
+        <v>7820000</v>
+      </c>
+      <c r="Q22" s="106">
+        <v>21.895</v>
+      </c>
+      <c r="R22" s="105">
+        <v>4664800</v>
+      </c>
+      <c r="S22" s="106">
+        <v>13.061</v>
+      </c>
+      <c r="T22" s="105">
+        <v>1537500</v>
+      </c>
+      <c r="U22" s="106">
+        <v>4.3049999999999997</v>
+      </c>
+      <c r="V22" s="105">
+        <v>8718550</v>
+      </c>
+      <c r="W22" s="106">
+        <v>24.411000000000001</v>
+      </c>
+      <c r="X22" s="105">
+        <v>264450</v>
+      </c>
+      <c r="Y22" s="106">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25">
+      <c r="A23" s="88">
+        <v>1997</v>
+      </c>
+      <c r="B23" s="89">
+        <v>41041778</v>
+      </c>
+      <c r="C23" s="90">
+        <v>100</v>
+      </c>
+      <c r="D23" s="91">
+        <v>3114595</v>
+      </c>
+      <c r="E23" s="90">
+        <v>7.5890000000000004</v>
+      </c>
+      <c r="F23" s="92">
+        <v>10315683</v>
+      </c>
+      <c r="G23" s="93">
+        <v>25.135000000000002</v>
+      </c>
+      <c r="H23" s="92">
+        <v>0</v>
+      </c>
+      <c r="I23" s="93">
+        <v>0</v>
+      </c>
+      <c r="J23" s="92">
+        <v>0</v>
+      </c>
+      <c r="K23" s="93">
+        <v>0</v>
+      </c>
+      <c r="L23" s="92">
+        <v>0</v>
+      </c>
+      <c r="M23" s="93">
+        <v>0</v>
+      </c>
+      <c r="N23" s="92">
+        <v>27611500</v>
+      </c>
+      <c r="O23" s="93">
+        <v>67.277000000000001</v>
+      </c>
+      <c r="P23" s="92">
+        <v>10200000</v>
+      </c>
+      <c r="Q23" s="93">
+        <v>24.853000000000002</v>
+      </c>
+      <c r="R23" s="92">
+        <v>4340000</v>
+      </c>
+      <c r="S23" s="93">
+        <v>10.574999999999999</v>
+      </c>
+      <c r="T23" s="92">
+        <v>1537500</v>
+      </c>
+      <c r="U23" s="93">
+        <v>3.746</v>
+      </c>
+      <c r="V23" s="92">
+        <v>11268550</v>
+      </c>
+      <c r="W23" s="93">
+        <v>27.456</v>
+      </c>
+      <c r="X23" s="92">
+        <v>265450</v>
+      </c>
+      <c r="Y23" s="93">
+        <v>0.64700000000000002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25">
+      <c r="A24" s="88">
+        <v>1998</v>
+      </c>
+      <c r="B24" s="89">
+        <v>43405841</v>
+      </c>
+      <c r="C24" s="90">
+        <v>100</v>
+      </c>
+      <c r="D24" s="91">
+        <v>3131208</v>
+      </c>
+      <c r="E24" s="90">
+        <v>7.2140000000000004</v>
+      </c>
+      <c r="F24" s="92">
+        <v>12015683</v>
+      </c>
+      <c r="G24" s="93">
+        <v>27.681999999999999</v>
+      </c>
+      <c r="H24" s="92">
+        <v>0</v>
+      </c>
+      <c r="I24" s="93">
+        <v>0</v>
+      </c>
+      <c r="J24" s="92">
+        <v>0</v>
+      </c>
+      <c r="K24" s="93">
+        <v>0</v>
+      </c>
+      <c r="L24" s="92">
+        <v>0</v>
+      </c>
+      <c r="M24" s="93">
+        <v>0</v>
+      </c>
+      <c r="N24" s="92">
+        <v>28258950</v>
+      </c>
+      <c r="O24" s="93">
+        <v>65.103999999999999</v>
+      </c>
+      <c r="P24" s="92">
+        <v>11331000</v>
+      </c>
+      <c r="Q24" s="93">
+        <v>26.105</v>
+      </c>
+      <c r="R24" s="92">
+        <v>4340000</v>
+      </c>
+      <c r="S24" s="93">
+        <v>9.9990000000000006</v>
+      </c>
+      <c r="T24" s="92">
+        <v>1537500</v>
+      </c>
+      <c r="U24" s="93">
+        <v>3.5419999999999998</v>
+      </c>
+      <c r="V24" s="92">
+        <v>10785000</v>
+      </c>
+      <c r="W24" s="93">
+        <v>24.847000000000001</v>
+      </c>
+      <c r="X24" s="92">
+        <v>265450</v>
+      </c>
+      <c r="Y24" s="93">
+        <v>0.61199999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25">
+      <c r="A25" s="88">
+        <v>1999</v>
+      </c>
+      <c r="B25" s="89">
+        <v>46977697</v>
+      </c>
+      <c r="C25" s="90">
+        <v>100</v>
+      </c>
+      <c r="D25" s="91">
+        <v>3147564</v>
+      </c>
+      <c r="E25" s="90">
+        <v>6.7</v>
+      </c>
+      <c r="F25" s="92">
+        <v>13715683</v>
+      </c>
+      <c r="G25" s="93">
+        <v>29.196000000000002</v>
+      </c>
+      <c r="H25" s="92">
+        <v>0</v>
+      </c>
+      <c r="I25" s="93">
+        <v>0</v>
+      </c>
+      <c r="J25" s="92">
+        <v>0</v>
+      </c>
+      <c r="K25" s="93">
+        <v>0</v>
+      </c>
+      <c r="L25" s="92">
+        <v>0</v>
+      </c>
+      <c r="M25" s="93">
+        <v>0</v>
+      </c>
+      <c r="N25" s="92">
+        <v>30114450</v>
+      </c>
+      <c r="O25" s="93">
+        <v>64.103999999999999</v>
+      </c>
+      <c r="P25" s="92">
+        <v>13031000</v>
+      </c>
+      <c r="Q25" s="93">
+        <v>27.739000000000001</v>
+      </c>
+      <c r="R25" s="92">
+        <v>4340000</v>
+      </c>
+      <c r="S25" s="93">
+        <v>9.2379999999999995</v>
+      </c>
+      <c r="T25" s="92">
+        <v>1537500</v>
+      </c>
+      <c r="U25" s="93">
+        <v>3.2730000000000001</v>
+      </c>
+      <c r="V25" s="92">
+        <v>10935000</v>
+      </c>
+      <c r="W25" s="93">
+        <v>23.277000000000001</v>
+      </c>
+      <c r="X25" s="92">
+        <v>270950</v>
+      </c>
+      <c r="Y25" s="93">
+        <v>0.57699999999999996</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25">
+      <c r="A26" s="95">
+        <v>2000</v>
+      </c>
+      <c r="B26" s="96">
+        <v>48450717</v>
+      </c>
+      <c r="C26" s="97">
+        <v>100</v>
+      </c>
+      <c r="D26" s="98">
+        <v>3148664</v>
+      </c>
+      <c r="E26" s="97">
+        <v>6.4989999999999997</v>
+      </c>
+      <c r="F26" s="99">
+        <v>13715683</v>
+      </c>
+      <c r="G26" s="100">
+        <v>28.309000000000001</v>
+      </c>
+      <c r="H26" s="99">
+        <v>0</v>
+      </c>
+      <c r="I26" s="100">
+        <v>0</v>
+      </c>
+      <c r="J26" s="99">
+        <v>0</v>
+      </c>
+      <c r="K26" s="100">
+        <v>0</v>
+      </c>
+      <c r="L26" s="99">
+        <v>0</v>
+      </c>
+      <c r="M26" s="100">
+        <v>0</v>
+      </c>
+      <c r="N26" s="99">
+        <v>31586370</v>
+      </c>
+      <c r="O26" s="100">
+        <v>65.192999999999998</v>
+      </c>
+      <c r="P26" s="99">
+        <v>14031000</v>
+      </c>
+      <c r="Q26" s="100">
+        <v>28.959</v>
+      </c>
+      <c r="R26" s="99">
+        <v>4490000</v>
+      </c>
+      <c r="S26" s="100">
+        <v>9.2669999999999995</v>
+      </c>
+      <c r="T26" s="99">
+        <v>1537500</v>
+      </c>
+      <c r="U26" s="100">
+        <v>3.173</v>
+      </c>
+      <c r="V26" s="99">
+        <v>11256920</v>
+      </c>
+      <c r="W26" s="100">
+        <v>23.234000000000002</v>
+      </c>
+      <c r="X26" s="99">
+        <v>270950</v>
+      </c>
+      <c r="Y26" s="100">
+        <v>0.55900000000000005</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25">
+      <c r="A27" s="101">
+        <v>2001</v>
+      </c>
+      <c r="B27" s="102">
+        <v>50858647</v>
+      </c>
+      <c r="C27" s="103">
+        <v>100</v>
+      </c>
+      <c r="D27" s="104">
+        <v>3875764</v>
+      </c>
+      <c r="E27" s="103">
+        <v>7.6210000000000004</v>
+      </c>
+      <c r="F27" s="105">
+        <v>13715683</v>
+      </c>
+      <c r="G27" s="106">
+        <v>26.968</v>
+      </c>
+      <c r="H27" s="105">
+        <v>0</v>
+      </c>
+      <c r="I27" s="106">
+        <v>0</v>
+      </c>
+      <c r="J27" s="105">
+        <v>0</v>
+      </c>
+      <c r="K27" s="106">
+        <v>0</v>
+      </c>
+      <c r="L27" s="105">
+        <v>0</v>
+      </c>
+      <c r="M27" s="106">
+        <v>0</v>
+      </c>
+      <c r="N27" s="105">
+        <v>33267200</v>
+      </c>
+      <c r="O27" s="106">
+        <v>65.411000000000001</v>
+      </c>
+      <c r="P27" s="105">
+        <v>15531000</v>
+      </c>
+      <c r="Q27" s="106">
+        <v>30.538</v>
+      </c>
+      <c r="R27" s="105">
+        <v>4490000</v>
+      </c>
+      <c r="S27" s="106">
+        <v>8.8279999999999994</v>
+      </c>
+      <c r="T27" s="107">
+        <v>1537500</v>
+      </c>
+      <c r="U27" s="106">
+        <v>3.0230000000000001</v>
+      </c>
+      <c r="V27" s="105">
+        <v>11435750</v>
+      </c>
+      <c r="W27" s="106">
+        <v>22.484999999999999</v>
+      </c>
+      <c r="X27" s="105">
+        <v>272950</v>
+      </c>
+      <c r="Y27" s="106">
+        <v>0.53700000000000003</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25">
+      <c r="A28" s="88">
+        <v>2002</v>
+      </c>
+      <c r="B28" s="89">
+        <v>53800847</v>
+      </c>
+      <c r="C28" s="90">
+        <v>100</v>
+      </c>
+      <c r="D28" s="91">
+        <v>3875764</v>
+      </c>
+      <c r="E28" s="90">
+        <v>7.2039999999999997</v>
+      </c>
+      <c r="F28" s="92">
+        <v>15715683</v>
+      </c>
+      <c r="G28" s="93">
+        <v>29.210999999999999</v>
+      </c>
+      <c r="H28" s="92">
+        <v>0</v>
+      </c>
+      <c r="I28" s="93">
+        <v>0</v>
+      </c>
+      <c r="J28" s="92">
+        <v>0</v>
+      </c>
+      <c r="K28" s="93">
+        <v>0</v>
+      </c>
+      <c r="L28" s="92">
+        <v>0</v>
+      </c>
+      <c r="M28" s="93">
+        <v>0</v>
+      </c>
+      <c r="N28" s="92">
+        <v>34209400</v>
+      </c>
+      <c r="O28" s="93">
+        <v>63.585000000000001</v>
+      </c>
+      <c r="P28" s="92">
+        <v>15931000</v>
+      </c>
+      <c r="Q28" s="93">
+        <v>29.611000000000001</v>
+      </c>
+      <c r="R28" s="92">
+        <v>4280000</v>
+      </c>
+      <c r="S28" s="93">
+        <v>7.9550000000000001</v>
+      </c>
+      <c r="T28" s="109">
+        <v>1537500</v>
+      </c>
+      <c r="U28" s="93">
+        <v>2.8580000000000001</v>
+      </c>
+      <c r="V28" s="92">
+        <v>12185750</v>
+      </c>
+      <c r="W28" s="93">
+        <v>22.65</v>
+      </c>
+      <c r="X28" s="92">
+        <v>275150</v>
+      </c>
+      <c r="Y28" s="93">
+        <v>0.51100000000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25">
+      <c r="A29" s="88">
+        <v>2003</v>
+      </c>
+      <c r="B29" s="89">
+        <v>56052677</v>
+      </c>
+      <c r="C29" s="90">
+        <v>100</v>
+      </c>
+      <c r="D29" s="91">
+        <v>3876779</v>
+      </c>
+      <c r="E29" s="90">
+        <v>6.9160000000000004</v>
+      </c>
+      <c r="F29" s="92">
+        <v>15715683</v>
+      </c>
+      <c r="G29" s="93">
+        <v>28.036999999999999</v>
+      </c>
+      <c r="H29" s="92">
+        <v>1296200</v>
+      </c>
+      <c r="I29" s="93">
+        <v>2.3119999999999998</v>
+      </c>
+      <c r="J29" s="92">
+        <v>83315</v>
+      </c>
+      <c r="K29" s="93">
+        <v>0.14899999999999999</v>
+      </c>
+      <c r="L29" s="92">
+        <v>0</v>
+      </c>
+      <c r="M29" s="93">
+        <v>0</v>
+      </c>
+      <c r="N29" s="92">
+        <v>35080700</v>
+      </c>
+      <c r="O29" s="93">
+        <v>62.585000000000001</v>
+      </c>
+      <c r="P29" s="92">
+        <v>15931000</v>
+      </c>
+      <c r="Q29" s="93">
+        <v>28.420999999999999</v>
+      </c>
+      <c r="R29" s="92">
+        <v>4280000</v>
+      </c>
+      <c r="S29" s="93">
+        <v>7.6360000000000001</v>
+      </c>
+      <c r="T29" s="109">
+        <v>1537500</v>
+      </c>
+      <c r="U29" s="93">
+        <v>2.7429999999999999</v>
+      </c>
+      <c r="V29" s="92">
+        <v>13085750</v>
+      </c>
+      <c r="W29" s="93">
+        <v>23.344999999999999</v>
+      </c>
+      <c r="X29" s="92">
+        <v>246450</v>
+      </c>
+      <c r="Y29" s="93">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25">
+      <c r="A30" s="88">
+        <v>2004</v>
+      </c>
+      <c r="B30" s="89">
+        <v>59961131</v>
+      </c>
+      <c r="C30" s="90">
+        <v>100</v>
+      </c>
+      <c r="D30" s="91">
+        <v>3879313</v>
+      </c>
+      <c r="E30" s="90">
+        <v>6.47</v>
+      </c>
+      <c r="F30" s="92">
+        <v>16715683</v>
+      </c>
+      <c r="G30" s="93">
+        <v>27.878</v>
+      </c>
+      <c r="H30" s="92">
+        <v>1381500</v>
+      </c>
+      <c r="I30" s="93">
+        <v>2.3039999999999998</v>
+      </c>
+      <c r="J30" s="92">
+        <v>107905</v>
+      </c>
+      <c r="K30" s="93">
+        <v>0.18</v>
+      </c>
+      <c r="L30" s="92">
+        <v>0</v>
+      </c>
+      <c r="M30" s="93">
+        <v>0</v>
+      </c>
+      <c r="N30" s="92">
+        <v>37876730</v>
+      </c>
+      <c r="O30" s="93">
+        <v>63.168999999999997</v>
+      </c>
+      <c r="P30" s="92">
+        <v>17465000</v>
+      </c>
+      <c r="Q30" s="93">
+        <v>29.126999999999999</v>
+      </c>
+      <c r="R30" s="92">
+        <v>4308600</v>
+      </c>
+      <c r="S30" s="93">
+        <v>7.1859999999999999</v>
+      </c>
+      <c r="T30" s="109">
+        <v>1537500</v>
+      </c>
+      <c r="U30" s="93">
+        <v>2.5640000000000001</v>
+      </c>
+      <c r="V30" s="92">
+        <v>14313350</v>
+      </c>
+      <c r="W30" s="93">
+        <v>23.870999999999999</v>
+      </c>
+      <c r="X30" s="92">
+        <v>252280</v>
+      </c>
+      <c r="Y30" s="93">
+        <v>0.42099999999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25">
+      <c r="A31" s="95">
+        <v>2005</v>
+      </c>
+      <c r="B31" s="96">
+        <v>62258197</v>
+      </c>
+      <c r="C31" s="97">
+        <v>100</v>
+      </c>
+      <c r="D31" s="98">
+        <v>3882813</v>
+      </c>
+      <c r="E31" s="97">
+        <v>6.2370000000000001</v>
+      </c>
+      <c r="F31" s="99">
+        <v>17715683</v>
+      </c>
+      <c r="G31" s="100">
+        <v>28.454999999999998</v>
+      </c>
+      <c r="H31" s="99">
+        <v>1381500</v>
+      </c>
+      <c r="I31" s="100">
+        <v>2.2189999999999999</v>
+      </c>
+      <c r="J31" s="99">
+        <v>155622</v>
+      </c>
+      <c r="K31" s="100">
+        <v>0.25</v>
+      </c>
+      <c r="L31" s="99">
+        <v>0</v>
+      </c>
+      <c r="M31" s="100">
+        <v>0</v>
+      </c>
+      <c r="N31" s="99">
+        <v>39122579</v>
+      </c>
+      <c r="O31" s="100">
+        <v>62.838999999999999</v>
+      </c>
+      <c r="P31" s="99">
+        <v>17965000</v>
+      </c>
+      <c r="Q31" s="100">
+        <v>28.856000000000002</v>
+      </c>
+      <c r="R31" s="99">
+        <v>4308600</v>
+      </c>
+      <c r="S31" s="100">
+        <v>6.9210000000000003</v>
+      </c>
+      <c r="T31" s="110">
+        <v>1537500</v>
+      </c>
+      <c r="U31" s="100">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="V31" s="99">
+        <v>15014789</v>
+      </c>
+      <c r="W31" s="100">
+        <v>24.117000000000001</v>
+      </c>
+      <c r="X31" s="99">
+        <v>296690</v>
+      </c>
+      <c r="Y31" s="100">
+        <v>0.47699999999999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25">
+      <c r="A32" s="101">
+        <v>2006</v>
+      </c>
+      <c r="B32" s="102">
+        <v>65514242</v>
+      </c>
+      <c r="C32" s="103">
+        <v>100</v>
+      </c>
+      <c r="D32" s="104">
+        <v>5484858</v>
+      </c>
+      <c r="E32" s="103">
+        <v>8.3719999999999999</v>
+      </c>
+      <c r="F32" s="105">
+        <v>17715683</v>
+      </c>
+      <c r="G32" s="106">
+        <v>27.041</v>
+      </c>
+      <c r="H32" s="105">
+        <v>1381500</v>
+      </c>
+      <c r="I32" s="106">
+        <v>2.109</v>
+      </c>
+      <c r="J32" s="105">
+        <v>240422</v>
+      </c>
+      <c r="K32" s="106">
+        <v>0.36699999999999999</v>
+      </c>
+      <c r="L32" s="105">
+        <v>0</v>
+      </c>
+      <c r="M32" s="106">
+        <v>0</v>
+      </c>
+      <c r="N32" s="105">
+        <v>40691779</v>
+      </c>
+      <c r="O32" s="106">
+        <v>62.110999999999997</v>
+      </c>
+      <c r="P32" s="105">
+        <v>18465000</v>
+      </c>
+      <c r="Q32" s="106">
+        <v>28.184999999999999</v>
+      </c>
+      <c r="R32" s="105">
+        <v>4388600</v>
+      </c>
+      <c r="S32" s="106">
+        <v>6.6989999999999998</v>
+      </c>
+      <c r="T32" s="107">
+        <v>1537500</v>
+      </c>
+      <c r="U32" s="106">
+        <v>2.347</v>
+      </c>
+      <c r="V32" s="105">
+        <v>16003989</v>
+      </c>
+      <c r="W32" s="106">
+        <v>24.428000000000001</v>
+      </c>
+      <c r="X32" s="105">
+        <v>296690</v>
+      </c>
+      <c r="Y32" s="106">
+        <v>0.45300000000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25">
+      <c r="A33" s="88">
+        <v>2007</v>
+      </c>
+      <c r="B33" s="89">
+        <v>68268188</v>
+      </c>
+      <c r="C33" s="90">
+        <v>100</v>
+      </c>
+      <c r="D33" s="91">
+        <v>5492087</v>
+      </c>
+      <c r="E33" s="90">
+        <v>8.0449999999999999</v>
+      </c>
+      <c r="F33" s="92">
+        <v>17715683</v>
+      </c>
+      <c r="G33" s="93">
+        <v>25.95</v>
+      </c>
+      <c r="H33" s="92">
+        <v>1381500</v>
+      </c>
+      <c r="I33" s="93">
+        <v>2.024</v>
+      </c>
+      <c r="J33" s="92">
+        <v>373659</v>
+      </c>
+      <c r="K33" s="93">
+        <v>0.54700000000000004</v>
+      </c>
+      <c r="L33" s="92">
+        <v>0</v>
+      </c>
+      <c r="M33" s="93">
+        <v>0</v>
+      </c>
+      <c r="N33" s="92">
+        <v>43305259</v>
+      </c>
+      <c r="O33" s="93">
+        <v>63.433999999999997</v>
+      </c>
+      <c r="P33" s="92">
+        <v>20465000</v>
+      </c>
+      <c r="Q33" s="93">
+        <v>29.977</v>
+      </c>
+      <c r="R33" s="92">
+        <v>4488600</v>
+      </c>
+      <c r="S33" s="93">
+        <v>6.5750000000000002</v>
+      </c>
+      <c r="T33" s="109">
+        <v>1537500</v>
+      </c>
+      <c r="U33" s="93">
+        <v>2.2519999999999998</v>
+      </c>
+      <c r="V33" s="92">
+        <v>16510989</v>
+      </c>
+      <c r="W33" s="93">
+        <v>24.184999999999999</v>
+      </c>
+      <c r="X33" s="92">
+        <v>303170</v>
+      </c>
+      <c r="Y33" s="93">
+        <v>0.44400000000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25">
+      <c r="A34" s="88">
+        <v>2008</v>
+      </c>
+      <c r="B34" s="89">
+        <v>72490691.533000007</v>
+      </c>
+      <c r="C34" s="90">
+        <v>100</v>
+      </c>
+      <c r="D34" s="91">
+        <v>5505137.2000000002</v>
+      </c>
+      <c r="E34" s="90">
+        <v>7.5940000000000003</v>
+      </c>
+      <c r="F34" s="92">
+        <v>17715683</v>
+      </c>
+      <c r="G34" s="93">
+        <v>24.439</v>
+      </c>
+      <c r="H34" s="92">
+        <v>1459630</v>
+      </c>
+      <c r="I34" s="93">
+        <v>2.0139999999999998</v>
+      </c>
+      <c r="J34" s="92">
+        <v>728337.33299999998</v>
+      </c>
+      <c r="K34" s="93">
+        <v>1.0049999999999999</v>
+      </c>
+      <c r="L34" s="92">
+        <v>0</v>
+      </c>
+      <c r="M34" s="93">
+        <v>0</v>
+      </c>
+      <c r="N34" s="92">
+        <v>47081904</v>
+      </c>
+      <c r="O34" s="93">
+        <v>64.948999999999998</v>
+      </c>
+      <c r="P34" s="92">
+        <v>23705000</v>
+      </c>
+      <c r="Q34" s="93">
+        <v>32.701000000000001</v>
+      </c>
+      <c r="R34" s="92">
+        <v>4488600</v>
+      </c>
+      <c r="S34" s="93">
+        <v>6.1920000000000002</v>
+      </c>
+      <c r="T34" s="109">
+        <v>1537500</v>
+      </c>
+      <c r="U34" s="93">
+        <v>2.121</v>
+      </c>
+      <c r="V34" s="92">
+        <v>17043989</v>
+      </c>
+      <c r="W34" s="93">
+        <v>23.512</v>
+      </c>
+      <c r="X34" s="92">
+        <v>306815</v>
+      </c>
+      <c r="Y34" s="93">
+        <v>0.42299999999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25">
+      <c r="A35" s="88">
+        <v>2009</v>
+      </c>
+      <c r="B35" s="89">
+        <v>73469978.003999993</v>
+      </c>
+      <c r="C35" s="90">
+        <v>100</v>
+      </c>
+      <c r="D35" s="91">
+        <v>5514571.7999999998</v>
+      </c>
+      <c r="E35" s="90">
+        <v>7.5060000000000002</v>
+      </c>
+      <c r="F35" s="92">
+        <v>17715683</v>
+      </c>
+      <c r="G35" s="93">
+        <v>24.113</v>
+      </c>
+      <c r="H35" s="92">
+        <v>1610210</v>
+      </c>
+      <c r="I35" s="93">
+        <v>2.1920000000000002</v>
+      </c>
+      <c r="J35" s="92">
+        <v>1136352</v>
+      </c>
+      <c r="K35" s="93">
+        <v>1.5469999999999999</v>
+      </c>
+      <c r="L35" s="92">
+        <v>0</v>
+      </c>
+      <c r="M35" s="93">
+        <v>0</v>
+      </c>
+      <c r="N35" s="92">
+        <v>47493161</v>
+      </c>
+      <c r="O35" s="93">
+        <v>64.643000000000001</v>
+      </c>
+      <c r="P35" s="92">
+        <v>24205000</v>
+      </c>
+      <c r="Q35" s="93">
+        <v>32.945</v>
+      </c>
+      <c r="R35" s="92">
+        <v>4478600</v>
+      </c>
+      <c r="S35" s="93">
+        <v>6.0960000000000001</v>
+      </c>
+      <c r="T35" s="109">
+        <v>887500</v>
+      </c>
+      <c r="U35" s="93">
+        <v>1.208</v>
+      </c>
+      <c r="V35" s="92">
+        <v>17574961</v>
+      </c>
+      <c r="W35" s="93">
+        <v>23.920999999999999</v>
+      </c>
+      <c r="X35" s="92">
+        <v>347100</v>
+      </c>
+      <c r="Y35" s="93">
+        <v>0.47199999999999998</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25">
+      <c r="A36" s="95">
+        <v>2010</v>
+      </c>
+      <c r="B36" s="96">
+        <v>76078188.180000007</v>
+      </c>
+      <c r="C36" s="97">
+        <v>100</v>
+      </c>
+      <c r="D36" s="98">
+        <v>5524540</v>
+      </c>
+      <c r="E36" s="97">
+        <v>7.2619999999999996</v>
+      </c>
+      <c r="F36" s="99">
+        <v>17715683</v>
+      </c>
+      <c r="G36" s="100">
+        <v>23.286000000000001</v>
+      </c>
+      <c r="H36" s="99">
+        <v>2066724</v>
+      </c>
+      <c r="I36" s="100">
+        <v>2.7170000000000001</v>
+      </c>
+      <c r="J36" s="99">
+        <v>1748980.18</v>
+      </c>
+      <c r="K36" s="100">
+        <v>2.2989999999999999</v>
+      </c>
+      <c r="L36" s="99">
+        <v>0</v>
+      </c>
+      <c r="M36" s="100">
+        <v>0</v>
+      </c>
+      <c r="N36" s="99">
+        <v>49022261</v>
+      </c>
+      <c r="O36" s="100">
+        <v>64.436999999999998</v>
+      </c>
+      <c r="P36" s="99">
+        <v>24205000</v>
+      </c>
+      <c r="Q36" s="100">
+        <v>31.815999999999999</v>
+      </c>
+      <c r="R36" s="99">
+        <v>4478600</v>
+      </c>
+      <c r="S36" s="100">
+        <v>5.8869999999999996</v>
+      </c>
+      <c r="T36" s="110">
+        <v>887500</v>
+      </c>
+      <c r="U36" s="100">
+        <v>1.167</v>
+      </c>
+      <c r="V36" s="99">
+        <v>19100161</v>
+      </c>
+      <c r="W36" s="100">
+        <v>25.106000000000002</v>
+      </c>
+      <c r="X36" s="99">
+        <v>351000</v>
+      </c>
+      <c r="Y36" s="100">
+        <v>0.46100000000000002</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25">
+      <c r="A37" s="88">
+        <v>2011</v>
+      </c>
+      <c r="B37" s="89">
+        <v>79341867.266000003</v>
+      </c>
+      <c r="C37" s="90">
+        <v>100</v>
+      </c>
+      <c r="D37" s="91">
+        <v>6418389</v>
+      </c>
+      <c r="E37" s="103">
+        <v>8.09</v>
+      </c>
+      <c r="F37" s="92">
+        <v>18715683</v>
+      </c>
+      <c r="G37" s="93">
+        <v>23.588999999999999</v>
+      </c>
+      <c r="H37" s="92">
+        <v>2623224</v>
+      </c>
+      <c r="I37" s="93">
+        <v>3.306</v>
+      </c>
+      <c r="J37" s="92">
+        <v>1858660.2660000001</v>
+      </c>
+      <c r="K37" s="93">
+        <v>2.343</v>
+      </c>
+      <c r="L37" s="92">
+        <v>0</v>
+      </c>
+      <c r="M37" s="93">
+        <v>0</v>
+      </c>
+      <c r="N37" s="92">
+        <v>49725911</v>
+      </c>
+      <c r="O37" s="93">
+        <v>62.673000000000002</v>
+      </c>
+      <c r="P37" s="92">
+        <v>24205000</v>
+      </c>
+      <c r="Q37" s="106">
+        <v>30.507000000000001</v>
+      </c>
+      <c r="R37" s="92">
+        <v>4478600</v>
+      </c>
+      <c r="S37" s="93">
+        <v>5.6449999999999996</v>
+      </c>
+      <c r="T37" s="109">
+        <v>887500</v>
+      </c>
+      <c r="U37" s="93">
+        <v>1.119</v>
+      </c>
+      <c r="V37" s="92">
+        <v>19799361</v>
+      </c>
+      <c r="W37" s="93">
+        <v>24.954000000000001</v>
+      </c>
+      <c r="X37" s="92">
+        <v>355450</v>
+      </c>
+      <c r="Y37" s="93">
+        <v>0.44800000000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25">
+      <c r="A38" s="88">
+        <v>2012</v>
+      </c>
+      <c r="B38" s="89">
+        <v>81805576</v>
+      </c>
+      <c r="C38" s="90">
+        <v>100</v>
+      </c>
+      <c r="D38" s="91">
+        <v>6446030</v>
+      </c>
+      <c r="E38" s="90">
+        <v>7.88</v>
+      </c>
+      <c r="F38" s="92">
+        <v>20715683</v>
+      </c>
+      <c r="G38" s="93">
+        <v>25.323</v>
+      </c>
+      <c r="H38" s="92">
+        <v>2768012</v>
+      </c>
+      <c r="I38" s="93">
+        <v>3.3839999999999999</v>
+      </c>
+      <c r="J38" s="92">
+        <v>2338050</v>
+      </c>
+      <c r="K38" s="93">
+        <v>2.8580000000000001</v>
+      </c>
+      <c r="L38" s="92">
+        <v>0</v>
+      </c>
+      <c r="M38" s="93">
+        <v>0</v>
+      </c>
+      <c r="N38" s="92">
+        <v>49537801</v>
+      </c>
+      <c r="O38" s="93">
+        <v>60.555999999999997</v>
+      </c>
+      <c r="P38" s="92">
+        <v>24533600</v>
+      </c>
+      <c r="Q38" s="93">
+        <v>29.99</v>
+      </c>
+      <c r="R38" s="92">
+        <v>3950000</v>
+      </c>
+      <c r="S38" s="93">
+        <v>4.8289999999999997</v>
+      </c>
+      <c r="T38" s="109">
+        <v>887500</v>
+      </c>
+      <c r="U38" s="93">
+        <v>1.085</v>
+      </c>
+      <c r="V38" s="92">
+        <v>19799361</v>
+      </c>
+      <c r="W38" s="93">
+        <v>24.202999999999999</v>
+      </c>
+      <c r="X38" s="92">
+        <v>367340</v>
+      </c>
+      <c r="Y38" s="93">
+        <v>0.44900000000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25">
+      <c r="A39" s="111">
+        <v>2013</v>
+      </c>
+      <c r="B39" s="89">
+        <v>86968936.821999997</v>
+      </c>
+      <c r="C39" s="90">
+        <v>100</v>
+      </c>
+      <c r="D39" s="91">
+        <v>6454462</v>
+      </c>
+      <c r="E39" s="90">
+        <v>7.4219999999999997</v>
+      </c>
+      <c r="F39" s="92">
+        <v>20715683</v>
+      </c>
+      <c r="G39" s="93">
+        <v>23.82</v>
+      </c>
+      <c r="H39" s="92">
+        <v>3106068</v>
+      </c>
+      <c r="I39" s="93">
+        <v>3.5710000000000002</v>
+      </c>
+      <c r="J39" s="92">
+        <v>3518701.8220000002</v>
+      </c>
+      <c r="K39" s="93">
+        <v>4.0460000000000003</v>
+      </c>
+      <c r="L39" s="92">
+        <v>0</v>
+      </c>
+      <c r="M39" s="93">
+        <v>0</v>
+      </c>
+      <c r="N39" s="92">
+        <v>53174022</v>
+      </c>
+      <c r="O39" s="93">
+        <v>61.140999999999998</v>
+      </c>
+      <c r="P39" s="92">
+        <v>24533600</v>
+      </c>
+      <c r="Q39" s="93">
+        <v>28.21</v>
+      </c>
+      <c r="R39" s="92">
+        <v>3950000</v>
+      </c>
+      <c r="S39" s="93">
+        <v>4.5419999999999998</v>
+      </c>
+      <c r="T39" s="109">
+        <v>887500</v>
+      </c>
+      <c r="U39" s="93">
+        <v>1.02</v>
+      </c>
+      <c r="V39" s="92">
+        <v>23473232</v>
+      </c>
+      <c r="W39" s="93">
+        <v>26.99</v>
+      </c>
+      <c r="X39" s="92">
+        <v>329690</v>
+      </c>
+      <c r="Y39" s="93">
+        <v>0.379</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25">
+      <c r="A40" s="111">
+        <v>2014</v>
+      </c>
+      <c r="B40" s="91">
+        <v>93215755</v>
+      </c>
+      <c r="C40" s="90">
+        <v>100</v>
+      </c>
+      <c r="D40" s="91">
+        <v>6466936</v>
+      </c>
+      <c r="E40" s="90">
+        <v>6.9379999999999997</v>
+      </c>
+      <c r="F40" s="92">
+        <v>20715683</v>
+      </c>
+      <c r="G40" s="93">
+        <v>22.222999999999999</v>
+      </c>
+      <c r="H40" s="92">
+        <v>4322509</v>
+      </c>
+      <c r="I40" s="93">
+        <v>4.6369999999999996</v>
+      </c>
+      <c r="J40" s="92">
+        <v>4473945</v>
+      </c>
+      <c r="K40" s="93">
+        <v>4.8</v>
+      </c>
+      <c r="L40" s="92">
+        <v>0</v>
+      </c>
+      <c r="M40" s="93">
+        <v>0</v>
+      </c>
+      <c r="N40" s="92">
+        <v>57236681</v>
+      </c>
+      <c r="O40" s="93">
+        <v>61.402000000000001</v>
+      </c>
+      <c r="P40" s="92">
+        <v>26273600</v>
+      </c>
+      <c r="Q40" s="93">
+        <v>28.186</v>
+      </c>
+      <c r="R40" s="92">
+        <v>2950000</v>
+      </c>
+      <c r="S40" s="93">
+        <v>3.165</v>
+      </c>
+      <c r="T40" s="109">
+        <v>387500</v>
+      </c>
+      <c r="U40" s="93">
+        <v>0.41599999999999998</v>
+      </c>
+      <c r="V40" s="92">
+        <v>27295891</v>
+      </c>
+      <c r="W40" s="93">
+        <v>29.282</v>
+      </c>
+      <c r="X40" s="92">
+        <v>329690</v>
+      </c>
+      <c r="Y40" s="93">
+        <v>0.35399999999999998</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25">
+      <c r="A41" s="111">
+        <v>2015</v>
+      </c>
+      <c r="B41" s="91">
+        <v>97648761.430000007</v>
+      </c>
+      <c r="C41" s="90">
+        <v>100</v>
+      </c>
+      <c r="D41" s="91">
+        <v>6470709</v>
+      </c>
+      <c r="E41" s="97">
+        <v>6.6269999999999998</v>
+      </c>
+      <c r="F41" s="92">
+        <v>21715683</v>
+      </c>
+      <c r="G41" s="93">
+        <v>22.239000000000001</v>
+      </c>
+      <c r="H41" s="92">
+        <v>5360020</v>
+      </c>
+      <c r="I41" s="93">
+        <v>5.4889999999999999</v>
+      </c>
+      <c r="J41" s="92">
+        <v>5649367.4299999997</v>
+      </c>
+      <c r="K41" s="93">
+        <v>5.7850000000000001</v>
+      </c>
+      <c r="L41" s="92">
+        <v>0</v>
+      </c>
+      <c r="M41" s="93">
+        <v>0</v>
+      </c>
+      <c r="N41" s="92">
+        <v>58452981</v>
+      </c>
+      <c r="O41" s="93">
+        <v>59.86</v>
+      </c>
+      <c r="P41" s="92">
+        <v>26273600</v>
+      </c>
+      <c r="Q41" s="100">
+        <v>26.905999999999999</v>
+      </c>
+      <c r="R41" s="92">
+        <v>2950000</v>
+      </c>
+      <c r="S41" s="100">
+        <v>3.0209999999999999</v>
+      </c>
+      <c r="T41" s="109">
+        <v>387500</v>
+      </c>
+      <c r="U41" s="100">
+        <v>0.39700000000000002</v>
+      </c>
+      <c r="V41" s="92">
+        <v>28512191</v>
+      </c>
+      <c r="W41" s="100">
+        <v>29.199000000000002</v>
+      </c>
+      <c r="X41" s="92">
+        <v>329690</v>
+      </c>
+      <c r="Y41" s="93">
+        <v>0.33800000000000002</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25">
+      <c r="A42" s="112">
+        <v>2016</v>
+      </c>
+      <c r="B42" s="104">
+        <v>105865557.095</v>
+      </c>
+      <c r="C42" s="103">
+        <v>100</v>
+      </c>
+      <c r="D42" s="104">
+        <v>6485211</v>
+      </c>
+      <c r="E42" s="103">
+        <v>6.1260000000000003</v>
+      </c>
+      <c r="F42" s="105">
+        <v>23115683</v>
+      </c>
+      <c r="G42" s="106">
+        <v>21.835000000000001</v>
+      </c>
+      <c r="H42" s="105">
+        <v>6200144</v>
+      </c>
+      <c r="I42" s="106">
+        <v>5.8570000000000002</v>
+      </c>
+      <c r="J42" s="105">
+        <v>7477088.0949999997</v>
+      </c>
+      <c r="K42" s="106">
+        <v>7.0629999999999997</v>
+      </c>
+      <c r="L42" s="105">
+        <v>0</v>
+      </c>
+      <c r="M42" s="106">
+        <v>0</v>
+      </c>
+      <c r="N42" s="105">
+        <v>62587431</v>
+      </c>
+      <c r="O42" s="106">
+        <v>59.12</v>
+      </c>
+      <c r="P42" s="105">
+        <v>30545800</v>
+      </c>
+      <c r="Q42" s="106">
+        <v>28.853000000000002</v>
+      </c>
+      <c r="R42" s="105">
+        <v>2950000</v>
+      </c>
+      <c r="S42" s="93">
+        <v>2.7869999999999999</v>
+      </c>
+      <c r="T42" s="107">
+        <v>250000</v>
+      </c>
+      <c r="U42" s="106">
+        <v>0.23599999999999999</v>
+      </c>
+      <c r="V42" s="105">
+        <v>28512191</v>
+      </c>
+      <c r="W42" s="93">
+        <v>26.931999999999999</v>
+      </c>
+      <c r="X42" s="105">
+        <v>329440</v>
+      </c>
+      <c r="Y42" s="106">
+        <v>0.311</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25">
+      <c r="A43" s="111">
+        <v>2017</v>
+      </c>
+      <c r="B43" s="91">
+        <v>116907641</v>
+      </c>
+      <c r="C43" s="90">
+        <v>100</v>
+      </c>
+      <c r="D43" s="91">
+        <v>6489456</v>
+      </c>
+      <c r="E43" s="90">
+        <v>5.5510000000000002</v>
+      </c>
+      <c r="F43" s="92">
+        <v>22528683</v>
+      </c>
+      <c r="G43" s="93">
+        <v>19.27</v>
+      </c>
+      <c r="H43" s="92">
+        <v>7682304</v>
+      </c>
+      <c r="I43" s="93">
+        <v>6.5709999999999997</v>
+      </c>
+      <c r="J43" s="92">
+        <v>9186923</v>
+      </c>
+      <c r="K43" s="93">
+        <v>7.8579999999999997</v>
+      </c>
+      <c r="L43" s="92">
+        <v>0</v>
+      </c>
+      <c r="M43" s="93">
+        <v>0</v>
+      </c>
+      <c r="N43" s="92">
+        <v>71020275</v>
+      </c>
+      <c r="O43" s="93">
+        <v>60.749000000000002</v>
+      </c>
+      <c r="P43" s="92">
+        <v>35314578</v>
+      </c>
+      <c r="Q43" s="93">
+        <v>30.207000000000001</v>
+      </c>
+      <c r="R43" s="92">
+        <v>2950000</v>
+      </c>
+      <c r="S43" s="93">
+        <v>2.5230000000000001</v>
+      </c>
+      <c r="T43" s="109">
+        <v>0</v>
+      </c>
+      <c r="U43" s="93">
+        <v>0</v>
+      </c>
+      <c r="V43" s="92">
+        <v>32416227</v>
+      </c>
+      <c r="W43" s="93">
+        <v>27.728000000000002</v>
+      </c>
+      <c r="X43" s="92">
+        <v>339470</v>
+      </c>
+      <c r="Y43" s="93">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25">
+      <c r="A44" s="111">
+        <v>2018</v>
+      </c>
+      <c r="B44" s="91">
+        <v>119091659.508</v>
+      </c>
+      <c r="C44" s="90">
+        <v>100</v>
+      </c>
+      <c r="D44" s="91">
+        <v>6490410.4000000004</v>
+      </c>
+      <c r="E44" s="90">
+        <v>5.45</v>
+      </c>
+      <c r="F44" s="92">
+        <v>21850000</v>
+      </c>
+      <c r="G44" s="93">
+        <v>18.347000000000001</v>
+      </c>
+      <c r="H44" s="92">
+        <v>9207684</v>
+      </c>
+      <c r="I44" s="93">
+        <v>7.7320000000000002</v>
+      </c>
+      <c r="J44" s="92">
+        <v>11622809.107999999</v>
+      </c>
+      <c r="K44" s="93">
+        <v>9.76</v>
+      </c>
+      <c r="L44" s="92">
+        <v>0</v>
+      </c>
+      <c r="M44" s="93">
+        <v>0</v>
+      </c>
+      <c r="N44" s="92">
+        <v>69920756</v>
+      </c>
+      <c r="O44" s="93">
+        <v>58.712000000000003</v>
+      </c>
+      <c r="P44" s="92">
+        <v>35407613</v>
+      </c>
+      <c r="Q44" s="93">
+        <v>29.731000000000002</v>
+      </c>
+      <c r="R44" s="92">
+        <v>2950000</v>
+      </c>
+      <c r="S44" s="93">
+        <v>2.4769999999999999</v>
+      </c>
+      <c r="T44" s="109">
+        <v>0</v>
+      </c>
+      <c r="U44" s="93">
+        <v>0</v>
+      </c>
+      <c r="V44" s="92">
+        <v>31223673</v>
+      </c>
+      <c r="W44" s="93">
+        <v>26.218</v>
+      </c>
+      <c r="X44" s="92">
+        <v>339470</v>
+      </c>
+      <c r="Y44" s="93">
+        <v>0.28499999999999998</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25">
+      <c r="A45" s="111">
+        <v>2019</v>
+      </c>
+      <c r="B45" s="91">
+        <v>125337668.536</v>
+      </c>
+      <c r="C45" s="90">
+        <v>100</v>
+      </c>
+      <c r="D45" s="91">
+        <v>6508103.4000000004</v>
+      </c>
+      <c r="E45" s="90">
+        <v>5.1920000000000002</v>
+      </c>
+      <c r="F45" s="92">
+        <v>23250000</v>
+      </c>
+      <c r="G45" s="93">
+        <v>18.55</v>
+      </c>
+      <c r="H45" s="92">
+        <v>9190984</v>
+      </c>
+      <c r="I45" s="93">
+        <v>7.3330000000000002</v>
+      </c>
+      <c r="J45" s="92">
+        <v>14249553.136</v>
+      </c>
+      <c r="K45" s="93">
+        <v>11.369</v>
+      </c>
+      <c r="L45" s="92">
+        <v>851790</v>
+      </c>
+      <c r="M45" s="93">
+        <v>0.68</v>
+      </c>
+      <c r="N45" s="92">
+        <v>71287238</v>
+      </c>
+      <c r="O45" s="93">
+        <v>56.875999999999998</v>
+      </c>
+      <c r="P45" s="92">
+        <v>35500658</v>
+      </c>
+      <c r="Q45" s="93">
+        <v>28.324000000000002</v>
+      </c>
+      <c r="R45" s="92">
+        <v>2600000</v>
+      </c>
+      <c r="S45" s="93">
+        <v>2.0739999999999998</v>
+      </c>
+      <c r="T45" s="109">
+        <v>0</v>
+      </c>
+      <c r="U45" s="93">
+        <v>0</v>
+      </c>
+      <c r="V45" s="92">
+        <v>32845963</v>
+      </c>
+      <c r="W45" s="93">
+        <v>26.206</v>
+      </c>
+      <c r="X45" s="92">
+        <v>340617</v>
+      </c>
+      <c r="Y45" s="93">
+        <v>0.27200000000000002</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25">
+      <c r="A46" s="111">
+        <v>2020</v>
+      </c>
+      <c r="B46" s="91">
+        <v>129191273.47</v>
+      </c>
+      <c r="C46" s="90">
+        <v>100</v>
+      </c>
+      <c r="D46" s="91">
+        <v>6505768.4000000004</v>
+      </c>
+      <c r="E46" s="97">
+        <v>5.0359999999999996</v>
+      </c>
+      <c r="F46" s="92">
+        <v>23250000</v>
+      </c>
+      <c r="G46" s="93">
+        <v>17.997</v>
+      </c>
+      <c r="H46" s="92">
+        <v>9190984</v>
+      </c>
+      <c r="I46" s="93">
+        <v>7.1139999999999999</v>
+      </c>
+      <c r="J46" s="92">
+        <v>18739127.07</v>
+      </c>
+      <c r="K46" s="93">
+        <v>14.505000000000001</v>
+      </c>
+      <c r="L46" s="92">
+        <v>366204</v>
+      </c>
+      <c r="M46" s="100">
+        <v>0.28299999999999997</v>
+      </c>
+      <c r="N46" s="92">
+        <v>71139190</v>
+      </c>
+      <c r="O46" s="93">
+        <v>55.064999999999998</v>
+      </c>
+      <c r="P46" s="92">
+        <v>35350658</v>
+      </c>
+      <c r="Q46" s="100">
+        <v>27.363</v>
+      </c>
+      <c r="R46" s="92">
+        <v>1200000</v>
+      </c>
+      <c r="S46" s="100">
+        <v>0.92900000000000005</v>
+      </c>
+      <c r="T46" s="109">
+        <v>1400000</v>
+      </c>
+      <c r="U46" s="93">
+        <v>1.0840000000000001</v>
+      </c>
+      <c r="V46" s="92">
+        <v>33012852</v>
+      </c>
+      <c r="W46" s="100">
+        <v>25.553000000000001</v>
+      </c>
+      <c r="X46" s="92">
+        <v>175680</v>
+      </c>
+      <c r="Y46" s="113">
+        <v>0.13600000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25">
+      <c r="A47" s="112">
+        <v>2021</v>
+      </c>
+      <c r="B47" s="104">
+        <v>134019775.42299999</v>
+      </c>
+      <c r="C47" s="103">
+        <v>100</v>
+      </c>
+      <c r="D47" s="104">
+        <v>6541335.4000000004</v>
+      </c>
+      <c r="E47" s="103">
+        <v>4.8810000000000002</v>
+      </c>
+      <c r="F47" s="105">
+        <v>23250000</v>
+      </c>
+      <c r="G47" s="106">
+        <v>17.347999999999999</v>
+      </c>
+      <c r="H47" s="105">
+        <v>9229174</v>
+      </c>
+      <c r="I47" s="106">
+        <v>6.8860000000000001</v>
+      </c>
+      <c r="J47" s="105">
+        <v>23014162.022999998</v>
+      </c>
+      <c r="K47" s="106">
+        <v>17.172000000000001</v>
+      </c>
+      <c r="L47" s="105">
+        <v>366784</v>
+      </c>
+      <c r="M47" s="106">
+        <v>0.27400000000000002</v>
+      </c>
+      <c r="N47" s="105">
+        <v>71618320</v>
+      </c>
+      <c r="O47" s="106">
+        <v>53.439</v>
+      </c>
+      <c r="P47" s="105">
+        <v>35828658</v>
+      </c>
+      <c r="Q47" s="106">
+        <v>26.734000000000002</v>
+      </c>
+      <c r="R47" s="105">
+        <v>1200000</v>
+      </c>
+      <c r="S47" s="106">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="T47" s="107">
+        <v>1400000</v>
+      </c>
+      <c r="U47" s="106">
+        <v>1.0449999999999999</v>
+      </c>
+      <c r="V47" s="105">
+        <v>33012852</v>
+      </c>
+      <c r="W47" s="106">
+        <v>24.632999999999999</v>
+      </c>
+      <c r="X47" s="105">
+        <v>176810</v>
+      </c>
+      <c r="Y47" s="106">
+        <v>0.13200000000000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25">
+      <c r="A48" s="111">
+        <v>2022</v>
+      </c>
+      <c r="B48" s="91">
+        <v>138194754.61000001</v>
+      </c>
+      <c r="C48" s="90">
+        <v>100</v>
+      </c>
+      <c r="D48" s="91">
+        <v>6513123.4000000004</v>
+      </c>
+      <c r="E48" s="90">
+        <v>4.7130000000000001</v>
+      </c>
+      <c r="F48" s="92">
+        <v>24650000</v>
+      </c>
+      <c r="G48" s="93">
+        <v>17.837</v>
+      </c>
+      <c r="H48" s="92">
+        <v>8919174</v>
+      </c>
+      <c r="I48" s="93">
+        <v>6.4539999999999997</v>
+      </c>
+      <c r="J48" s="92">
+        <v>26325542.210000001</v>
+      </c>
+      <c r="K48" s="93">
+        <v>19.05</v>
+      </c>
+      <c r="L48" s="92">
+        <v>368595</v>
+      </c>
+      <c r="M48" s="93">
+        <v>0.26700000000000002</v>
+      </c>
+      <c r="N48" s="92">
+        <v>71418320</v>
+      </c>
+      <c r="O48" s="93">
+        <v>51.679000000000002</v>
+      </c>
+      <c r="P48" s="92">
+        <v>36868658</v>
+      </c>
+      <c r="Q48" s="93">
+        <v>26.678999999999998</v>
+      </c>
+      <c r="R48" s="92">
+        <v>0</v>
+      </c>
+      <c r="S48" s="93">
+        <v>0</v>
+      </c>
+      <c r="T48" s="109">
+        <v>1400000</v>
+      </c>
+      <c r="U48" s="93">
+        <v>1.0129999999999999</v>
+      </c>
+      <c r="V48" s="92">
+        <v>33012852</v>
+      </c>
+      <c r="W48" s="93">
+        <v>23.888999999999999</v>
+      </c>
+      <c r="X48" s="92">
+        <v>136810</v>
+      </c>
+      <c r="Y48" s="93">
+        <v>9.9000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" ht="15.75" thickBot="1">
+      <c r="A49" s="114">
+        <v>2023</v>
+      </c>
+      <c r="B49" s="115">
+        <v>143380908.007</v>
+      </c>
+      <c r="C49" s="116">
+        <v>100</v>
+      </c>
+      <c r="D49" s="115">
+        <v>6516996.4000000004</v>
+      </c>
+      <c r="E49" s="116">
+        <v>4.5449999999999999</v>
+      </c>
+      <c r="F49" s="117">
+        <v>24650000</v>
+      </c>
+      <c r="G49" s="118">
+        <v>17.192</v>
+      </c>
+      <c r="H49" s="117">
+        <v>9821006</v>
+      </c>
+      <c r="I49" s="118">
+        <v>6.85</v>
+      </c>
+      <c r="J49" s="117">
+        <v>29578510.607000001</v>
+      </c>
+      <c r="K49" s="118">
+        <v>20.629000000000001</v>
+      </c>
+      <c r="L49" s="117">
+        <v>370935</v>
+      </c>
+      <c r="M49" s="118">
+        <v>0.25900000000000001</v>
+      </c>
+      <c r="N49" s="117">
+        <v>72443460</v>
+      </c>
+      <c r="O49" s="118">
+        <v>50.524999999999999</v>
+      </c>
+      <c r="P49" s="117">
+        <v>36868658</v>
+      </c>
+      <c r="Q49" s="118">
+        <v>25.713999999999999</v>
+      </c>
+      <c r="R49" s="117">
+        <v>0</v>
+      </c>
+      <c r="S49" s="118">
+        <v>0</v>
+      </c>
+      <c r="T49" s="119">
+        <v>1400000</v>
+      </c>
+      <c r="U49" s="118">
+        <v>0.97599999999999998</v>
+      </c>
+      <c r="V49" s="117">
+        <v>34038252</v>
+      </c>
+      <c r="W49" s="118">
+        <v>23.74</v>
+      </c>
+      <c r="X49" s="117">
+        <v>136550</v>
+      </c>
+      <c r="Y49" s="118">
+        <v>9.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25">
+      <c r="A50" s="52" t="s">
+        <v>422</v>
+      </c>
+      <c r="B50" s="91"/>
+      <c r="C50" s="90"/>
+      <c r="D50" s="120"/>
+      <c r="E50" s="121"/>
+      <c r="F50" s="120"/>
+      <c r="G50" s="121"/>
+      <c r="H50" s="120"/>
+      <c r="I50" s="121"/>
+      <c r="J50" s="120"/>
+      <c r="K50" s="121"/>
+      <c r="L50" s="121"/>
+      <c r="M50" s="121"/>
+      <c r="N50" s="52" t="s">
+        <v>423</v>
+      </c>
+      <c r="O50" s="52"/>
+      <c r="P50" s="52"/>
+      <c r="Q50" s="122"/>
+      <c r="R50" s="123"/>
+      <c r="S50" s="124"/>
+      <c r="T50" s="123"/>
+      <c r="U50" s="124"/>
+      <c r="V50" s="123"/>
+      <c r="W50" s="124"/>
+      <c r="X50" s="123"/>
+      <c r="Y50" s="124"/>
+    </row>
+    <row r="51" spans="1:25">
+      <c r="A51" s="51" t="s">
+        <v>424</v>
+      </c>
+      <c r="B51" s="120"/>
+      <c r="C51" s="125"/>
+      <c r="D51" s="52"/>
+      <c r="E51" s="53"/>
+      <c r="F51" s="52"/>
+      <c r="G51" s="53"/>
+      <c r="H51" s="52"/>
+      <c r="I51" s="53"/>
+      <c r="J51" s="52"/>
+      <c r="K51" s="53"/>
+      <c r="L51" s="53"/>
+      <c r="M51" s="53"/>
+      <c r="N51" s="52" t="s">
+        <v>425</v>
+      </c>
+      <c r="O51" s="52"/>
+      <c r="P51" s="52"/>
+      <c r="Q51" s="122"/>
+      <c r="R51" s="126"/>
+      <c r="S51" s="122"/>
+      <c r="T51" s="126"/>
+      <c r="U51" s="122"/>
+      <c r="V51" s="126"/>
+      <c r="W51" s="122"/>
+      <c r="X51" s="126"/>
+      <c r="Y51" s="122"/>
+    </row>
+    <row r="52" spans="1:25">
+      <c r="A52" s="52" t="s">
+        <v>426</v>
+      </c>
+      <c r="B52" s="52"/>
+      <c r="C52" s="52"/>
+      <c r="D52" s="52"/>
+      <c r="E52" s="53"/>
+      <c r="F52" s="127"/>
+      <c r="G52" s="53"/>
+      <c r="H52" s="52"/>
+      <c r="I52" s="53"/>
+      <c r="J52" s="52"/>
+      <c r="K52" s="53"/>
+      <c r="L52" s="53"/>
+      <c r="M52" s="53"/>
+      <c r="N52" s="51" t="s">
+        <v>427</v>
+      </c>
+      <c r="O52" s="51"/>
+      <c r="P52" s="51"/>
+      <c r="Q52" s="122"/>
+      <c r="R52" s="126"/>
+      <c r="S52" s="122"/>
+      <c r="T52" s="126"/>
+      <c r="U52" s="122"/>
+      <c r="V52" s="126"/>
+      <c r="W52" s="122"/>
+      <c r="X52" s="126"/>
+      <c r="Y52" s="122"/>
+    </row>
+    <row r="53" spans="1:25">
+      <c r="A53" s="128" t="s">
+        <v>428</v>
+      </c>
+      <c r="B53" s="128"/>
+      <c r="C53" s="128"/>
+      <c r="D53" s="127"/>
+      <c r="E53" s="53"/>
+      <c r="F53" s="52"/>
+      <c r="G53" s="53"/>
+      <c r="H53" s="52"/>
+      <c r="I53" s="53"/>
+      <c r="J53" s="52"/>
+      <c r="K53" s="53"/>
+      <c r="L53" s="53"/>
+      <c r="M53" s="53"/>
+      <c r="N53" s="129" t="s">
+        <v>429</v>
+      </c>
+      <c r="O53" s="129"/>
+      <c r="P53" s="129"/>
+      <c r="Q53" s="54"/>
+      <c r="R53" s="126"/>
+      <c r="S53" s="122"/>
+      <c r="T53" s="126"/>
+      <c r="U53" s="122"/>
+      <c r="V53" s="126"/>
+      <c r="W53" s="122"/>
+      <c r="X53" s="126"/>
+      <c r="Y53" s="122"/>
+    </row>
+  </sheetData>
+  <mergeCells count="32">
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="V5:W5"/>
+    <mergeCell ref="X5:Y5"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
@@ -13281,11 +17788,12 @@
         <v>0</v>
       </c>
       <c r="E5" s="16">
-        <f>'Nuclear Additions'!D19</f>
-        <v>1429</v>
+        <f>('KOSIS Capacities'!F48-'KOSIS Capacities'!F47)/1000</f>
+        <v>1400</v>
       </c>
       <c r="F5">
-        <v>1400</v>
+        <f>('KOSIS Capacities'!F49-'KOSIS Capacities'!F48)/1000</f>
+        <v>0</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -15407,6 +19915,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
     <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
@@ -15550,22 +20073,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B79B8AEF-803A-4C5A-B04E-B80AE175902F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B24FF82-77E2-4C47-88CE-8E1D1040FA1D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43ED1489-0F0F-460E-8DB0-F645CB7D0188}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -15581,21 +20106,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B24FF82-77E2-4C47-88CE-8E1D1040FA1D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B79B8AEF-803A-4C5A-B04E-B80AE175902F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/InputData/elec/BPMCCS/BAU Pol Mandated Cap Const Sched.xlsx
+++ b/InputData/elec/BPMCCS/BAU Pol Mandated Cap Const Sched.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energyinnovation.sharepoint.com/sites/ExternalSharing-PolicyExternal2/Shared Documents/Policy - Modeling and Analysis External/South Korea EPS/New Files_June/20260703/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\South Korea\Models\eps-southkorea\InputData\elec\BPMCCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{D9894EA2-03E5-4719-9F58-634C7E9E19D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD037AE0-8F1C-4049-9B2A-80240D17F018}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF249023-3B75-4723-847B-C8191E189920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19305" yWindow="-4650" windowWidth="19410" windowHeight="20985" tabRatio="846" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6825" yWindow="4485" windowWidth="17280" windowHeight="10005" tabRatio="846" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="6" r:id="rId1"/>
@@ -37,8 +37,32 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Robbie Orvis</author>
+  </authors>
+  <commentList>
+    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{58CC3172-DDCD-47E6-B751-190C75303F0B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>2026-09-04: 124.044 MW moved here from BHRaSYC-StartYearCapacities Vintage2021 (source sheet shows 0 for 2021); start-year vintages must end in 2020.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="221">
   <si>
     <t>연도</t>
   </si>
@@ -780,6 +804,15 @@
   <si>
     <t>피크기여도</t>
   </si>
+  <si>
+    <t>2026-09-04 start-year convention (matches eps-us, INITIAL TIME 2025 / vintages end 2024 / BPMCCS 2025 = first-year builds / BBNPPTY bans all sources through the last historical year): 2021 (first model year) builds stay in this file (solar 3,956 MW, onshore 64 MW, NGCC 482 MW, biomass 124 MW moved from BHRaSYC); the matching Vintage2021 entries were removed from BHRaSYC-StartYearCapacities so nothing is counted twice. An earlier same-day edit that zeroed the 2021 column here was reverted.</t>
+  </si>
+  <si>
+    <t>2026-09-04: H29 set to 0 - raw I6 (1,814.85 MW) is the cumulative conventional hydro fleet as of 2025 (KEEI 1.82 GW), not a 2025 addition; no new conventional hydro was built in 2025.</t>
+  </si>
+  <si>
+    <t>2026-09-04: hydro 2025 mandated build (1,815 MW) removed - the source cell was the cumulative conventional hydro fleet total, not an addition. EPS hydro capacity had jumped 2.1 -&gt; 3.9 GW in 2025 (actual fleet ~1.8 GW).</t>
+  </si>
 </sst>
 </file>
 
@@ -792,7 +825,7 @@
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -951,6 +984,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="17">
@@ -1576,6 +1616,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1604,9 +1647,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1985,9 +2025,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{412B3F4C-C052-4E1C-AAAD-A68F7E4EFB62}">
   <dimension ref="A1:B36"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="67.08984375" customWidth="1"/>
+    <col min="2" max="2" width="67.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -2086,34 +2126,41 @@
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="1:1" ht="16">
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
       <c r="A27" s="2"/>
     </row>
-    <row r="28" spans="1:1" ht="16">
-      <c r="A28" s="1"/>
-    </row>
-    <row r="29" spans="1:1" ht="16">
+    <row r="28" spans="1:1">
+      <c r="A28" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
       <c r="A29" s="1"/>
     </row>
-    <row r="30" spans="1:1" ht="16">
+    <row r="30" spans="1:1">
       <c r="A30" s="1"/>
     </row>
-    <row r="31" spans="1:1" ht="16">
+    <row r="31" spans="1:1">
       <c r="A31" s="1"/>
     </row>
-    <row r="32" spans="1:1" ht="16">
+    <row r="32" spans="1:1">
       <c r="A32" s="1"/>
     </row>
-    <row r="33" spans="1:1" ht="16">
+    <row r="33" spans="1:1">
       <c r="A33" s="1"/>
     </row>
-    <row r="34" spans="1:1" ht="16">
+    <row r="34" spans="1:1">
       <c r="A34" s="1"/>
     </row>
-    <row r="35" spans="1:1" ht="16">
+    <row r="35" spans="1:1">
       <c r="A35" s="1"/>
     </row>
-    <row r="36" spans="1:1" ht="16">
+    <row r="36" spans="1:1">
       <c r="A36" s="1"/>
     </row>
   </sheetData>
@@ -2129,21 +2176,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA695273-2CF3-45E6-9FCD-C1FCC1300692}">
   <dimension ref="A1:R111"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.08984375" customWidth="1"/>
-    <col min="2" max="2" width="19.90625" customWidth="1"/>
-    <col min="3" max="3" width="18.08984375" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" customWidth="1"/>
-    <col min="5" max="5" width="9.453125" customWidth="1"/>
-    <col min="6" max="6" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.36328125" customWidth="1"/>
-    <col min="10" max="10" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" customWidth="1"/>
+    <col min="2" max="2" width="19.85546875" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" customWidth="1"/>
+    <col min="5" max="5" width="9.42578125" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="82" customFormat="1" ht="15.5">
+    <row r="1" spans="1:18" s="82" customFormat="1" ht="15.75">
       <c r="A1" s="81" t="s">
         <v>182</v>
       </c>
@@ -2209,7 +2256,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="29">
+    <row r="5" spans="1:18" ht="30">
       <c r="A5" s="65" t="s">
         <v>162</v>
       </c>
@@ -2416,7 +2463,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="16">
+    <row r="18" spans="1:13">
       <c r="A18" s="62" t="s">
         <v>143</v>
       </c>
@@ -2684,7 +2731,7 @@
     <row r="38" spans="1:13">
       <c r="A38" s="63"/>
     </row>
-    <row r="39" spans="1:13" s="83" customFormat="1" ht="15.5">
+    <row r="39" spans="1:13" s="83" customFormat="1" ht="15.75">
       <c r="A39" s="81" t="s">
         <v>193</v>
       </c>
@@ -3345,15 +3392,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{989B43D5-5E80-4E96-A0E6-9AF45A7C32E3}">
-  <dimension ref="A2:I48"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A2:J48"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="35.90625" customWidth="1"/>
-    <col min="2" max="2" width="9.7265625" customWidth="1"/>
-    <col min="11" max="11" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.85546875" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="20" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.36328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.90625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:9">
@@ -3589,7 +3636,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:10">
       <c r="A17" s="7" t="s">
         <v>1</v>
       </c>
@@ -3600,7 +3647,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:10">
       <c r="A18" s="7" t="s">
         <v>12</v>
       </c>
@@ -3611,7 +3658,7 @@
         <v>77203</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:10">
       <c r="A19" s="7" t="s">
         <v>104</v>
       </c>
@@ -3622,7 +3669,7 @@
         <v>40671</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:10">
       <c r="A20" s="7" t="s">
         <v>15</v>
       </c>
@@ -3633,12 +3680,12 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:10">
       <c r="A24" s="7" t="s">
         <v>16</v>
       </c>
@@ -3664,7 +3711,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:10">
       <c r="A25" s="27" t="s">
         <v>3</v>
       </c>
@@ -3699,7 +3746,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:10">
       <c r="A26" s="7" t="s">
         <v>17</v>
       </c>
@@ -3725,7 +3772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:10">
       <c r="A27" s="28" t="s">
         <v>4</v>
       </c>
@@ -3758,7 +3805,7 @@
         <v>1332.4</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:10">
       <c r="A28" s="29" t="s">
         <v>2</v>
       </c>
@@ -3791,7 +3838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:10">
       <c r="A29" s="30" t="s">
         <v>7</v>
       </c>
@@ -3820,11 +3867,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="7">
-        <f t="shared" si="3"/>
-        <v>1814.8493999999998</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
+        <v>0</v>
+      </c>
+      <c r="J29" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" s="31" t="s">
         <v>13</v>
       </c>
@@ -3857,7 +3906,7 @@
         <v>620.69999999999982</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:10">
       <c r="A31" s="33" t="s">
         <v>12</v>
       </c>
@@ -3890,7 +3939,7 @@
         <v>3814</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:10">
       <c r="A32" s="7" t="s">
         <v>18</v>
       </c>
@@ -4348,13 +4397,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA04839C-7E1C-4865-9899-1ED4BC37516C}">
   <dimension ref="A1:Q87"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.08984375" customWidth="1"/>
-    <col min="2" max="13" width="9.6328125" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" customWidth="1"/>
+    <col min="2" max="13" width="9.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="83" customFormat="1" ht="15.5">
+    <row r="1" spans="1:13" s="83" customFormat="1" ht="15.75">
       <c r="A1" s="81" t="s">
         <v>204</v>
       </c>
@@ -4393,7 +4442,7 @@
       <c r="L3" s="14"/>
       <c r="M3" s="14"/>
     </row>
-    <row r="4" spans="1:13" ht="15" thickBot="1">
+    <row r="4" spans="1:13" ht="15.75" thickBot="1">
       <c r="A4" s="14"/>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -4411,51 +4460,51 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="100" t="s">
+      <c r="A5" s="98" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="101" t="s">
         <v>108</v>
       </c>
-      <c r="C5" s="100"/>
-      <c r="D5" s="100"/>
-      <c r="E5" s="100"/>
-      <c r="F5" s="100"/>
-      <c r="G5" s="100"/>
-      <c r="H5" s="100"/>
-      <c r="I5" s="100"/>
-      <c r="J5" s="100"/>
-      <c r="K5" s="100"/>
-      <c r="L5" s="100" t="s">
+      <c r="C5" s="101"/>
+      <c r="D5" s="101"/>
+      <c r="E5" s="101"/>
+      <c r="F5" s="101"/>
+      <c r="G5" s="101"/>
+      <c r="H5" s="101"/>
+      <c r="I5" s="101"/>
+      <c r="J5" s="101"/>
+      <c r="K5" s="101"/>
+      <c r="L5" s="101" t="s">
         <v>109</v>
       </c>
-      <c r="M5" s="103" t="s">
+      <c r="M5" s="104" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="98"/>
-      <c r="B6" s="101" t="s">
+      <c r="A6" s="99"/>
+      <c r="B6" s="102" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="101"/>
-      <c r="D6" s="101"/>
-      <c r="E6" s="101"/>
-      <c r="F6" s="101"/>
-      <c r="G6" s="101"/>
-      <c r="H6" s="101" t="s">
+      <c r="C6" s="102"/>
+      <c r="D6" s="102"/>
+      <c r="E6" s="102"/>
+      <c r="F6" s="102"/>
+      <c r="G6" s="102"/>
+      <c r="H6" s="102" t="s">
         <v>5</v>
       </c>
-      <c r="I6" s="101"/>
-      <c r="J6" s="101"/>
-      <c r="K6" s="101" t="s">
+      <c r="I6" s="102"/>
+      <c r="J6" s="102"/>
+      <c r="K6" s="102" t="s">
         <v>110</v>
       </c>
-      <c r="L6" s="101"/>
-      <c r="M6" s="104"/>
-    </row>
-    <row r="7" spans="1:13" ht="15" thickBot="1">
-      <c r="A7" s="99"/>
+      <c r="L6" s="102"/>
+      <c r="M6" s="105"/>
+    </row>
+    <row r="7" spans="1:13" ht="15.75" thickBot="1">
+      <c r="A7" s="100"/>
       <c r="B7" s="24" t="s">
         <v>97</v>
       </c>
@@ -4483,12 +4532,12 @@
       <c r="J7" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="K7" s="102"/>
-      <c r="L7" s="102"/>
-      <c r="M7" s="105"/>
+      <c r="K7" s="103"/>
+      <c r="L7" s="103"/>
+      <c r="M7" s="106"/>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="106">
+      <c r="A8" s="107">
         <v>2024</v>
       </c>
       <c r="B8" s="22">
@@ -5592,8 +5641,8 @@
         <v>138068</v>
       </c>
     </row>
-    <row r="37" spans="1:17" ht="15" thickBot="1">
-      <c r="A37" s="107"/>
+    <row r="37" spans="1:17" ht="15.75" thickBot="1">
+      <c r="A37" s="97"/>
       <c r="B37" s="18">
         <v>11040</v>
       </c>
@@ -5644,13 +5693,13 @@
       <c r="L38" s="14"/>
       <c r="M38" s="14"/>
     </row>
-    <row r="42" spans="1:17" s="83" customFormat="1" ht="15.5">
+    <row r="42" spans="1:17" s="83" customFormat="1" ht="15.75">
       <c r="A42" s="81" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="43" spans="1:17" ht="15" thickBot="1"/>
-    <row r="44" spans="1:17" ht="15" thickBot="1">
+    <row r="43" spans="1:17" ht="15.75" thickBot="1"/>
+    <row r="44" spans="1:17" ht="15.75" thickBot="1">
       <c r="A44" s="46" t="s">
         <v>80</v>
       </c>
@@ -6029,7 +6078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:16" ht="15" thickBot="1">
+    <row r="50" spans="1:16" ht="15.75" thickBot="1">
       <c r="A50" s="40" t="s">
         <v>121</v>
       </c>
@@ -6090,17 +6139,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:16" s="83" customFormat="1" ht="15.5">
+    <row r="52" spans="1:16" s="83" customFormat="1" ht="15.75">
       <c r="A52" s="81" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="53" spans="1:16" ht="15" thickBot="1">
+    <row r="53" spans="1:16" ht="15.75" thickBot="1">
       <c r="A53" s="9" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="54" spans="1:16" ht="15" thickBot="1">
+    <row r="54" spans="1:16" ht="15.75" thickBot="1">
       <c r="A54" s="46" t="s">
         <v>80</v>
       </c>
@@ -6572,7 +6621,7 @@
       </c>
       <c r="P61" s="34"/>
     </row>
-    <row r="63" spans="1:16" ht="15.5">
+    <row r="63" spans="1:16" ht="15.75">
       <c r="A63" s="81" t="s">
         <v>205</v>
       </c>
@@ -6591,8 +6640,8 @@
       <c r="N63" s="81"/>
       <c r="O63" s="81"/>
     </row>
-    <row r="64" spans="1:16" ht="15" thickBot="1"/>
-    <row r="65" spans="1:15" ht="15" thickBot="1">
+    <row r="64" spans="1:16" ht="15.75" thickBot="1"/>
+    <row r="65" spans="1:15" ht="15.75" thickBot="1">
       <c r="A65" s="46" t="s">
         <v>80</v>
       </c>
@@ -7232,8 +7281,8 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="83" spans="1:15" ht="15" thickBot="1"/>
-    <row r="84" spans="1:15" ht="15" thickBot="1">
+    <row r="83" spans="1:15" ht="15.75" thickBot="1"/>
+    <row r="84" spans="1:15" ht="15.75" thickBot="1">
       <c r="A84" s="46" t="s">
         <v>80</v>
       </c>
@@ -7456,15 +7505,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="B5:K5"/>
@@ -7478,6 +7518,15 @@
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7488,18 +7537,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F0FC3DE-FB57-4949-8ACD-A608751B1C98}">
   <dimension ref="A2:AN48"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.7265625" customWidth="1"/>
-    <col min="2" max="2" width="11.90625" customWidth="1"/>
-    <col min="17" max="17" width="10.26953125" customWidth="1"/>
-    <col min="19" max="19" width="22.26953125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.08984375" customWidth="1"/>
-    <col min="21" max="21" width="6.6328125" customWidth="1"/>
+    <col min="1" max="1" width="31.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" customWidth="1"/>
+    <col min="17" max="17" width="10.28515625" customWidth="1"/>
+    <col min="19" max="19" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.140625" customWidth="1"/>
+    <col min="21" max="21" width="6.5703125" customWidth="1"/>
     <col min="22" max="22" width="18" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="20.26953125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="20.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:26">
@@ -7890,7 +7939,7 @@
       <c r="Y13" s="9"/>
       <c r="Z13" s="9"/>
     </row>
-    <row r="14" spans="1:26" ht="15" thickBot="1">
+    <row r="14" spans="1:26" ht="15.75" thickBot="1">
       <c r="R14" s="9"/>
       <c r="S14" s="9"/>
       <c r="T14" s="9"/>
@@ -7901,7 +7950,7 @@
       <c r="Y14" s="9"/>
       <c r="Z14" s="9"/>
     </row>
-    <row r="15" spans="1:26" ht="15" thickBot="1">
+    <row r="15" spans="1:26" ht="15.75" thickBot="1">
       <c r="A15" s="46" t="s">
         <v>80</v>
       </c>
@@ -8329,7 +8378,7 @@
       </c>
       <c r="AN20" s="9"/>
     </row>
-    <row r="21" spans="1:40" ht="15" thickBot="1">
+    <row r="21" spans="1:40" ht="15.75" thickBot="1">
       <c r="A21" s="56" t="s">
         <v>121</v>
       </c>
@@ -8700,7 +8749,7 @@
       </c>
       <c r="B29" s="76">
         <f>'설비현황_19~25'!H29</f>
-        <v>1814.8493999999998</v>
+        <v>0</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -9739,17 +9788,17 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E64C2F56-4C18-49EB-8736-B3A38598D87E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E64C2F56-4C18-49EB-8736-B3A38598D87E}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AG25"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.26953125" customWidth="1"/>
-    <col min="3" max="3" width="8.26953125" customWidth="1"/>
-    <col min="10" max="10" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" customWidth="1"/>
+    <col min="3" max="3" width="8.28515625" customWidth="1"/>
+    <col min="10" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33">
@@ -10414,7 +10463,7 @@
       </c>
       <c r="H6" s="76">
         <f>'설비현황_19~25'!H29</f>
-        <v>1814.8493999999998</v>
+        <v>0</v>
       </c>
       <c r="I6" s="76">
         <f>'건설계획표_26~38'!C29</f>
@@ -10929,8 +10978,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="76">
-        <f>'설비현황_19~25'!D33</f>
-        <v>0</v>
+        <v>124.044</v>
       </c>
       <c r="E10" s="76">
         <f>'설비현황_19~25'!E33</f>
@@ -13047,10 +13095,20 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="688c5d3b-a76a-458b-b159-91c2a1154680">
@@ -13058,15 +13116,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13246,19 +13295,19 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AC0E8B6-FC6C-47AD-8E91-EBF41CCB1712}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13444BB4-D2AE-4704-9F59-09418FDD2FE0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="688c5d3b-a76a-458b-b159-91c2a1154680"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AC0E8B6-FC6C-47AD-8E91-EBF41CCB1712}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
